--- a/output/monthly/2026-08 文献统计表.xlsx
+++ b/output/monthly/2026-08 文献统计表.xlsx
@@ -10878,7 +10878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11287,283 +11287,283 @@
         </is>
       </c>
       <c r="G18" s="38" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="24" t="n"/>
-      <c r="B19" s="25" t="n"/>
+      <c r="B19" s="24" t="n"/>
       <c r="C19" s="41" t="inlineStr">
         <is>
+          <t>Kinetic coupling derived interphase for extreme batteries</t>
+        </is>
+      </c>
+      <c r="D19" s="41" t="inlineStr">
+        <is>
+          <t>Xiulin Fan</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee04409c</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
           <t>Correction: Highly reversible zinc anode enabled by a trace-amount additive with pH buffering capability</t>
         </is>
       </c>
-      <c r="D19" s="41" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr">
         <is>
           <t>Yonggang Wang</t>
         </is>
       </c>
-      <c r="E19" s="42" t="n">
+      <c r="E20" s="42" t="n">
         <v>46258</v>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F20" s="43" t="inlineStr">
         <is>
           <t>https://doi.org/10.1039/d6ee90074g</t>
         </is>
       </c>
-      <c r="G19" s="25" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="G20" s="25" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n">
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B22" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C21" s="45" t="inlineStr">
+      <c r="C22" s="45" t="inlineStr">
         <is>
           <t>Unveiling Dual-Interface Coordination Orchestration for Durable Aqueous Zinc–Iodine Pouch Cells with Four-Electron Chemistry</t>
         </is>
       </c>
-      <c r="D21" s="45" t="inlineStr">
+      <c r="D22" s="45" t="inlineStr">
         <is>
           <t>Zhongwei Chen</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E22" s="46" t="n">
         <v>46238</v>
       </c>
-      <c r="F21" s="47" t="inlineStr">
+      <c r="F22" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c11308</t>
         </is>
       </c>
-      <c r="G21" s="45" t="n">
+      <c r="G22" s="45" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="24" t="n"/>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="48" t="inlineStr">
-        <is>
-          <t>High-Voltage Sodium–Metal Batteries with Asymmetric Fluoroalkoxylated Organoborate Anion Chemistry</t>
-        </is>
-      </c>
-      <c r="D22" s="48" t="inlineStr">
-        <is>
-          <t>Arumugam Manthiram</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c08026</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="24" t="n"/>
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="48" t="inlineStr">
         <is>
-          <t>An Electronically Coupled Interfacial Energy Descriptor for Predicting Coulombic Efficiency in Aqueous Zinc Batteries</t>
+          <t>High-Voltage Sodium–Metal Batteries with Asymmetric Fluoroalkoxylated Organoborate Anion Chemistry</t>
         </is>
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
-          <t>Xiaodong Chen</t>
+          <t>Arumugam Manthiram</t>
         </is>
       </c>
       <c r="E23" s="49" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F23" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08057</t>
+          <t>https://doi.org/10.1021/jacs.6c08026</t>
         </is>
       </c>
       <c r="G23" s="24" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="24" t="n"/>
-      <c r="B24" s="25" t="n"/>
+      <c r="B24" s="24" t="n"/>
       <c r="C24" s="48" t="inlineStr">
         <is>
-          <t>Enhanced Sodium-Ion Transport across Solid Electrolyte Interphase via Electric-Field Modulation</t>
+          <t>An Electronically Coupled Interfacial Energy Descriptor for Predicting Coulombic Efficiency in Aqueous Zinc Batteries</t>
         </is>
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Xiulin Fan</t>
+          <t>Xiaodong Chen</t>
         </is>
       </c>
       <c r="E24" s="49" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08495</t>
-        </is>
-      </c>
-      <c r="G24" s="25" t="n"/>
+          <t>https://doi.org/10.1021/jacs.6c08057</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="24" t="n"/>
-      <c r="B25" s="45" t="inlineStr">
-        <is>
-          <t>ACS Energy Letters</t>
-        </is>
-      </c>
-      <c r="C25" s="45" t="inlineStr">
-        <is>
-          <t>Decoupling Sodium Metal Artifacts from Hard Carbon Electrochemistry in Sodium-Ion Batteries</t>
-        </is>
-      </c>
-      <c r="D25" s="45" t="inlineStr">
-        <is>
-          <t>Clare P. Grey</t>
-        </is>
-      </c>
-      <c r="E25" s="46" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F25" s="47" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acsenergylett.6c01946</t>
-        </is>
-      </c>
-      <c r="G25" s="45" t="n">
-        <v>2</v>
-      </c>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="48" t="inlineStr">
+        <is>
+          <t>Enhanced Sodium-Ion Transport across Solid Electrolyte Interphase via Electric-Field Modulation</t>
+        </is>
+      </c>
+      <c r="D25" s="48" t="inlineStr">
+        <is>
+          <t>Xiulin Fan</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c08495</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="24" t="n"/>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="48" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>ACS Energy Letters</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>Decoupling Sodium Metal Artifacts from Hard Carbon Electrochemistry in Sodium-Ion Batteries</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>Clare P. Grey</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F26" s="47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acsenergylett.6c01946</t>
+        </is>
+      </c>
+      <c r="G26" s="45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="48" t="inlineStr">
         <is>
           <t>Decoding a Galvanic Corrosion-Driven Lithium Stripping Mechanism in Lithium-Free Anode Systems</t>
         </is>
       </c>
-      <c r="D26" s="48" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>Jun Lu</t>
         </is>
       </c>
-      <c r="E26" s="49" t="n">
+      <c r="E27" s="49" t="n">
         <v>46245</v>
       </c>
-      <c r="F26" s="50" t="inlineStr">
+      <c r="F27" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acsenergylett.6c00721</t>
         </is>
       </c>
-      <c r="G26" s="25" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="25" t="n"/>
-      <c r="B27" s="45" t="inlineStr">
+      <c r="G27" s="25" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>Chemical Reviews</t>
         </is>
       </c>
-      <c r="C27" s="45" t="n"/>
-      <c r="D27" s="45" t="n"/>
-      <c r="E27" s="45" t="n"/>
-      <c r="F27" s="45" t="n"/>
-      <c r="G27" s="45" t="n">
+      <c r="C28" s="45" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="45" t="n"/>
+      <c r="G28" s="45" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="51" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C28" s="52" t="inlineStr">
+      <c r="C29" s="52" t="inlineStr">
         <is>
           <t>A Polyzwitterionic “Ion‐Sponge” Interphase via In Situ Self‐Polymerization for Ultradurable Zinc Batteries</t>
         </is>
       </c>
-      <c r="D28" s="52" t="inlineStr">
+      <c r="D29" s="52" t="inlineStr">
         <is>
           <t>Shi Wang</t>
         </is>
       </c>
-      <c r="E28" s="53" t="n">
+      <c r="E29" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F28" s="54" t="inlineStr">
+      <c r="F29" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.5417029</t>
         </is>
       </c>
-      <c r="G28" s="52" t="n">
+      <c r="G29" s="52" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="55" t="inlineStr">
-        <is>
-          <t>Deciphering Kinetic Principles of Dual‐Anion Electrolytes for Extreme Fast‐Charging Lithium‐Ion Batteries</t>
-        </is>
-      </c>
-      <c r="D29" s="55" t="inlineStr">
-        <is>
-          <t>Zheng Chen</t>
-        </is>
-      </c>
-      <c r="E29" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F29" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.5861510</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="24" t="n"/>
       <c r="B30" s="24" t="n"/>
       <c r="C30" s="55" t="inlineStr">
         <is>
-          <t>Isotopic Engineering of Water Reactivity for Stable Aqueous Iron‐Metal Batteries</t>
+          <t>Deciphering Kinetic Principles of Dual‐Anion Electrolytes for Extreme Fast‐Charging Lithium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D30" s="55" t="inlineStr">
         <is>
-          <t>Hanfeng Liang</t>
+          <t>Zheng Chen</t>
         </is>
       </c>
       <c r="E30" s="56" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F30" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5007458</t>
+          <t>https://doi.org/10.1002/anie.5861510</t>
         </is>
       </c>
       <c r="G30" s="24" t="n"/>
@@ -11581,104 +11581,104 @@
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="55" t="inlineStr">
         <is>
-          <t>Ion Bridging Enables Dual‐Interface Engineering for High Capacity and Long Cycling Aqueous Zinc–Sulfur Battery</t>
+          <t>Isotopic Engineering of Water Reactivity for Stable Aqueous Iron‐Metal Batteries</t>
         </is>
       </c>
       <c r="D31" s="55" t="inlineStr">
         <is>
-          <t>Bao‐Lian Su</t>
+          <t>Hanfeng Liang</t>
         </is>
       </c>
       <c r="E31" s="56" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="F31" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9631813</t>
+          <t>https://doi.org/10.1002/anie.5007458</t>
         </is>
       </c>
       <c r="G31" s="24" t="n"/>
     </row>
-    <row r="32" ht="48" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="24" t="n"/>
       <c r="B32" s="24" t="n"/>
       <c r="C32" s="55" t="inlineStr">
         <is>
-          <t>Chain Rigidity Modulating Closed Pore and Inter‐Graphitic Domain Channels in Resin‐Derived Hard Carbon for Fast Plateau Sodium Storage</t>
+          <t>Ion Bridging Enables Dual‐Interface Engineering for High Capacity and Long Cycling Aqueous Zinc–Sulfur Battery</t>
         </is>
       </c>
       <c r="D32" s="55" t="inlineStr">
         <is>
-          <t>Huaihe Song</t>
+          <t>Bao‐Lian Su</t>
         </is>
       </c>
       <c r="E32" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F32" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6458234</t>
+          <t>https://doi.org/10.1002/anie.9631813</t>
         </is>
       </c>
       <c r="G32" s="24" t="n"/>
     </row>
-    <row r="33" ht="32" customHeight="1">
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="24" t="n"/>
       <c r="B33" s="24" t="n"/>
       <c r="C33" s="55" t="inlineStr">
         <is>
-          <t>Programming Ion‐Engineered Interphase for Practical Zinc Batteries Through Exogenous Cation‐Anion Synergy Chemistry</t>
+          <t>Chain Rigidity Modulating Closed Pore and Inter‐Graphitic Domain Channels in Resin‐Derived Hard Carbon for Fast Plateau Sodium Storage</t>
         </is>
       </c>
       <c r="D33" s="55" t="inlineStr">
         <is>
-          <t>Libao Chen</t>
+          <t>Huaihe Song</t>
         </is>
       </c>
       <c r="E33" s="56" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="F33" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3578686</t>
+          <t>https://doi.org/10.1002/anie.6458234</t>
         </is>
       </c>
       <c r="G33" s="24" t="n"/>
     </row>
-    <row r="34" ht="48" customHeight="1">
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="24" t="n"/>
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="55" t="inlineStr">
         <is>
-          <t>Electrochemically Activated Highly Reversible Sulfate Conversion Enables High‐Voltage and Large‐Volumetric‐Capacity Zinc‐Based Anion–Cation Shuttle Battery</t>
+          <t>Programming Ion‐Engineered Interphase for Practical Zinc Batteries Through Exogenous Cation‐Anion Synergy Chemistry</t>
         </is>
       </c>
       <c r="D34" s="55" t="inlineStr">
         <is>
-          <t>Bao‐Lian Su</t>
+          <t>Libao Chen</t>
         </is>
       </c>
       <c r="E34" s="56" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="F34" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3330483</t>
+          <t>https://doi.org/10.1002/anie.3578686</t>
         </is>
       </c>
       <c r="G34" s="24" t="n"/>
     </row>
-    <row r="35" ht="32" customHeight="1">
+    <row r="35" ht="48" customHeight="1">
       <c r="A35" s="24" t="n"/>
       <c r="B35" s="24" t="n"/>
       <c r="C35" s="55" t="inlineStr">
         <is>
-          <t>Transient Interfacial Electron Transfer: The Hidden Kinetic Driver of Graphite Lithiation</t>
+          <t>Electrochemically Activated Highly Reversible Sulfate Conversion Enables High‐Voltage and Large‐Volumetric‐Capacity Zinc‐Based Anion–Cation Shuttle Battery</t>
         </is>
       </c>
       <c r="D35" s="55" t="inlineStr">
         <is>
-          <t>Long Kong</t>
+          <t>Bao‐Lian Su</t>
         </is>
       </c>
       <c r="E35" s="56" t="n">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="F35" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5840654</t>
+          <t>https://doi.org/10.1002/anie.3330483</t>
         </is>
       </c>
       <c r="G35" s="24" t="n"/>
@@ -11696,66 +11696,66 @@
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="55" t="inlineStr">
         <is>
-          <t>A Stage‐Coupled View of Interfacial Reconstruction in Anode‐Free Sodium Metal Batteries</t>
+          <t>Transient Interfacial Electron Transfer: The Hidden Kinetic Driver of Graphite Lithiation</t>
         </is>
       </c>
       <c r="D36" s="55" t="inlineStr">
         <is>
-          <t>Haiyan Wang</t>
+          <t>Long Kong</t>
         </is>
       </c>
       <c r="E36" s="56" t="n">
-        <v>46257</v>
+        <v>46253</v>
       </c>
       <c r="F36" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3647021</t>
+          <t>https://doi.org/10.1002/anie.5840654</t>
         </is>
       </c>
       <c r="G36" s="24" t="n"/>
     </row>
-    <row r="37" ht="48" customHeight="1">
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="24" t="n"/>
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t>Dichalcogenide Electronegativity Engineering Enables Low‐Redox‐Potential Organic Anodes for High‐Performance Calcium‐Ion Batteries</t>
+          <t>A Stage‐Coupled View of Interfacial Reconstruction in Anode‐Free Sodium Metal Batteries</t>
         </is>
       </c>
       <c r="D37" s="55" t="inlineStr">
         <is>
-          <t>Mingxian Liu</t>
+          <t>Haiyan Wang</t>
         </is>
       </c>
       <c r="E37" s="56" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="F37" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5837924</t>
+          <t>https://doi.org/10.1002/anie.3647021</t>
         </is>
       </c>
       <c r="G37" s="24" t="n"/>
     </row>
-    <row r="38" ht="32" customHeight="1">
+    <row r="38" ht="48" customHeight="1">
       <c r="A38" s="24" t="n"/>
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="55" t="inlineStr">
         <is>
-          <t>Graphdiyne‐Based Heteronuclear Dual‐Atom Catalysts Enable High‐Energy‐Density Lithium–Sulfur Batteries</t>
+          <t>Dichalcogenide Electronegativity Engineering Enables Low‐Redox‐Potential Organic Anodes for High‐Performance Calcium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D38" s="55" t="inlineStr">
         <is>
-          <t>Guoxing Li</t>
+          <t>Mingxian Liu</t>
         </is>
       </c>
       <c r="E38" s="56" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="F38" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3002971</t>
+          <t>https://doi.org/10.1002/anie.5837924</t>
         </is>
       </c>
       <c r="G38" s="24" t="n"/>
@@ -11765,20 +11765,20 @@
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>From Passive Cocoon to Active Metamorphosis: High‐Current‐Driven Evolution of Silicon for Ultrastable Anodes</t>
+          <t>Graphdiyne‐Based Heteronuclear Dual‐Atom Catalysts Enable High‐Energy‐Density Lithium–Sulfur Batteries</t>
         </is>
       </c>
       <c r="D39" s="55" t="inlineStr">
         <is>
-          <t>Wenhong Ruan</t>
+          <t>Guoxing Li</t>
         </is>
       </c>
       <c r="E39" s="56" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="F39" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3879325</t>
+          <t>https://doi.org/10.1002/anie.3002971</t>
         </is>
       </c>
       <c r="G39" s="24" t="n"/>
@@ -11788,12 +11788,12 @@
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="55" t="inlineStr">
         <is>
-          <t>Unconventional Dendrite‐Free Deposition of Mg Metal Anodes at Low Temperatures</t>
+          <t>From Passive Cocoon to Active Metamorphosis: High‐Current‐Driven Evolution of Silicon for Ultrastable Anodes</t>
         </is>
       </c>
       <c r="D40" s="55" t="inlineStr">
         <is>
-          <t>Shuhong Jiao</t>
+          <t>Wenhong Ruan</t>
         </is>
       </c>
       <c r="E40" s="56" t="n">
@@ -11801,120 +11801,120 @@
       </c>
       <c r="F40" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2311794</t>
+          <t>https://doi.org/10.1002/anie.3879325</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="24" t="n"/>
-      <c r="B41" s="25" t="n"/>
+      <c r="B41" s="24" t="n"/>
       <c r="C41" s="55" t="inlineStr">
         <is>
+          <t>Unconventional Dendrite‐Free Deposition of Mg Metal Anodes at Low Temperatures</t>
+        </is>
+      </c>
+      <c r="D41" s="55" t="inlineStr">
+        <is>
+          <t>Shuhong Jiao</t>
+        </is>
+      </c>
+      <c r="E41" s="56" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F41" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.2311794</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
           <t>Enabling Fast Charging of Lithium‐Ion Batteries With Regioisomeric Nitrile Additives for Interphase Regulation</t>
         </is>
       </c>
-      <c r="D41" s="55" t="inlineStr">
+      <c r="D42" s="55" t="inlineStr">
         <is>
           <t>Arumugam Manthiram</t>
         </is>
       </c>
-      <c r="E41" s="56" t="n">
+      <c r="E42" s="56" t="n">
         <v>46261</v>
       </c>
-      <c r="F41" s="57" t="inlineStr">
+      <c r="F42" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.6426355</t>
         </is>
       </c>
-      <c r="G41" s="25" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="24" t="n"/>
-      <c r="B42" s="52" t="inlineStr">
-        <is>
-          <t>Advanced Materials</t>
-        </is>
-      </c>
-      <c r="C42" s="52" t="n"/>
-      <c r="D42" s="52" t="n"/>
-      <c r="E42" s="52" t="n"/>
-      <c r="F42" s="52" t="n"/>
-      <c r="G42" s="52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="48" customHeight="1">
+      <c r="G42" s="25" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="24" t="n"/>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>Advanced Energy Materials</t>
-        </is>
-      </c>
-      <c r="C43" s="52" t="inlineStr">
-        <is>
-          <t>Garnet‐Induced Amorphization of Fluoride Solid Electrolyte Interlayer Enables High‐Voltage and Large‐Capacity Lithium Metal Solid‐State Batteries</t>
-        </is>
-      </c>
-      <c r="D43" s="52" t="inlineStr">
-        <is>
-          <t>Chilin Li</t>
-        </is>
-      </c>
-      <c r="E43" s="53" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F43" s="54" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71375</t>
-        </is>
-      </c>
+          <t>Advanced Materials</t>
+        </is>
+      </c>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+      <c r="E43" s="52" t="n"/>
+      <c r="F43" s="52" t="n"/>
       <c r="G43" s="52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="24" t="n"/>
-      <c r="B44" s="24" t="n"/>
-      <c r="C44" s="55" t="inlineStr">
-        <is>
-          <t>Zinc Reverse Diffusion‐Induced Uniform Lithium Deposition in Composite Metal Anodes for High‐Performance Lithium Metal Pouch Batteries</t>
-        </is>
-      </c>
-      <c r="D44" s="55" t="inlineStr">
-        <is>
-          <t>Chunnian He</t>
-        </is>
-      </c>
-      <c r="E44" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F44" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71393</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="n"/>
+      <c r="B44" s="52" t="inlineStr">
+        <is>
+          <t>Advanced Energy Materials</t>
+        </is>
+      </c>
+      <c r="C44" s="52" t="inlineStr">
+        <is>
+          <t>Garnet‐Induced Amorphization of Fluoride Solid Electrolyte Interlayer Enables High‐Voltage and Large‐Capacity Lithium Metal Solid‐State Batteries</t>
+        </is>
+      </c>
+      <c r="D44" s="52" t="inlineStr">
+        <is>
+          <t>Chilin Li</t>
+        </is>
+      </c>
+      <c r="E44" s="53" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F44" s="54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71375</t>
+        </is>
+      </c>
+      <c r="G44" s="52" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="24" t="n"/>
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="55" t="inlineStr">
         <is>
-          <t>Nano‐Heterostructured TiO2‐TiO‐TiN/MoO3‐x‐Mo2N Composite LIB Anode With Enhanced Li+ Storage via Glycine‐assisted Anodization and Cathodic Deposition</t>
+          <t>Zinc Reverse Diffusion‐Induced Uniform Lithium Deposition in Composite Metal Anodes for High‐Performance Lithium Metal Pouch Batteries</t>
         </is>
       </c>
       <c r="D45" s="55" t="inlineStr">
         <is>
-          <t>Song‐Zhu Kure‐Chu</t>
+          <t>Chunnian He</t>
         </is>
       </c>
       <c r="E45" s="56" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F45" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71387</t>
+          <t>https://doi.org/10.1002/aenm.71393</t>
         </is>
       </c>
       <c r="G45" s="24" t="n"/>
@@ -11924,20 +11924,20 @@
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="55" t="inlineStr">
         <is>
-          <t>3D Micro‐Network Li/Al4Li9 Composite Anodes Constructed by One‐Step Melt‐Spinning for High Energy Density Lithium Metal Batteries</t>
+          <t>Nano‐Heterostructured TiO2‐TiO‐TiN/MoO3‐x‐Mo2N Composite LIB Anode With Enhanced Li+ Storage via Glycine‐assisted Anodization and Cathodic Deposition</t>
         </is>
       </c>
       <c r="D46" s="55" t="inlineStr">
         <is>
-          <t>Hongge Pan</t>
+          <t>Song‐Zhu Kure‐Chu</t>
         </is>
       </c>
       <c r="E46" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F46" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71402</t>
+          <t>https://doi.org/10.1002/aenm.71387</t>
         </is>
       </c>
       <c r="G46" s="24" t="n"/>
@@ -11947,12 +11947,12 @@
       <c r="B47" s="24" t="n"/>
       <c r="C47" s="55" t="inlineStr">
         <is>
-          <t>Biomimetic Multilayer Solid‐Electrolyte Interphase Customization for Long‐Lifespan Practical Aqueous Zinc‐Metal Batteries</t>
+          <t>3D Micro‐Network Li/Al4Li9 Composite Anodes Constructed by One‐Step Melt‐Spinning for High Energy Density Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="D47" s="55" t="inlineStr">
         <is>
-          <t>Peixin Zhang</t>
+          <t>Hongge Pan</t>
         </is>
       </c>
       <c r="E47" s="56" t="n">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="F47" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71421</t>
+          <t>https://doi.org/10.1002/aenm.71402</t>
         </is>
       </c>
       <c r="G47" s="24" t="n"/>
@@ -11970,12 +11970,12 @@
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="55" t="inlineStr">
         <is>
-          <t>Regulating Uniform Zinc Deposition via Covalently Tethered Imidazolium Cations in Polyacrylamide Hydrogel Electrolytes for Stable Aqueous Zinc Batteries</t>
+          <t>Biomimetic Multilayer Solid‐Electrolyte Interphase Customization for Long‐Lifespan Practical Aqueous Zinc‐Metal Batteries</t>
         </is>
       </c>
       <c r="D48" s="55" t="inlineStr">
         <is>
-          <t>Cheng Zhang</t>
+          <t>Peixin Zhang</t>
         </is>
       </c>
       <c r="E48" s="56" t="n">
@@ -11983,30 +11983,30 @@
       </c>
       <c r="F48" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71370</t>
+          <t>https://doi.org/10.1002/aenm.71421</t>
         </is>
       </c>
       <c r="G48" s="24" t="n"/>
     </row>
-    <row r="49" ht="32" customHeight="1">
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="24" t="n"/>
       <c r="B49" s="24" t="n"/>
       <c r="C49" s="55" t="inlineStr">
         <is>
-          <t>Defect Topology Governs Lithiation Pathways in Graphite Anodes</t>
+          <t>Regulating Uniform Zinc Deposition via Covalently Tethered Imidazolium Cations in Polyacrylamide Hydrogel Electrolytes for Stable Aqueous Zinc Batteries</t>
         </is>
       </c>
       <c r="D49" s="55" t="inlineStr">
         <is>
-          <t>Damien Saurel</t>
+          <t>Cheng Zhang</t>
         </is>
       </c>
       <c r="E49" s="56" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="F49" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71430</t>
+          <t>https://doi.org/10.1002/aenm.71370</t>
         </is>
       </c>
       <c r="G49" s="24" t="n"/>
@@ -12016,12 +12016,12 @@
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="55" t="inlineStr">
         <is>
-          <t>Multiscale Confinement Electrolyte Enables Low‐Temperature Stable Aqueous Zinc‐Iodine Batteries</t>
+          <t>Defect Topology Governs Lithiation Pathways in Graphite Anodes</t>
         </is>
       </c>
       <c r="D50" s="55" t="inlineStr">
         <is>
-          <t>Shaoming Huang</t>
+          <t>Damien Saurel</t>
         </is>
       </c>
       <c r="E50" s="56" t="n">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="F50" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71384</t>
+          <t>https://doi.org/10.1002/aenm.71430</t>
         </is>
       </c>
       <c r="G50" s="24" t="n"/>
@@ -12039,20 +12039,20 @@
       <c r="B51" s="24" t="n"/>
       <c r="C51" s="55" t="inlineStr">
         <is>
-          <t>Chemomechanically Adaptive MXene–Si–Ag Dual‐Seed Interlayer Enabling Low‐Pressure Sulfide all‐Solid‐State Batteries</t>
+          <t>Multiscale Confinement Electrolyte Enables Low‐Temperature Stable Aqueous Zinc‐Iodine Batteries</t>
         </is>
       </c>
       <c r="D51" s="55" t="inlineStr">
         <is>
-          <t>Soojin Park</t>
+          <t>Shaoming Huang</t>
         </is>
       </c>
       <c r="E51" s="56" t="n">
-        <v>46249</v>
+        <v>46247</v>
       </c>
       <c r="F51" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71461</t>
+          <t>https://doi.org/10.1002/aenm.71384</t>
         </is>
       </c>
       <c r="G51" s="24" t="n"/>
@@ -12062,12 +12062,12 @@
       <c r="B52" s="24" t="n"/>
       <c r="C52" s="55" t="inlineStr">
         <is>
-          <t>Hard Carbon Networks for Mitigating Graphite Lattice Strain Under Extreme‑Low‑Temperature Fast Charging</t>
+          <t>Chemomechanically Adaptive MXene–Si–Ag Dual‐Seed Interlayer Enabling Low‐Pressure Sulfide all‐Solid‐State Batteries</t>
         </is>
       </c>
       <c r="D52" s="55" t="inlineStr">
         <is>
-          <t>Ke‐Yu Xie</t>
+          <t>Soojin Park</t>
         </is>
       </c>
       <c r="E52" s="56" t="n">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="F52" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71446</t>
+          <t>https://doi.org/10.1002/aenm.71461</t>
         </is>
       </c>
       <c r="G52" s="24" t="n"/>
@@ -12085,12 +12085,12 @@
       <c r="B53" s="24" t="n"/>
       <c r="C53" s="55" t="inlineStr">
         <is>
-          <t>Reveal Non‐Uniform Passivation on Lithium Metal Anode With Operando Spectroscopic Ellipsometry</t>
+          <t>Hard Carbon Networks for Mitigating Graphite Lattice Strain Under Extreme‑Low‑Temperature Fast Charging</t>
         </is>
       </c>
       <c r="D53" s="55" t="inlineStr">
         <is>
-          <t>Feifei Shi</t>
+          <t>Ke‐Yu Xie</t>
         </is>
       </c>
       <c r="E53" s="56" t="n">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="F53" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71434</t>
+          <t>https://doi.org/10.1002/aenm.71446</t>
         </is>
       </c>
       <c r="G53" s="24" t="n"/>
@@ -12108,12 +12108,12 @@
       <c r="B54" s="24" t="n"/>
       <c r="C54" s="55" t="inlineStr">
         <is>
-          <t>Surface‐Fluorinated Conductive Carbon for Coupled Electron/Ion Transport Through the Graphite Anode</t>
+          <t>Reveal Non‐Uniform Passivation on Lithium Metal Anode With Operando Spectroscopic Ellipsometry</t>
         </is>
       </c>
       <c r="D54" s="55" t="inlineStr">
         <is>
-          <t>Xin He</t>
+          <t>Feifei Shi</t>
         </is>
       </c>
       <c r="E54" s="56" t="n">
@@ -12121,68 +12121,68 @@
       </c>
       <c r="F54" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71436</t>
+          <t>https://doi.org/10.1002/aenm.71434</t>
         </is>
       </c>
       <c r="G54" s="24" t="n"/>
     </row>
-    <row r="55" ht="48" customHeight="1">
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="24" t="n"/>
       <c r="B55" s="24" t="n"/>
       <c r="C55" s="55" t="inlineStr">
         <is>
-          <t>Grain‐Boundary‐Rich SEI Synergizing with an H2O‐Poor EDL Enables Multidimensional Interfacial Regulation for Stable Zn Anodes</t>
+          <t>Surface‐Fluorinated Conductive Carbon for Coupled Electron/Ion Transport Through the Graphite Anode</t>
         </is>
       </c>
       <c r="D55" s="55" t="inlineStr">
         <is>
-          <t>Xiang Gao</t>
+          <t>Xin He</t>
         </is>
       </c>
       <c r="E55" s="56" t="n">
-        <v>46252</v>
+        <v>46249</v>
       </c>
       <c r="F55" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71481</t>
+          <t>https://doi.org/10.1002/aenm.71436</t>
         </is>
       </c>
       <c r="G55" s="24" t="n"/>
     </row>
-    <row r="56" ht="32" customHeight="1">
+    <row r="56" ht="48" customHeight="1">
       <c r="A56" s="24" t="n"/>
       <c r="B56" s="24" t="n"/>
       <c r="C56" s="55" t="inlineStr">
         <is>
-          <t>Phase‐Engineered 1T/2H‐WS2 Heterostructures in Hybrid Carbon Networks for High‐Rate and Durable Sodium‐Ion Storage</t>
+          <t>Grain‐Boundary‐Rich SEI Synergizing with an H2O‐Poor EDL Enables Multidimensional Interfacial Regulation for Stable Zn Anodes</t>
         </is>
       </c>
       <c r="D56" s="55" t="inlineStr">
         <is>
-          <t>Manab Kundu</t>
+          <t>Xiang Gao</t>
         </is>
       </c>
       <c r="E56" s="56" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="F56" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71453</t>
+          <t>https://doi.org/10.1002/aenm.71481</t>
         </is>
       </c>
       <c r="G56" s="24" t="n"/>
     </row>
-    <row r="57" ht="48" customHeight="1">
+    <row r="57" ht="32" customHeight="1">
       <c r="A57" s="24" t="n"/>
       <c r="B57" s="24" t="n"/>
       <c r="C57" s="55" t="inlineStr">
         <is>
-          <t>Understanding the Electrolyte‐Hard Carbon Interphase Synergy in Sodium‐Ion Batteries: From Mechanistic Insights to Design Strategies</t>
+          <t>Phase‐Engineered 1T/2H‐WS2 Heterostructures in Hybrid Carbon Networks for High‐Rate and Durable Sodium‐Ion Storage</t>
         </is>
       </c>
       <c r="D57" s="55" t="inlineStr">
         <is>
-          <t>Xingqiao Wu</t>
+          <t>Manab Kundu</t>
         </is>
       </c>
       <c r="E57" s="56" t="n">
@@ -12190,45 +12190,45 @@
       </c>
       <c r="F57" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71425</t>
+          <t>https://doi.org/10.1002/aenm.71453</t>
         </is>
       </c>
       <c r="G57" s="24" t="n"/>
     </row>
-    <row r="58" ht="32" customHeight="1">
+    <row r="58" ht="48" customHeight="1">
       <c r="A58" s="24" t="n"/>
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>A Fluorine‐Free, Low Ion Pair Electrolyte for Transition Metal‐Free and Halogen‐Free Sodium Batteries</t>
+          <t>Understanding the Electrolyte‐Hard Carbon Interphase Synergy in Sodium‐Ion Batteries: From Mechanistic Insights to Design Strategies</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
         <is>
-          <t>Feng Lin</t>
+          <t>Xingqiao Wu</t>
         </is>
       </c>
       <c r="E58" s="56" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F58" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71422</t>
+          <t>https://doi.org/10.1002/aenm.71425</t>
         </is>
       </c>
       <c r="G58" s="24" t="n"/>
     </row>
-    <row r="59" ht="48" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="24" t="n"/>
       <c r="B59" s="24" t="n"/>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Fluoride‐Driven Interfacial Engineering: Architecting Functional Layers for High‐Performance Dendrite‐Free Li Metal Batteries</t>
+          <t>A Fluorine‐Free, Low Ion Pair Electrolyte for Transition Metal‐Free and Halogen‐Free Sodium Batteries</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
         <is>
-          <t>Hongqiang Wang</t>
+          <t>Feng Lin</t>
         </is>
       </c>
       <c r="E59" s="56" t="n">
@@ -12236,22 +12236,22 @@
       </c>
       <c r="F59" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71463</t>
+          <t>https://doi.org/10.1002/aenm.71422</t>
         </is>
       </c>
       <c r="G59" s="24" t="n"/>
     </row>
-    <row r="60" ht="32" customHeight="1">
+    <row r="60" ht="48" customHeight="1">
       <c r="A60" s="24" t="n"/>
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
-          <t>Multi‐Selective Dominant Coordination in Multi‐Salt High‐Entropy Electrolytes Toward High‐Performance Silicon Anodes</t>
+          <t>Fluoride‐Driven Interfacial Engineering: Architecting Functional Layers for High‐Performance Dendrite‐Free Li Metal Batteries</t>
         </is>
       </c>
       <c r="D60" s="55" t="inlineStr">
         <is>
-          <t>Wei‐Qiang Han</t>
+          <t>Hongqiang Wang</t>
         </is>
       </c>
       <c r="E60" s="56" t="n">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="F60" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71486</t>
+          <t>https://doi.org/10.1002/aenm.71463</t>
         </is>
       </c>
       <c r="G60" s="24" t="n"/>
@@ -12269,20 +12269,20 @@
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Composite Hydrogels With Controlled Liquid Metal Release for Dendrite‐Free Zinc Anodes</t>
+          <t>Multi‐Selective Dominant Coordination in Multi‐Salt High‐Entropy Electrolytes Toward High‐Performance Silicon Anodes</t>
         </is>
       </c>
       <c r="D61" s="55" t="inlineStr">
         <is>
-          <t>Jingyi Wu</t>
+          <t>Wei‐Qiang Han</t>
         </is>
       </c>
       <c r="E61" s="56" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="F61" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71504</t>
+          <t>https://doi.org/10.1002/aenm.71486</t>
         </is>
       </c>
       <c r="G61" s="24" t="n"/>
@@ -12292,71 +12292,79 @@
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
+          <t>Composite Hydrogels With Controlled Liquid Metal Release for Dendrite‐Free Zinc Anodes</t>
+        </is>
+      </c>
+      <c r="D62" s="55" t="inlineStr">
+        <is>
+          <t>Jingyi Wu</t>
+        </is>
+      </c>
+      <c r="E62" s="56" t="n">
+        <v>46258</v>
+      </c>
+      <c r="F62" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71504</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="n"/>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="24" t="n"/>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="55" t="inlineStr">
+        <is>
           <t>Challenges and Design Strategies Toward Aqueous Zinc‐Ion Batteries Beyond Laboratory</t>
         </is>
       </c>
-      <c r="D62" s="55" t="inlineStr">
+      <c r="D63" s="55" t="inlineStr">
         <is>
           <t>Anqiang Pan</t>
         </is>
       </c>
-      <c r="E62" s="56" t="n">
+      <c r="E63" s="56" t="n">
         <v>46259</v>
       </c>
-      <c r="F62" s="57" t="inlineStr">
+      <c r="F63" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aenm.71454</t>
         </is>
       </c>
-      <c r="G62" s="24" t="n"/>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="25" t="n"/>
-      <c r="B63" s="25" t="n"/>
-      <c r="C63" s="55" t="inlineStr">
+      <c r="G63" s="24" t="n"/>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="25" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="55" t="inlineStr">
         <is>
           <t>All‐in‐One 3D Printing for Highly‐Stretchable Zn Metal Batteries: Resolving the Dilemma Between Mechanical Compliance and Electrochemical Stability</t>
         </is>
       </c>
-      <c r="D63" s="55" t="inlineStr">
+      <c r="D64" s="55" t="inlineStr">
         <is>
           <t>Chuhong Zhang</t>
         </is>
       </c>
-      <c r="E63" s="56" t="n">
+      <c r="E64" s="56" t="n">
         <v>46264</v>
       </c>
-      <c r="F63" s="57" t="inlineStr">
+      <c r="F64" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aenm.71351</t>
         </is>
       </c>
-      <c r="G63" s="25" t="n"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="58" t="inlineStr">
+      <c r="G64" s="25" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B64" s="59" t="inlineStr">
+      <c r="B65" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
-        </is>
-      </c>
-      <c r="C64" s="59" t="n"/>
-      <c r="D64" s="59" t="n"/>
-      <c r="E64" s="59" t="n"/>
-      <c r="F64" s="59" t="n"/>
-      <c r="G64" s="59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="24" t="n"/>
-      <c r="B65" s="59" t="inlineStr">
-        <is>
-          <t>Chem</t>
         </is>
       </c>
       <c r="C65" s="59" t="n"/>
@@ -12368,10 +12376,10 @@
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="25" t="n"/>
+      <c r="A66" s="24" t="n"/>
       <c r="B66" s="59" t="inlineStr">
         <is>
-          <t>Materials Today</t>
+          <t>Chem</t>
         </is>
       </c>
       <c r="C66" s="59" t="n"/>
@@ -12383,29 +12391,29 @@
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="62" t="inlineStr">
+      <c r="A67" s="25" t="n"/>
+      <c r="B67" s="59" t="inlineStr">
+        <is>
+          <t>Materials Today</t>
+        </is>
+      </c>
+      <c r="C67" s="59" t="n"/>
+      <c r="D67" s="59" t="n"/>
+      <c r="E67" s="59" t="n"/>
+      <c r="F67" s="59" t="n"/>
+      <c r="G67" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="62" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B67" s="63" t="inlineStr">
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>PNAS</t>
-        </is>
-      </c>
-      <c r="C67" s="63" t="n"/>
-      <c r="D67" s="63" t="n"/>
-      <c r="E67" s="63" t="n"/>
-      <c r="F67" s="63" t="n"/>
-      <c r="G67" s="63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="25" t="n"/>
-      <c r="B68" s="63" t="inlineStr">
-        <is>
-          <t>National Science Review</t>
         </is>
       </c>
       <c r="C68" s="63" t="n"/>
@@ -12416,29 +12424,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="25" t="n"/>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>National Science Review</t>
+        </is>
+      </c>
+      <c r="C69" s="63" t="n"/>
+      <c r="D69" s="63" t="n"/>
+      <c r="E69" s="63" t="n"/>
+      <c r="F69" s="63" t="n"/>
+      <c r="G69" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B28:B41"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="G43:G63"/>
-    <mergeCell ref="A28:A63"/>
-    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="G44:G64"/>
+    <mergeCell ref="A29:A64"/>
+    <mergeCell ref="G29:G42"/>
+    <mergeCell ref="A22:A28"/>
     <mergeCell ref="G15:G16"/>
-    <mergeCell ref="G18:G19"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B43:B63"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="B3:B7"/>
-    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B29:B42"/>
+    <mergeCell ref="B44:B64"/>
+    <mergeCell ref="G22:G25"/>
     <mergeCell ref="G3:G7"/>
-    <mergeCell ref="G28:G41"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B26:B27"/>
     <mergeCell ref="A8:A17"/>
-    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="G18:G20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
@@ -12451,13 +12474,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId20"/>
@@ -12471,7 +12494,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId34"/>
@@ -12492,6 +12515,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15357,7 +15381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15744,487 +15768,487 @@
         </is>
       </c>
       <c r="G16" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="38" t="inlineStr">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Solubility-guided interlayer design toward balanced lithium metal plating and stripping in garnet solid-state batteries</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>Jennifer L. M. Rupp</t>
+        </is>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee03852b</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>An all-fluorinated interphase by Zn mediated reduction of organofluorine for a high energy Zinc metal pouch cell</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="inlineStr">
+        <is>
+          <t>Yizhan Wang</t>
+        </is>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee04249j</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="38" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="38" t="n">
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C20" s="45" t="inlineStr">
         <is>
           <t>An Electronically Coupled Interfacial Energy Descriptor for Predicting Coulombic Efficiency in Aqueous Zinc Batteries</t>
         </is>
       </c>
-      <c r="D18" s="45" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>Xiaodong Chen</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E20" s="46" t="n">
         <v>46242</v>
       </c>
-      <c r="F18" s="47" t="inlineStr">
+      <c r="F20" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c08057</t>
         </is>
       </c>
-      <c r="G18" s="45" t="n">
+      <c r="G20" s="45" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="24" t="n"/>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="48" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="48" t="inlineStr">
         <is>
           <t>Quantitative Dielectric Constant Engineering of the Separator for Reversible Lithium Metal Batteries</t>
         </is>
       </c>
-      <c r="D19" s="48" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Meifang Zhu</t>
         </is>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E21" s="49" t="n">
         <v>46247</v>
       </c>
-      <c r="F19" s="50" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c06934</t>
         </is>
       </c>
-      <c r="G19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>A Statistical Mechanical Framework for Predicting Fermi Contact NMR Shifts</t>
-        </is>
-      </c>
-      <c r="D20" s="48" t="inlineStr">
-        <is>
-          <t>Raphaële J. Clément</t>
-        </is>
-      </c>
-      <c r="E20" s="49" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F20" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c07045</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="48" t="inlineStr">
-        <is>
-          <t>Self-Transformed MOF-on-MXene Heterostructure as an Ion-Expedited Interphase toward Low-Temperature Multivalent Metal Batteries</t>
-        </is>
-      </c>
-      <c r="D21" s="48" t="inlineStr">
-        <is>
-          <t>Jian Wang</t>
-        </is>
-      </c>
-      <c r="E21" s="49" t="n">
-        <v>46254</v>
-      </c>
-      <c r="F21" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c10753</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="n"/>
+      <c r="G21" s="24" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="24" t="n"/>
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>A Statistical Mechanical Framework for Predicting Fermi Contact NMR Shifts</t>
+        </is>
+      </c>
+      <c r="D22" s="48" t="inlineStr">
+        <is>
+          <t>Raphaële J. Clément</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c07045</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="48" t="inlineStr">
+        <is>
+          <t>Self-Transformed MOF-on-MXene Heterostructure as an Ion-Expedited Interphase toward Low-Temperature Multivalent Metal Batteries</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>Jian Wang</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F23" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c10753</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="45" t="inlineStr">
         <is>
           <t>ACS Energy Letters</t>
         </is>
       </c>
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C24" s="45" t="inlineStr">
         <is>
           <t>Standardizing Operando Diffraction Studies for Battery Systems</t>
         </is>
       </c>
-      <c r="D22" s="45" t="inlineStr">
+      <c r="D24" s="45" t="inlineStr">
         <is>
           <t>Ashok S. Menon</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n">
+      <c r="E24" s="46" t="n">
         <v>46247</v>
       </c>
-      <c r="F22" s="47" t="inlineStr">
+      <c r="F24" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acsenergylett.6c01791</t>
         </is>
       </c>
-      <c r="G22" s="45" t="n">
+      <c r="G24" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="45" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="45" t="inlineStr">
         <is>
           <t>Chemical Reviews</t>
         </is>
       </c>
-      <c r="C23" s="45" t="n"/>
-      <c r="D23" s="45" t="n"/>
-      <c r="E23" s="45" t="n"/>
-      <c r="F23" s="45" t="n"/>
-      <c r="G23" s="45" t="n">
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+      <c r="F25" s="45" t="n"/>
+      <c r="G25" s="45" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="51" t="inlineStr">
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B24" s="52" t="inlineStr">
+      <c r="B26" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C24" s="52" t="inlineStr">
+      <c r="C26" s="52" t="inlineStr">
         <is>
           <t>Dual‐Domain Coupling‐Driven Interface Remodeling Enables Ultra‐Dilute Flame‐Retardant Electrolytes for High‐Voltage, Wide‐Temperature Batteries</t>
         </is>
       </c>
-      <c r="D24" s="52" t="inlineStr">
+      <c r="D26" s="52" t="inlineStr">
         <is>
           <t>Xing‐Long Wu</t>
         </is>
       </c>
-      <c r="E24" s="53" t="n">
+      <c r="E26" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F24" s="54" t="inlineStr">
+      <c r="F26" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.8321379</t>
         </is>
       </c>
-      <c r="G24" s="52" t="n">
+      <c r="G26" s="52" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="24" t="n"/>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="55" t="inlineStr">
-        <is>
-          <t>Reflex Charging for Anion‐Derived Solid Electrolyte Interphase Formation</t>
-        </is>
-      </c>
-      <c r="D25" s="55" t="inlineStr">
-        <is>
-          <t>Seung‐Hyeok Kim</t>
-        </is>
-      </c>
-      <c r="E25" s="56" t="n">
-        <v>46242</v>
-      </c>
-      <c r="F25" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.4035251</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="55" t="inlineStr">
-        <is>
-          <t>Supramolecular Self‐Assembly Enables Controlled Lithium Replenishment Toward High‐Performance and Sustainable Regeneration of Spent LiFePO4 Batteries</t>
-        </is>
-      </c>
-      <c r="D26" s="55" t="inlineStr">
-        <is>
-          <t>Jiaheng Zhang</t>
-        </is>
-      </c>
-      <c r="E26" s="56" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F26" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.4146793</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="48" customHeight="1">
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="24" t="n"/>
       <c r="B27" s="24" t="n"/>
       <c r="C27" s="55" t="inlineStr">
         <is>
-          <t>Vacuum‐Assisted Impurities Removing Triggered Electronic Configuration Reconstruction of Spent NCM for Ultrafast Lithium Storage</t>
+          <t>Reflex Charging for Anion‐Derived Solid Electrolyte Interphase Formation</t>
         </is>
       </c>
       <c r="D27" s="55" t="inlineStr">
         <is>
-          <t>Peng Ge</t>
+          <t>Seung‐Hyeok Kim</t>
         </is>
       </c>
       <c r="E27" s="56" t="n">
-        <v>46256</v>
+        <v>46242</v>
       </c>
       <c r="F27" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4391410</t>
+          <t>https://doi.org/10.1002/anie.4035251</t>
         </is>
       </c>
       <c r="G27" s="24" t="n"/>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="24" t="n"/>
       <c r="B28" s="24" t="n"/>
       <c r="C28" s="55" t="inlineStr">
         <is>
-          <t>Eliminating Interfacial Stress Concentration Enables High‐Energy and High‐Safety Gel Polymer Lithium Metal Pouch Cells</t>
+          <t>Supramolecular Self‐Assembly Enables Controlled Lithium Replenishment Toward High‐Performance and Sustainable Regeneration of Spent LiFePO4 Batteries</t>
         </is>
       </c>
       <c r="D28" s="55" t="inlineStr">
         <is>
-          <t>Weifeng Wei</t>
+          <t>Jiaheng Zhang</t>
         </is>
       </c>
       <c r="E28" s="56" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="F28" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5503056</t>
+          <t>https://doi.org/10.1002/anie.4146793</t>
         </is>
       </c>
       <c r="G28" s="24" t="n"/>
     </row>
-    <row r="29" ht="32" customHeight="1">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="24" t="n"/>
       <c r="B29" s="24" t="n"/>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>Synchronous Interfacial Chemistry via a Fluorine‐Free Bifunctional Additive for Ultrastable Aqueous Zinc‐Iodine Batteries</t>
+          <t>Vacuum‐Assisted Impurities Removing Triggered Electronic Configuration Reconstruction of Spent NCM for Ultrafast Lithium Storage</t>
         </is>
       </c>
       <c r="D29" s="55" t="inlineStr">
         <is>
-          <t>Xifei Li</t>
+          <t>Peng Ge</t>
         </is>
       </c>
       <c r="E29" s="56" t="n">
-        <v>46260</v>
+        <v>46256</v>
       </c>
       <c r="F29" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7649417</t>
+          <t>https://doi.org/10.1002/anie.4391410</t>
         </is>
       </c>
       <c r="G29" s="24" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="24" t="n"/>
-      <c r="B30" s="25" t="n"/>
+      <c r="B30" s="24" t="n"/>
       <c r="C30" s="55" t="inlineStr">
         <is>
-          <t>Enabling Fast Charging of Lithium‐Ion Batteries With Regioisomeric Nitrile Additives for Interphase Regulation</t>
+          <t>Eliminating Interfacial Stress Concentration Enables High‐Energy and High‐Safety Gel Polymer Lithium Metal Pouch Cells</t>
         </is>
       </c>
       <c r="D30" s="55" t="inlineStr">
         <is>
-          <t>Arumugam Manthiram</t>
+          <t>Weifeng Wei</t>
         </is>
       </c>
       <c r="E30" s="56" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="F30" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6426355</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
+          <t>https://doi.org/10.1002/anie.5503056</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="24" t="n"/>
-      <c r="B31" s="52" t="inlineStr">
-        <is>
-          <t>Advanced Materials</t>
-        </is>
-      </c>
-      <c r="C31" s="52" t="inlineStr">
-        <is>
-          <t>Giving AI a ‘case library’ to diagnose battery failures</t>
-        </is>
-      </c>
-      <c r="D31" s="52" t="inlineStr">
-        <is>
-          <t>Feng Lin</t>
-        </is>
-      </c>
-      <c r="E31" s="53" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F31" s="54" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/nsr/nwag483</t>
-        </is>
-      </c>
-      <c r="G31" s="52" t="n">
-        <v>2</v>
-      </c>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="55" t="inlineStr">
+        <is>
+          <t>Synchronous Interfacial Chemistry via a Fluorine‐Free Bifunctional Additive for Ultrastable Aqueous Zinc‐Iodine Batteries</t>
+        </is>
+      </c>
+      <c r="D31" s="55" t="inlineStr">
+        <is>
+          <t>Xifei Li</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F31" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.7649417</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="24" t="n"/>
       <c r="B32" s="25" t="n"/>
       <c r="C32" s="55" t="inlineStr">
         <is>
-          <t>Smart MOF separator towards long-cycling high-energy-density sodium-metal batteries</t>
+          <t>Enabling Fast Charging of Lithium‐Ion Batteries With Regioisomeric Nitrile Additives for Interphase Regulation</t>
         </is>
       </c>
       <c r="D32" s="55" t="inlineStr">
         <is>
-          <t>Xing-Long Wu</t>
+          <t>Arumugam Manthiram</t>
         </is>
       </c>
       <c r="E32" s="56" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F32" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag542</t>
+          <t>https://doi.org/10.1002/anie.6426355</t>
         </is>
       </c>
       <c r="G32" s="25" t="n"/>
     </row>
-    <row r="33" ht="48" customHeight="1">
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="24" t="n"/>
       <c r="B33" s="52" t="inlineStr">
         <is>
-          <t>Advanced Energy Materials</t>
+          <t>Advanced Materials</t>
         </is>
       </c>
       <c r="C33" s="52" t="inlineStr">
         <is>
-          <t>In Situ Interfacial Reconstruction Enables Sodiophilic and Ion‐Conductive Current Collectors for Anode‐Free Sodium Metal Batteries</t>
+          <t>Giving AI a ‘case library’ to diagnose battery failures</t>
         </is>
       </c>
       <c r="D33" s="52" t="inlineStr">
         <is>
-          <t>Gongkai Wang</t>
+          <t>Feng Lin</t>
         </is>
       </c>
       <c r="E33" s="53" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="F33" s="54" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71390</t>
+          <t>https://doi.org/10.1093/nsr/nwag483</t>
         </is>
       </c>
       <c r="G33" s="52" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
+      <c r="B34" s="25" t="n"/>
       <c r="C34" s="55" t="inlineStr">
         <is>
-          <t>Magnetic Insights Into Heterogeneous and Nonequilibrium Electrochemical Reactions</t>
+          <t>Smart MOF separator towards long-cycling high-energy-density sodium-metal batteries</t>
         </is>
       </c>
       <c r="D34" s="55" t="inlineStr">
         <is>
-          <t>Qiang Li</t>
+          <t>Xing-Long Wu</t>
         </is>
       </c>
       <c r="E34" s="56" t="n">
-        <v>46242</v>
+        <v>46260</v>
       </c>
       <c r="F34" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71401</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
+          <t>https://doi.org/10.1093/nsr/nwag542</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
       <c r="A35" s="24" t="n"/>
-      <c r="B35" s="24" t="n"/>
-      <c r="C35" s="55" t="inlineStr">
-        <is>
-          <t>Chemomechanically Adaptive MXene–Si–Ag Dual‐Seed Interlayer Enabling Low‐Pressure Sulfide all‐Solid‐State Batteries</t>
-        </is>
-      </c>
-      <c r="D35" s="55" t="inlineStr">
-        <is>
-          <t>Soojin Park</t>
-        </is>
-      </c>
-      <c r="E35" s="56" t="n">
-        <v>46249</v>
-      </c>
-      <c r="F35" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71461</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="n"/>
+      <c r="B35" s="52" t="inlineStr">
+        <is>
+          <t>Advanced Energy Materials</t>
+        </is>
+      </c>
+      <c r="C35" s="52" t="inlineStr">
+        <is>
+          <t>In Situ Interfacial Reconstruction Enables Sodiophilic and Ion‐Conductive Current Collectors for Anode‐Free Sodium Metal Batteries</t>
+        </is>
+      </c>
+      <c r="D35" s="52" t="inlineStr">
+        <is>
+          <t>Gongkai Wang</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F35" s="54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71390</t>
+        </is>
+      </c>
+      <c r="G35" s="52" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="24" t="n"/>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="55" t="inlineStr">
         <is>
-          <t>Surface‐Fluorinated Conductive Carbon for Coupled Electron/Ion Transport Through the Graphite Anode</t>
+          <t>Magnetic Insights Into Heterogeneous and Nonequilibrium Electrochemical Reactions</t>
         </is>
       </c>
       <c r="D36" s="55" t="inlineStr">
         <is>
-          <t>Xin He</t>
+          <t>Qiang Li</t>
         </is>
       </c>
       <c r="E36" s="56" t="n">
-        <v>46249</v>
+        <v>46242</v>
       </c>
       <c r="F36" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71436</t>
+          <t>https://doi.org/10.1002/aenm.71401</t>
         </is>
       </c>
       <c r="G36" s="24" t="n"/>
@@ -16234,12 +16258,12 @@
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t>Ultrahigh‐Loading Cathodes for Next‐Generation Lithium‐Ion Batteries</t>
+          <t>Chemomechanically Adaptive MXene–Si–Ag Dual‐Seed Interlayer Enabling Low‐Pressure Sulfide all‐Solid‐State Batteries</t>
         </is>
       </c>
       <c r="D37" s="55" t="inlineStr">
         <is>
-          <t>Weidong He</t>
+          <t>Soojin Park</t>
         </is>
       </c>
       <c r="E37" s="56" t="n">
@@ -16247,68 +16271,68 @@
       </c>
       <c r="F37" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71439</t>
+          <t>https://doi.org/10.1002/aenm.71461</t>
         </is>
       </c>
       <c r="G37" s="24" t="n"/>
     </row>
-    <row r="38" ht="48" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="24" t="n"/>
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="55" t="inlineStr">
         <is>
-          <t>Entropy‐Mediated Nonporous Polymer Separator Unlocks Ultra‐Wide Temperature Range (−70°C to 150°C) Lithium Metal Batteries</t>
+          <t>Surface‐Fluorinated Conductive Carbon for Coupled Electron/Ion Transport Through the Graphite Anode</t>
         </is>
       </c>
       <c r="D38" s="55" t="inlineStr">
         <is>
-          <t>Yuliang Gao</t>
+          <t>Xin He</t>
         </is>
       </c>
       <c r="E38" s="56" t="n">
-        <v>46253</v>
+        <v>46249</v>
       </c>
       <c r="F38" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71480</t>
+          <t>https://doi.org/10.1002/aenm.71436</t>
         </is>
       </c>
       <c r="G38" s="24" t="n"/>
     </row>
-    <row r="39" ht="48" customHeight="1">
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="24" t="n"/>
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>Fluorine‐Aligned Electrostatic Gatekeepers Regulating Polysulfide Migration for Stable Lithium–Sulfur Batteries (Adv. Energy Mater. 31/2026)</t>
+          <t>Ultrahigh‐Loading Cathodes for Next‐Generation Lithium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D39" s="55" t="inlineStr">
         <is>
-          <t>Hee‐Dae Lim</t>
+          <t>Weidong He</t>
         </is>
       </c>
       <c r="E39" s="56" t="n">
-        <v>46253</v>
+        <v>46249</v>
       </c>
       <c r="F39" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71328</t>
+          <t>https://doi.org/10.1002/aenm.71439</t>
         </is>
       </c>
       <c r="G39" s="24" t="n"/>
     </row>
-    <row r="40" ht="32" customHeight="1">
+    <row r="40" ht="48" customHeight="1">
       <c r="A40" s="24" t="n"/>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="55" t="inlineStr">
         <is>
-          <t>Regulating Interfacial Electron Density of Carbon for Stable and High‐Performance Batteries</t>
+          <t>Entropy‐Mediated Nonporous Polymer Separator Unlocks Ultra‐Wide Temperature Range (−70°C to 150°C) Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="D40" s="55" t="inlineStr">
         <is>
-          <t>Yuping Wu</t>
+          <t>Yuliang Gao</t>
         </is>
       </c>
       <c r="E40" s="56" t="n">
@@ -16316,22 +16340,22 @@
       </c>
       <c r="F40" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71466</t>
+          <t>https://doi.org/10.1002/aenm.71480</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
     </row>
-    <row r="41" ht="32" customHeight="1">
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="24" t="n"/>
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="55" t="inlineStr">
         <is>
-          <t>Separating Hydrogen Evolution From Electroplating in Zn Metal Batteries Using Scanning Electrochemical Microscopy</t>
+          <t>Fluorine‐Aligned Electrostatic Gatekeepers Regulating Polysulfide Migration for Stable Lithium–Sulfur Batteries (Adv. Energy Mater. 31/2026)</t>
         </is>
       </c>
       <c r="D41" s="55" t="inlineStr">
         <is>
-          <t>Svetlana Menkin</t>
+          <t>Hee‐Dae Lim</t>
         </is>
       </c>
       <c r="E41" s="56" t="n">
@@ -16339,22 +16363,22 @@
       </c>
       <c r="F41" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71398</t>
+          <t>https://doi.org/10.1002/aenm.71328</t>
         </is>
       </c>
       <c r="G41" s="24" t="n"/>
     </row>
-    <row r="42" ht="48" customHeight="1">
+    <row r="42" ht="32" customHeight="1">
       <c r="A42" s="24" t="n"/>
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="55" t="inlineStr">
         <is>
-          <t>Stable and Low‐Pressure Anode‐Free All‐Solid‐State Li–S Batteries Enabled by Reaction‐Derived Nanocrystalline‐Amorphous Li2S Cathodes and Deformable Sodium Current Collectors</t>
+          <t>Regulating Interfacial Electron Density of Carbon for Stable and High‐Performance Batteries</t>
         </is>
       </c>
       <c r="D42" s="55" t="inlineStr">
         <is>
-          <t>Jinkui Feng</t>
+          <t>Yuping Wu</t>
         </is>
       </c>
       <c r="E42" s="56" t="n">
@@ -16362,30 +16386,30 @@
       </c>
       <c r="F42" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71471</t>
+          <t>https://doi.org/10.1002/aenm.71466</t>
         </is>
       </c>
       <c r="G42" s="24" t="n"/>
     </row>
-    <row r="43" ht="48" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="24" t="n"/>
       <c r="B43" s="24" t="n"/>
       <c r="C43" s="55" t="inlineStr">
         <is>
-          <t>Fluoride‐Driven Interfacial Engineering: Architecting Functional Layers for High‐Performance Dendrite‐Free Li Metal Batteries</t>
+          <t>Separating Hydrogen Evolution From Electroplating in Zn Metal Batteries Using Scanning Electrochemical Microscopy</t>
         </is>
       </c>
       <c r="D43" s="55" t="inlineStr">
         <is>
-          <t>Hongqiang Wang</t>
+          <t>Svetlana Menkin</t>
         </is>
       </c>
       <c r="E43" s="56" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F43" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71463</t>
+          <t>https://doi.org/10.1002/aenm.71398</t>
         </is>
       </c>
       <c r="G43" s="24" t="n"/>
@@ -16395,43 +16419,43 @@
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="55" t="inlineStr">
         <is>
-          <t>From Top to Bottom: Manufacturing Process‐Context Aware Resolution of Energy Device Electrodes Through a 3D Diffusion Generative Model</t>
+          <t>Stable and Low‐Pressure Anode‐Free All‐Solid‐State Li–S Batteries Enabled by Reaction‐Derived Nanocrystalline‐Amorphous Li2S Cathodes and Deformable Sodium Current Collectors</t>
         </is>
       </c>
       <c r="D44" s="55" t="inlineStr">
         <is>
-          <t>Alejandro A. Franco</t>
+          <t>Jinkui Feng</t>
         </is>
       </c>
       <c r="E44" s="56" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F44" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71418</t>
+          <t>https://doi.org/10.1002/aenm.71471</t>
         </is>
       </c>
       <c r="G44" s="24" t="n"/>
     </row>
-    <row r="45" ht="64" customHeight="1">
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="24" t="n"/>
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="55" t="inlineStr">
         <is>
-          <t>High‐Spin 3d Orbital Configuration Driven by Lattice Strain‐Induced Electronic Modulation in Co4N/Co2P Composites Enables Metal–Sulfur Hybridization for Efficient Polysulfide Conversion</t>
+          <t>Fluoride‐Driven Interfacial Engineering: Architecting Functional Layers for High‐Performance Dendrite‐Free Li Metal Batteries</t>
         </is>
       </c>
       <c r="D45" s="55" t="inlineStr">
         <is>
-          <t>Junlei Qi</t>
+          <t>Hongqiang Wang</t>
         </is>
       </c>
       <c r="E45" s="56" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="F45" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71506</t>
+          <t>https://doi.org/10.1002/aenm.71463</t>
         </is>
       </c>
       <c r="G45" s="24" t="n"/>
@@ -16441,213 +16465,261 @@
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="55" t="inlineStr">
         <is>
-          <t>Temperature‐Responsive Electrical Double Layer for Self‐Adaptive Solid Electrolyte Interphase Unlocks Wide‐Temperature Aqueous Zinc Ion Batteries</t>
+          <t>From Top to Bottom: Manufacturing Process‐Context Aware Resolution of Energy Device Electrodes Through a 3D Diffusion Generative Model</t>
         </is>
       </c>
       <c r="D46" s="55" t="inlineStr">
         <is>
-          <t>Lingzhi Zhao</t>
+          <t>Alejandro A. Franco</t>
         </is>
       </c>
       <c r="E46" s="56" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="F46" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71472</t>
+          <t>https://doi.org/10.1002/aenm.71418</t>
         </is>
       </c>
       <c r="G46" s="24" t="n"/>
     </row>
-    <row r="47" ht="32" customHeight="1">
+    <row r="47" ht="64" customHeight="1">
       <c r="A47" s="24" t="n"/>
       <c r="B47" s="24" t="n"/>
       <c r="C47" s="55" t="inlineStr">
         <is>
-          <t>Challenges and Design Strategies Toward Aqueous Zinc‐Ion Batteries Beyond Laboratory</t>
+          <t>High‐Spin 3d Orbital Configuration Driven by Lattice Strain‐Induced Electronic Modulation in Co4N/Co2P Composites Enables Metal–Sulfur Hybridization for Efficient Polysulfide Conversion</t>
         </is>
       </c>
       <c r="D47" s="55" t="inlineStr">
         <is>
-          <t>Anqiang Pan</t>
+          <t>Junlei Qi</t>
         </is>
       </c>
       <c r="E47" s="56" t="n">
-        <v>46259</v>
+        <v>46256</v>
       </c>
       <c r="F47" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71454</t>
+          <t>https://doi.org/10.1002/aenm.71506</t>
         </is>
       </c>
       <c r="G47" s="24" t="n"/>
     </row>
-    <row r="48" ht="32" customHeight="1">
+    <row r="48" ht="48" customHeight="1">
       <c r="A48" s="24" t="n"/>
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="55" t="inlineStr">
         <is>
+          <t>Temperature‐Responsive Electrical Double Layer for Self‐Adaptive Solid Electrolyte Interphase Unlocks Wide‐Temperature Aqueous Zinc Ion Batteries</t>
+        </is>
+      </c>
+      <c r="D48" s="55" t="inlineStr">
+        <is>
+          <t>Lingzhi Zhao</t>
+        </is>
+      </c>
+      <c r="E48" s="56" t="n">
+        <v>46258</v>
+      </c>
+      <c r="F48" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71472</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="24" t="n"/>
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="55" t="inlineStr">
+        <is>
+          <t>Challenges and Design Strategies Toward Aqueous Zinc‐Ion Batteries Beyond Laboratory</t>
+        </is>
+      </c>
+      <c r="D49" s="55" t="inlineStr">
+        <is>
+          <t>Anqiang Pan</t>
+        </is>
+      </c>
+      <c r="E49" s="56" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F49" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71454</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
           <t>Ultrafast Synthesis of High‐Purity LiMnxFe1‐xPO4 With Locked‐Nanosize From Spent LiFePO4</t>
         </is>
       </c>
-      <c r="D48" s="55" t="inlineStr">
+      <c r="D50" s="55" t="inlineStr">
         <is>
           <t>Huiqiao Li</t>
         </is>
       </c>
-      <c r="E48" s="56" t="n">
+      <c r="E50" s="56" t="n">
         <v>46259</v>
       </c>
-      <c r="F48" s="57" t="inlineStr">
+      <c r="F50" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aenm.71487</t>
         </is>
       </c>
-      <c r="G48" s="24" t="n"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="25" t="n"/>
-      <c r="C49" s="55" t="inlineStr">
+      <c r="G50" s="24" t="n"/>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="55" t="inlineStr">
         <is>
           <t>Cellulose Materials Integrate Ion Transport, Interfacial Chemistry, and Structural Stability in Zinc Battery Systems</t>
         </is>
       </c>
-      <c r="D49" s="55" t="inlineStr">
+      <c r="D51" s="55" t="inlineStr">
         <is>
           <t>Hengwei Wang</t>
         </is>
       </c>
-      <c r="E49" s="56" t="n">
+      <c r="E51" s="56" t="n">
         <v>46264</v>
       </c>
-      <c r="F49" s="57" t="inlineStr">
+      <c r="F51" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aenm.71473</t>
         </is>
       </c>
-      <c r="G49" s="25" t="n"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="58" t="inlineStr">
+      <c r="G51" s="25" t="n"/>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B50" s="59" t="inlineStr">
+      <c r="B52" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
         </is>
       </c>
-      <c r="C50" s="59" t="inlineStr">
+      <c r="C52" s="59" t="inlineStr">
         <is>
           <t>On-demand capacity extraction through thermo-electrochemical hysteresis in metastable Li-Cu alloy</t>
         </is>
       </c>
-      <c r="D50" s="59" t="inlineStr">
+      <c r="D52" s="59" t="inlineStr">
         <is>
           <t>Yi Cui</t>
         </is>
       </c>
-      <c r="E50" s="60" t="n">
+      <c r="E52" s="60" t="n">
         <v>46253</v>
       </c>
-      <c r="F50" s="61" t="inlineStr">
+      <c r="F52" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.joule.2026.102632</t>
         </is>
       </c>
-      <c r="G50" s="59" t="n">
+      <c r="G52" s="59" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="24" t="n"/>
-      <c r="B51" s="59" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="24" t="n"/>
+      <c r="B53" s="59" t="inlineStr">
         <is>
           <t>Chem</t>
         </is>
       </c>
-      <c r="C51" s="59" t="n"/>
-      <c r="D51" s="59" t="n"/>
-      <c r="E51" s="59" t="n"/>
-      <c r="F51" s="59" t="n"/>
-      <c r="G51" s="59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="59" t="inlineStr">
-        <is>
-          <t>Materials Today</t>
-        </is>
-      </c>
-      <c r="C52" s="59" t="n"/>
-      <c r="D52" s="59" t="n"/>
-      <c r="E52" s="59" t="n"/>
-      <c r="F52" s="59" t="n"/>
-      <c r="G52" s="59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="62" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="B53" s="63" t="inlineStr">
-        <is>
-          <t>PNAS</t>
-        </is>
-      </c>
-      <c r="C53" s="63" t="n"/>
-      <c r="D53" s="63" t="n"/>
-      <c r="E53" s="63" t="n"/>
-      <c r="F53" s="63" t="n"/>
-      <c r="G53" s="63" t="n">
+      <c r="C53" s="59" t="n"/>
+      <c r="D53" s="59" t="n"/>
+      <c r="E53" s="59" t="n"/>
+      <c r="F53" s="59" t="n"/>
+      <c r="G53" s="59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="n"/>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="B54" s="59" t="inlineStr">
+        <is>
+          <t>Materials Today</t>
+        </is>
+      </c>
+      <c r="C54" s="59" t="n"/>
+      <c r="D54" s="59" t="n"/>
+      <c r="E54" s="59" t="n"/>
+      <c r="F54" s="59" t="n"/>
+      <c r="G54" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="62" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>PNAS</t>
+        </is>
+      </c>
+      <c r="C55" s="63" t="n"/>
+      <c r="D55" s="63" t="n"/>
+      <c r="E55" s="63" t="n"/>
+      <c r="F55" s="63" t="n"/>
+      <c r="G55" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="25" t="n"/>
+      <c r="B56" s="63" t="inlineStr">
         <is>
           <t>National Science Review</t>
         </is>
       </c>
-      <c r="C54" s="63" t="n"/>
-      <c r="D54" s="63" t="n"/>
-      <c r="E54" s="63" t="n"/>
-      <c r="F54" s="63" t="n"/>
-      <c r="G54" s="63" t="n">
+      <c r="C56" s="63" t="n"/>
+      <c r="D56" s="63" t="n"/>
+      <c r="E56" s="63" t="n"/>
+      <c r="F56" s="63" t="n"/>
+      <c r="G56" s="63" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A18:A23"/>
+  <mergeCells count="23">
+    <mergeCell ref="B35:B51"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A24:A49"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B18:B21"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="G33:G49"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G24:G30"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="A16:A19"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A52:A54"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B33:B49"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="A55:A56"/>
     <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B24:B30"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:A15"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="G26:G32"/>
+    <mergeCell ref="A26:A51"/>
+    <mergeCell ref="B26:B32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="G35:G51"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
@@ -16659,13 +16731,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId19"/>
@@ -16691,6 +16763,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16702,7 +16776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17332,99 +17406,99 @@
         </is>
       </c>
       <c r="G27" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="38" t="inlineStr">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>A falcon-inspired mechano-driven power cloak enabling autonomous on-body electricity supply</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>Kai Dong</t>
+        </is>
+      </c>
+      <c r="E28" s="42" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F28" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee04132a</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="38" t="n"/>
-      <c r="E28" s="38" t="n"/>
-      <c r="F28" s="38" t="n"/>
-      <c r="G28" s="38" t="n">
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="38" t="n"/>
+      <c r="G29" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="44" t="inlineStr">
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B30" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C30" s="45" t="inlineStr">
         <is>
           <t>Activity–Stability Volcano in Supported Electrocatalysis: Single Entity Correlation of Au25 Nanoclusters Between Oxygen Reduction Activity and Metal–Support Interaction</t>
         </is>
       </c>
-      <c r="D29" s="45" t="inlineStr">
+      <c r="D30" s="45" t="inlineStr">
         <is>
           <t>Wei Ma</t>
         </is>
       </c>
-      <c r="E29" s="46" t="n">
+      <c r="E30" s="46" t="n">
         <v>46241</v>
       </c>
-      <c r="F29" s="47" t="inlineStr">
+      <c r="F30" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c01996</t>
         </is>
       </c>
-      <c r="G29" s="45" t="n">
+      <c r="G30" s="45" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="24" t="n"/>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="48" t="inlineStr">
-        <is>
-          <t>Bioinspired Large-Area Polymeric Cucurbituril Monolayers with Ultrahigh-Density Nanopores Enabling Reversible Charge-Gating of Ion Transport via Host–Guest Recognition</t>
-        </is>
-      </c>
-      <c r="D30" s="48" t="inlineStr">
-        <is>
-          <t>Xue Liu</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F30" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c07373</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="n"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="24" t="n"/>
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="48" t="inlineStr">
         <is>
-          <t>Solvent-Assisted Delamination of Boridene toward High-Performance Micro-Supercapacitors and Integrated Microsystems</t>
+          <t>Bioinspired Large-Area Polymeric Cucurbituril Monolayers with Ultrahigh-Density Nanopores Enabling Reversible Charge-Gating of Ion Transport via Host–Guest Recognition</t>
         </is>
       </c>
       <c r="D31" s="48" t="inlineStr">
         <is>
-          <t>Zhong-Shuai Wu</t>
+          <t>Xue Liu</t>
         </is>
       </c>
       <c r="E31" s="49" t="n">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="F31" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08895</t>
+          <t>https://doi.org/10.1021/jacs.6c07373</t>
         </is>
       </c>
       <c r="G31" s="24" t="n"/>
@@ -17434,20 +17508,20 @@
       <c r="B32" s="24" t="n"/>
       <c r="C32" s="48" t="inlineStr">
         <is>
-          <t>Decoupling Ion Transport from Water Flow in Rigid Subnanometer Channels for Efficient Osmotic Energy Harvesting</t>
+          <t>Solvent-Assisted Delamination of Boridene toward High-Performance Micro-Supercapacitors and Integrated Microsystems</t>
         </is>
       </c>
       <c r="D32" s="48" t="inlineStr">
         <is>
-          <t>Bo Tang</t>
+          <t>Zhong-Shuai Wu</t>
         </is>
       </c>
       <c r="E32" s="49" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="F32" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c03924</t>
+          <t>https://doi.org/10.1021/jacs.6c08895</t>
         </is>
       </c>
       <c r="G32" s="24" t="n"/>
@@ -17457,20 +17531,20 @@
       <c r="B33" s="24" t="n"/>
       <c r="C33" s="48" t="inlineStr">
         <is>
-          <t>Rechargeable Aluminum-Organic Batteries with Electro-Oligomers</t>
+          <t>Decoupling Ion Transport from Water Flow in Rigid Subnanometer Channels for Efficient Osmotic Energy Harvesting</t>
         </is>
       </c>
       <c r="D33" s="48" t="inlineStr">
         <is>
-          <t>Hongjie Dai</t>
+          <t>Bo Tang</t>
         </is>
       </c>
       <c r="E33" s="49" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="F33" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09549</t>
+          <t>https://doi.org/10.1021/jacs.6c03924</t>
         </is>
       </c>
       <c r="G33" s="24" t="n"/>
@@ -17480,166 +17554,166 @@
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="48" t="inlineStr">
         <is>
-          <t>Mastering Electrocatalytic Microenvironment Achieves Aqueous Hydrogen Batteries Exceeding 200 Wh kg–1</t>
+          <t>Rechargeable Aluminum-Organic Batteries with Electro-Oligomers</t>
         </is>
       </c>
       <c r="D34" s="48" t="inlineStr">
         <is>
-          <t>Wei Chen</t>
+          <t>Hongjie Dai</t>
         </is>
       </c>
       <c r="E34" s="49" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="F34" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c05840</t>
+          <t>https://doi.org/10.1021/jacs.6c09549</t>
         </is>
       </c>
       <c r="G34" s="24" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="24" t="n"/>
-      <c r="B35" s="25" t="n"/>
+      <c r="B35" s="24" t="n"/>
       <c r="C35" s="48" t="inlineStr">
         <is>
-          <t>Interfacial Water Networks Regulate Solid–Liquid Contact Electrification</t>
+          <t>Mastering Electrocatalytic Microenvironment Achieves Aqueous Hydrogen Batteries Exceeding 200 Wh kg–1</t>
         </is>
       </c>
       <c r="D35" s="48" t="inlineStr">
         <is>
-          <t>Zuankai Wang</t>
+          <t>Wei Chen</t>
         </is>
       </c>
       <c r="E35" s="49" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="F35" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c14324</t>
-        </is>
-      </c>
-      <c r="G35" s="25" t="n"/>
+          <t>https://doi.org/10.1021/jacs.6c05840</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="24" t="n"/>
-      <c r="B36" s="45" t="inlineStr">
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>Interfacial Water Networks Regulate Solid–Liquid Contact Electrification</t>
+        </is>
+      </c>
+      <c r="D36" s="48" t="inlineStr">
+        <is>
+          <t>Zuankai Wang</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F36" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c14324</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="24" t="n"/>
+      <c r="B37" s="45" t="inlineStr">
         <is>
           <t>ACS Energy Letters</t>
         </is>
       </c>
-      <c r="C36" s="45" t="inlineStr">
+      <c r="C37" s="45" t="inlineStr">
         <is>
           <t>Recyclable Zinc Ion Structural Supercapacitor Enabled by Porous Vitrimer</t>
         </is>
       </c>
-      <c r="D36" s="45" t="inlineStr">
+      <c r="D37" s="45" t="inlineStr">
         <is>
           <t>Tse Nga Ng</t>
         </is>
       </c>
-      <c r="E36" s="46" t="n">
+      <c r="E37" s="46" t="n">
         <v>46245</v>
       </c>
-      <c r="F36" s="47" t="inlineStr">
+      <c r="F37" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acsenergylett.6c01274</t>
         </is>
       </c>
-      <c r="G36" s="45" t="n">
+      <c r="G37" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="45" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="45" t="inlineStr">
         <is>
           <t>Chemical Reviews</t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="45" t="n"/>
-      <c r="G37" s="45" t="n">
+      <c r="C38" s="45" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="45" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="51" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B38" s="52" t="inlineStr">
+      <c r="B39" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C38" s="52" t="inlineStr">
+      <c r="C39" s="52" t="inlineStr">
         <is>
           <t>Crystal Void Fraction‐Engineered Fe‐S Catalysts for Self‐Sustaining Li‐CO2 Mars Batteries</t>
         </is>
       </c>
-      <c r="D38" s="52" t="inlineStr">
+      <c r="D39" s="52" t="inlineStr">
         <is>
           <t>Min Zhou</t>
         </is>
       </c>
-      <c r="E38" s="53" t="n">
+      <c r="E39" s="53" t="n">
         <v>46241</v>
       </c>
-      <c r="F38" s="54" t="inlineStr">
+      <c r="F39" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.6292528</t>
         </is>
       </c>
-      <c r="G38" s="52" t="n">
+      <c r="G39" s="52" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="24" t="n"/>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="55" t="inlineStr">
-        <is>
-          <t>Field‐Free Spin‐Polarized Charge Transport in Chiral Co3O4 Boosts Supercapacitor Kinetics</t>
-        </is>
-      </c>
-      <c r="D39" s="55" t="inlineStr">
-        <is>
-          <t>Zhihong Nie</t>
-        </is>
-      </c>
-      <c r="E39" s="56" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F39" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.7713214</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="24" t="n"/>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="55" t="inlineStr">
         <is>
-          <t>Component Self‐Initiated Photopolymerization for Gel Polymer Electrolytes in Zinc–Air Batteries</t>
+          <t>Field‐Free Spin‐Polarized Charge Transport in Chiral Co3O4 Boosts Supercapacitor Kinetics</t>
         </is>
       </c>
       <c r="D40" s="55" t="inlineStr">
         <is>
-          <t>Qi Liu</t>
+          <t>Zhihong Nie</t>
         </is>
       </c>
       <c r="E40" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F40" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3048454</t>
+          <t>https://doi.org/10.1002/anie.7713214</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
@@ -17649,20 +17723,20 @@
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="55" t="inlineStr">
         <is>
-          <t>Moisture‐Responsive Ion‐Coupling Networks in Molecularly Engineered MoS2 Channels for Enhanced Ion Transport</t>
+          <t>Component Self‐Initiated Photopolymerization for Gel Polymer Electrolytes in Zinc–Air Batteries</t>
         </is>
       </c>
       <c r="D41" s="55" t="inlineStr">
         <is>
-          <t>Shuang Zheng</t>
+          <t>Qi Liu</t>
         </is>
       </c>
       <c r="E41" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F41" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9721428</t>
+          <t>https://doi.org/10.1002/anie.3048454</t>
         </is>
       </c>
       <c r="G41" s="24" t="n"/>
@@ -17672,43 +17746,43 @@
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="55" t="inlineStr">
         <is>
-          <t>Closed‐Loop Recyclable Solid Polymer Electrolytes via Dynamic Lipoate Cross‐Linking</t>
+          <t>Moisture‐Responsive Ion‐Coupling Networks in Molecularly Engineered MoS2 Channels for Enhanced Ion Transport</t>
         </is>
       </c>
       <c r="D42" s="55" t="inlineStr">
         <is>
-          <t>Cyrille Boyer</t>
+          <t>Shuang Zheng</t>
         </is>
       </c>
       <c r="E42" s="56" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="F42" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3540036</t>
+          <t>https://doi.org/10.1002/anie.9721428</t>
         </is>
       </c>
       <c r="G42" s="24" t="n"/>
     </row>
-    <row r="43" ht="48" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="24" t="n"/>
       <c r="B43" s="24" t="n"/>
       <c r="C43" s="55" t="inlineStr">
         <is>
-          <t>Solvation Reconfiguration Enables Two‐Electron Iodine Chemistry Through Chloride Activation for High‐Energy Zn–Iodine Flow Batteries</t>
+          <t>Closed‐Loop Recyclable Solid Polymer Electrolytes via Dynamic Lipoate Cross‐Linking</t>
         </is>
       </c>
       <c r="D43" s="55" t="inlineStr">
         <is>
-          <t>Qing Li</t>
+          <t>Cyrille Boyer</t>
         </is>
       </c>
       <c r="E43" s="56" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F43" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4798889</t>
+          <t>https://doi.org/10.1002/anie.3540036</t>
         </is>
       </c>
       <c r="G43" s="24" t="n"/>
@@ -17718,12 +17792,12 @@
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="55" t="inlineStr">
         <is>
-          <t>Visualizing Labor Division in Oxygen Electrocatalysis: Fully Exposed Ni Clusters Enabling Dual‐Site Catalysis via Asymmetric Atomic Bridging</t>
+          <t>Solvation Reconfiguration Enables Two‐Electron Iodine Chemistry Through Chloride Activation for High‐Energy Zn–Iodine Flow Batteries</t>
         </is>
       </c>
       <c r="D44" s="55" t="inlineStr">
         <is>
-          <t>Zhenbo Wang</t>
+          <t>Qing Li</t>
         </is>
       </c>
       <c r="E44" s="56" t="n">
@@ -17731,7 +17805,7 @@
       </c>
       <c r="F44" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.8680687</t>
+          <t>https://doi.org/10.1002/anie.4798889</t>
         </is>
       </c>
       <c r="G44" s="24" t="n"/>
@@ -17741,20 +17815,20 @@
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="55" t="inlineStr">
         <is>
-          <t>Tuning Polarization Fields in Zwitterionic Covalent Organic Frameworks for Efficient Photo‐Assisted Rechargeable Zinc–Air Batteries</t>
+          <t>Visualizing Labor Division in Oxygen Electrocatalysis: Fully Exposed Ni Clusters Enabling Dual‐Site Catalysis via Asymmetric Atomic Bridging</t>
         </is>
       </c>
       <c r="D45" s="55" t="inlineStr">
         <is>
-          <t>Long Chen</t>
+          <t>Zhenbo Wang</t>
         </is>
       </c>
       <c r="E45" s="56" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F45" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9559286</t>
+          <t>https://doi.org/10.1002/anie.8680687</t>
         </is>
       </c>
       <c r="G45" s="24" t="n"/>
@@ -17764,12 +17838,12 @@
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="55" t="inlineStr">
         <is>
-          <t>Ultrathin Membrane With Ion‐Specific Gating Enables Interfacial Decoupling of Conductivity–Selectivity for Aqueous Flow Batteries</t>
+          <t>Tuning Polarization Fields in Zwitterionic Covalent Organic Frameworks for Efficient Photo‐Assisted Rechargeable Zinc–Air Batteries</t>
         </is>
       </c>
       <c r="D46" s="55" t="inlineStr">
         <is>
-          <t>Yi‐Chun Lu</t>
+          <t>Long Chen</t>
         </is>
       </c>
       <c r="E46" s="56" t="n">
@@ -17777,7 +17851,7 @@
       </c>
       <c r="F46" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2958917</t>
+          <t>https://doi.org/10.1002/anie.9559286</t>
         </is>
       </c>
       <c r="G46" s="24" t="n"/>
@@ -17787,35 +17861,35 @@
       <c r="B47" s="24" t="n"/>
       <c r="C47" s="55" t="inlineStr">
         <is>
-          <t>A Bioinspired Antifreezing Electrolyte Enabling Stable and Low‐Temperature Fluoride‐Ion Batteries via Hydrogen‐Bond Reconfiguration</t>
+          <t>Ultrathin Membrane With Ion‐Specific Gating Enables Interfacial Decoupling of Conductivity–Selectivity for Aqueous Flow Batteries</t>
         </is>
       </c>
       <c r="D47" s="55" t="inlineStr">
         <is>
-          <t>Chilin Li</t>
+          <t>Yi‐Chun Lu</t>
         </is>
       </c>
       <c r="E47" s="56" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="F47" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9339272</t>
+          <t>https://doi.org/10.1002/anie.2958917</t>
         </is>
       </c>
       <c r="G47" s="24" t="n"/>
     </row>
-    <row r="48" ht="32" customHeight="1">
+    <row r="48" ht="48" customHeight="1">
       <c r="A48" s="24" t="n"/>
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="55" t="inlineStr">
         <is>
-          <t>Hierarchical Flux Competition Governs Electrochemical‐Chemical Coupling in Redox‐Mediated Batteries</t>
+          <t>A Bioinspired Antifreezing Electrolyte Enabling Stable and Low‐Temperature Fluoride‐Ion Batteries via Hydrogen‐Bond Reconfiguration</t>
         </is>
       </c>
       <c r="D48" s="55" t="inlineStr">
         <is>
-          <t>Qing Wang</t>
+          <t>Chilin Li</t>
         </is>
       </c>
       <c r="E48" s="56" t="n">
@@ -17823,22 +17897,22 @@
       </c>
       <c r="F48" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7034615</t>
+          <t>https://doi.org/10.1002/anie.9339272</t>
         </is>
       </c>
       <c r="G48" s="24" t="n"/>
     </row>
-    <row r="49" ht="48" customHeight="1">
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="24" t="n"/>
       <c r="B49" s="24" t="n"/>
       <c r="C49" s="55" t="inlineStr">
         <is>
-          <t>Solvation‐Gradient Thin‐Film Composite Membranes Decouple Ferricyanide Rejection From Hydroxide Conduction in Alkaline Zinc–Iron Flow Batteries</t>
+          <t>Hierarchical Flux Competition Governs Electrochemical‐Chemical Coupling in Redox‐Mediated Batteries</t>
         </is>
       </c>
       <c r="D49" s="55" t="inlineStr">
         <is>
-          <t>Jian Jin</t>
+          <t>Qing Wang</t>
         </is>
       </c>
       <c r="E49" s="56" t="n">
@@ -17846,226 +17920,226 @@
       </c>
       <c r="F49" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9300778</t>
+          <t>https://doi.org/10.1002/anie.7034615</t>
         </is>
       </c>
       <c r="G49" s="24" t="n"/>
     </row>
-    <row r="50" ht="32" customHeight="1">
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="24" t="n"/>
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="55" t="inlineStr">
         <is>
-          <t>Over 7500 Cycles Achieved in Platinum‐Group‐Metal‐Free Ni–H2 Battery Through Reversible Hydrogen Spillover</t>
+          <t>Solvation‐Gradient Thin‐Film Composite Membranes Decouple Ferricyanide Rejection From Hydroxide Conduction in Alkaline Zinc–Iron Flow Batteries</t>
         </is>
       </c>
       <c r="D50" s="55" t="inlineStr">
         <is>
-          <t>Shijia Mu</t>
+          <t>Jian Jin</t>
         </is>
       </c>
       <c r="E50" s="56" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="F50" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7674442</t>
+          <t>https://doi.org/10.1002/anie.9300778</t>
         </is>
       </c>
       <c r="G50" s="24" t="n"/>
     </row>
-    <row r="51" ht="48" customHeight="1">
+    <row r="51" ht="32" customHeight="1">
       <c r="A51" s="24" t="n"/>
       <c r="B51" s="24" t="n"/>
       <c r="C51" s="55" t="inlineStr">
         <is>
-          <t>LEGO‐Like Granular‐Electrode Capacitive Deionization with Ultrahigh Mass Loading for Ultrafast Electrochemical Ion Capture</t>
+          <t>Over 7500 Cycles Achieved in Platinum‐Group‐Metal‐Free Ni–H2 Battery Through Reversible Hydrogen Spillover</t>
         </is>
       </c>
       <c r="D51" s="55" t="inlineStr">
         <is>
-          <t>Jie Ma</t>
+          <t>Shijia Mu</t>
         </is>
       </c>
       <c r="E51" s="56" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="F51" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9170775</t>
+          <t>https://doi.org/10.1002/anie.7674442</t>
         </is>
       </c>
       <c r="G51" s="24" t="n"/>
     </row>
-    <row r="52" ht="32" customHeight="1">
+    <row r="52" ht="48" customHeight="1">
       <c r="A52" s="24" t="n"/>
       <c r="B52" s="24" t="n"/>
       <c r="C52" s="55" t="inlineStr">
         <is>
+          <t>LEGO‐Like Granular‐Electrode Capacitive Deionization with Ultrahigh Mass Loading for Ultrafast Electrochemical Ion Capture</t>
+        </is>
+      </c>
+      <c r="D52" s="55" t="inlineStr">
+        <is>
+          <t>Jie Ma</t>
+        </is>
+      </c>
+      <c r="E52" s="56" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F52" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.9170775</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="24" t="n"/>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="55" t="inlineStr">
+        <is>
           <t>Axial Sulfur Ligation Unlocks the Rigidity of p‐Block Aluminum Single‐Atoms for Accelerated Oxygen Reduction</t>
         </is>
       </c>
-      <c r="D52" s="55" t="inlineStr">
+      <c r="D53" s="55" t="inlineStr">
         <is>
           <t>Huishan Shang</t>
         </is>
       </c>
-      <c r="E52" s="56" t="n">
+      <c r="E53" s="56" t="n">
         <v>46260</v>
       </c>
-      <c r="F52" s="57" t="inlineStr">
+      <c r="F53" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.4525727</t>
         </is>
       </c>
-      <c r="G52" s="24" t="n"/>
-    </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="24" t="n"/>
-      <c r="B53" s="25" t="n"/>
-      <c r="C53" s="55" t="inlineStr">
+      <c r="G53" s="24" t="n"/>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="24" t="n"/>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="55" t="inlineStr">
         <is>
           <t>A Plasmonic S‐Scheme Heterojunction Achieves Broadband Response and Ultralow Overpotential of Photo‐Assisted Li─O2 Batteries</t>
         </is>
       </c>
-      <c r="D53" s="55" t="inlineStr">
+      <c r="D54" s="55" t="inlineStr">
         <is>
           <t>Zhong‐Shuai Wu</t>
         </is>
       </c>
-      <c r="E53" s="56" t="n">
+      <c r="E54" s="56" t="n">
         <v>46263</v>
       </c>
-      <c r="F53" s="57" t="inlineStr">
+      <c r="F54" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.2006350</t>
         </is>
       </c>
-      <c r="G53" s="25" t="n"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="24" t="n"/>
-      <c r="B54" s="52" t="inlineStr">
+      <c r="G54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="52" t="inlineStr">
         <is>
           <t>Advanced Materials</t>
         </is>
       </c>
-      <c r="C54" s="52" t="inlineStr">
+      <c r="C55" s="52" t="inlineStr">
         <is>
           <t>Continuously powering intelligent microrobots through an electrochemical polymer skin membrane</t>
         </is>
       </c>
-      <c r="D54" s="52" t="inlineStr">
+      <c r="D55" s="52" t="inlineStr">
         <is>
           <t>Yue Gao</t>
         </is>
       </c>
-      <c r="E54" s="53" t="n">
+      <c r="E55" s="53" t="n">
         <v>46256</v>
       </c>
-      <c r="F54" s="54" t="inlineStr">
+      <c r="F55" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/nsr/nwag529</t>
         </is>
       </c>
-      <c r="G54" s="52" t="n">
+      <c r="G55" s="52" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="24" t="n"/>
-      <c r="B55" s="25" t="n"/>
-      <c r="C55" s="55" t="inlineStr">
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="24" t="n"/>
+      <c r="B56" s="25" t="n"/>
+      <c r="C56" s="55" t="inlineStr">
         <is>
           <t>Revealing the stabilization pathway, stack validation, and techno-economic assessment of phosphonate-Fe(III) complex for near-neutral aqueous all-iron flow batteries</t>
         </is>
       </c>
-      <c r="D55" s="55" t="inlineStr">
+      <c r="D56" s="55" t="inlineStr">
         <is>
           <t>Zhong Jin</t>
         </is>
       </c>
-      <c r="E55" s="56" t="n">
+      <c r="E56" s="56" t="n">
         <v>46258</v>
       </c>
-      <c r="F55" s="57" t="inlineStr">
+      <c r="F56" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/nsr/nwag533</t>
         </is>
       </c>
-      <c r="G55" s="25" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="24" t="n"/>
-      <c r="B56" s="52" t="inlineStr">
-        <is>
-          <t>Advanced Energy Materials</t>
-        </is>
-      </c>
-      <c r="C56" s="52" t="inlineStr">
-        <is>
-          <t>Network‐Structured All Organic Composite for High‐Temperature Capacitive Energy Storage</t>
-        </is>
-      </c>
-      <c r="D56" s="52" t="inlineStr">
-        <is>
-          <t>Yang Liu</t>
-        </is>
-      </c>
-      <c r="E56" s="53" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F56" s="54" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71395</t>
-        </is>
-      </c>
-      <c r="G56" s="52" t="n">
-        <v>10</v>
-      </c>
+      <c r="G56" s="25" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="24" t="n"/>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="55" t="inlineStr">
-        <is>
-          <t>Fluoride‐Ion Batteries: Unraveling the Fundamental Science for Next‐Generation Energy Storage</t>
-        </is>
-      </c>
-      <c r="D57" s="55" t="inlineStr">
-        <is>
-          <t>Sijiang Hu</t>
-        </is>
-      </c>
-      <c r="E57" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F57" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71391</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="48" customHeight="1">
+      <c r="B57" s="52" t="inlineStr">
+        <is>
+          <t>Advanced Energy Materials</t>
+        </is>
+      </c>
+      <c r="C57" s="52" t="inlineStr">
+        <is>
+          <t>Network‐Structured All Organic Composite for High‐Temperature Capacitive Energy Storage</t>
+        </is>
+      </c>
+      <c r="D57" s="52" t="inlineStr">
+        <is>
+          <t>Yang Liu</t>
+        </is>
+      </c>
+      <c r="E57" s="53" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F57" s="54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71395</t>
+        </is>
+      </c>
+      <c r="G57" s="52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
       <c r="A58" s="24" t="n"/>
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>Topological Defect‐Engineered Cu/N–C Catalysts for Zinc‐Air Battery With Ultra‐Stable Cycling Over 2000 h at High Current Densities</t>
+          <t>Fluoride‐Ion Batteries: Unraveling the Fundamental Science for Next‐Generation Energy Storage</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
         <is>
-          <t>Ruitao Lv</t>
+          <t>Sijiang Hu</t>
         </is>
       </c>
       <c r="E58" s="56" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="F58" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71441</t>
+          <t>https://doi.org/10.1002/aenm.71391</t>
         </is>
       </c>
       <c r="G58" s="24" t="n"/>
@@ -18075,20 +18149,20 @@
       <c r="B59" s="24" t="n"/>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Half‐Electrode Absence and Asymmetric Arrangement Design Integrated With Shielding Electrodes for Boosting Sliding Triboelectric Nanogenerator Performance</t>
+          <t>Topological Defect‐Engineered Cu/N–C Catalysts for Zinc‐Air Battery With Ultra‐Stable Cycling Over 2000 h at High Current Densities</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
         <is>
-          <t>Chenguo Hu</t>
+          <t>Ruitao Lv</t>
         </is>
       </c>
       <c r="E59" s="56" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="F59" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71476</t>
+          <t>https://doi.org/10.1002/aenm.71441</t>
         </is>
       </c>
       <c r="G59" s="24" t="n"/>
@@ -18098,12 +18172,12 @@
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
-          <t>Toward In Vivo Energy Harvesters: High Piezoelectric Response in a Pharmaceutical Drug Polymorph Enabled by Monopolar Domain Architecture</t>
+          <t>Half‐Electrode Absence and Asymmetric Arrangement Design Integrated With Shielding Electrodes for Boosting Sliding Triboelectric Nanogenerator Performance</t>
         </is>
       </c>
       <c r="D60" s="55" t="inlineStr">
         <is>
-          <t>Sajesh P. Thomas</t>
+          <t>Chenguo Hu</t>
         </is>
       </c>
       <c r="E60" s="56" t="n">
@@ -18111,7 +18185,7 @@
       </c>
       <c r="F60" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71458</t>
+          <t>https://doi.org/10.1002/aenm.71476</t>
         </is>
       </c>
       <c r="G60" s="24" t="n"/>
@@ -18121,12 +18195,12 @@
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Wide‐Stable Dynamics Enabling Ultra‐High Power Density in Compact Magneto‐Mechano‐Electric Energy Harvesters for Self‐Powered Smart Grid Monitoring</t>
+          <t>Toward In Vivo Energy Harvesters: High Piezoelectric Response in a Pharmaceutical Drug Polymorph Enabled by Monopolar Domain Architecture</t>
         </is>
       </c>
       <c r="D61" s="55" t="inlineStr">
         <is>
-          <t>Ming Liu</t>
+          <t>Sajesh P. Thomas</t>
         </is>
       </c>
       <c r="E61" s="56" t="n">
@@ -18134,30 +18208,30 @@
       </c>
       <c r="F61" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71352</t>
+          <t>https://doi.org/10.1002/aenm.71458</t>
         </is>
       </c>
       <c r="G61" s="24" t="n"/>
     </row>
-    <row r="62" ht="32" customHeight="1">
+    <row r="62" ht="48" customHeight="1">
       <c r="A62" s="24" t="n"/>
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
-          <t>Sulfidation‐Carbonization Enabled Smart Thermal Management for Moisture‐Driven Energy Generators</t>
+          <t>Wide‐Stable Dynamics Enabling Ultra‐High Power Density in Compact Magneto‐Mechano‐Electric Energy Harvesters for Self‐Powered Smart Grid Monitoring</t>
         </is>
       </c>
       <c r="D62" s="55" t="inlineStr">
         <is>
-          <t>Wei Lü</t>
+          <t>Ming Liu</t>
         </is>
       </c>
       <c r="E62" s="56" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F62" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71494</t>
+          <t>https://doi.org/10.1002/aenm.71352</t>
         </is>
       </c>
       <c r="G62" s="24" t="n"/>
@@ -18167,20 +18241,20 @@
       <c r="B63" s="24" t="n"/>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>Empowering Triboelectric Nanogenerators With Origami and Kirigami Mechanics: From Metamaterials to Self‐Powered Systems</t>
+          <t>Sulfidation‐Carbonization Enabled Smart Thermal Management for Moisture‐Driven Energy Generators</t>
         </is>
       </c>
       <c r="D63" s="55" t="inlineStr">
         <is>
-          <t>Jie Wang</t>
+          <t>Wei Lü</t>
         </is>
       </c>
       <c r="E63" s="56" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="F63" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71484</t>
+          <t>https://doi.org/10.1002/aenm.71494</t>
         </is>
       </c>
       <c r="G63" s="24" t="n"/>
@@ -18190,35 +18264,35 @@
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="55" t="inlineStr">
         <is>
+          <t>Empowering Triboelectric Nanogenerators With Origami and Kirigami Mechanics: From Metamaterials to Self‐Powered Systems</t>
+        </is>
+      </c>
+      <c r="D64" s="55" t="inlineStr">
+        <is>
+          <t>Jie Wang</t>
+        </is>
+      </c>
+      <c r="E64" s="56" t="n">
+        <v>46258</v>
+      </c>
+      <c r="F64" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71484</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="n"/>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="24" t="n"/>
+      <c r="B65" s="24" t="n"/>
+      <c r="C65" s="55" t="inlineStr">
+        <is>
           <t>Cellulose Materials Integrate Ion Transport, Interfacial Chemistry, and Structural Stability in Zinc Battery Systems</t>
         </is>
       </c>
-      <c r="D64" s="55" t="inlineStr">
+      <c r="D65" s="55" t="inlineStr">
         <is>
           <t>Hengwei Wang</t>
-        </is>
-      </c>
-      <c r="E64" s="56" t="n">
-        <v>46264</v>
-      </c>
-      <c r="F64" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71473</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="n"/>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="25" t="n"/>
-      <c r="B65" s="25" t="n"/>
-      <c r="C65" s="55" t="inlineStr">
-        <is>
-          <t>Self‐Supported Flexible Film F‐Pt1/MnO2 With Long Bending Cyclability Towards Robust Wearable Al‐Air Batteries</t>
-        </is>
-      </c>
-      <c r="D65" s="55" t="inlineStr">
-        <is>
-          <t>Feilong Gong</t>
         </is>
       </c>
       <c r="E65" s="56" t="n">
@@ -18226,87 +18300,95 @@
       </c>
       <c r="F65" s="57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1002/aenm.71473</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="n"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="25" t="n"/>
+      <c r="B66" s="25" t="n"/>
+      <c r="C66" s="55" t="inlineStr">
+        <is>
+          <t>Self‐Supported Flexible Film F‐Pt1/MnO2 With Long Bending Cyclability Towards Robust Wearable Al‐Air Batteries</t>
+        </is>
+      </c>
+      <c r="D66" s="55" t="inlineStr">
+        <is>
+          <t>Feilong Gong</t>
+        </is>
+      </c>
+      <c r="E66" s="56" t="n">
+        <v>46264</v>
+      </c>
+      <c r="F66" s="57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1002/aenm.71505</t>
         </is>
       </c>
-      <c r="G65" s="25" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="58" t="inlineStr">
+      <c r="G66" s="25" t="n"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B66" s="59" t="inlineStr">
+      <c r="B67" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
         </is>
       </c>
-      <c r="C66" s="59" t="inlineStr">
+      <c r="C67" s="59" t="inlineStr">
         <is>
           <t>Continuous, fuel-cell-like operation of aluminum-air batteries via precipitate control and interfacial hydration</t>
         </is>
       </c>
-      <c r="D66" s="59" t="inlineStr">
+      <c r="D67" s="59" t="inlineStr">
         <is>
           <t>James H. Pikul</t>
         </is>
       </c>
-      <c r="E66" s="60" t="n">
+      <c r="E67" s="60" t="n">
         <v>46246</v>
       </c>
-      <c r="F66" s="61" t="inlineStr">
+      <c r="F67" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.joule.2026.102629</t>
         </is>
       </c>
-      <c r="G66" s="59" t="n">
+      <c r="G67" s="59" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="24" t="n"/>
-      <c r="B67" s="25" t="n"/>
-      <c r="C67" s="59" t="inlineStr">
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="24" t="n"/>
+      <c r="B68" s="25" t="n"/>
+      <c r="C68" s="59" t="inlineStr">
         <is>
           <t>Multiscale design principles for ultrafast ion-electron synergy in electrochemical filter capacitors</t>
         </is>
       </c>
-      <c r="D67" s="59" t="inlineStr">
+      <c r="D68" s="59" t="inlineStr">
         <is>
           <t>Liangti Qu</t>
         </is>
       </c>
-      <c r="E67" s="60" t="n">
+      <c r="E68" s="60" t="n">
         <v>46252</v>
       </c>
-      <c r="F67" s="61" t="inlineStr">
+      <c r="F68" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.joule.2026.102622</t>
         </is>
       </c>
-      <c r="G67" s="25" t="n"/>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="24" t="n"/>
-      <c r="B68" s="59" t="inlineStr">
+      <c r="G68" s="25" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="24" t="n"/>
+      <c r="B69" s="59" t="inlineStr">
         <is>
           <t>Chem</t>
-        </is>
-      </c>
-      <c r="C68" s="59" t="n"/>
-      <c r="D68" s="59" t="n"/>
-      <c r="E68" s="59" t="n"/>
-      <c r="F68" s="59" t="n"/>
-      <c r="G68" s="59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="25" t="n"/>
-      <c r="B69" s="59" t="inlineStr">
-        <is>
-          <t>Materials Today</t>
         </is>
       </c>
       <c r="C69" s="59" t="n"/>
@@ -18318,29 +18400,29 @@
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="62" t="inlineStr">
+      <c r="A70" s="25" t="n"/>
+      <c r="B70" s="59" t="inlineStr">
+        <is>
+          <t>Materials Today</t>
+        </is>
+      </c>
+      <c r="C70" s="59" t="n"/>
+      <c r="D70" s="59" t="n"/>
+      <c r="E70" s="59" t="n"/>
+      <c r="F70" s="59" t="n"/>
+      <c r="G70" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="62" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B70" s="63" t="inlineStr">
+      <c r="B71" s="63" t="inlineStr">
         <is>
           <t>PNAS</t>
-        </is>
-      </c>
-      <c r="C70" s="63" t="n"/>
-      <c r="D70" s="63" t="n"/>
-      <c r="E70" s="63" t="n"/>
-      <c r="F70" s="63" t="n"/>
-      <c r="G70" s="63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="25" t="n"/>
-      <c r="B71" s="63" t="inlineStr">
-        <is>
-          <t>National Science Review</t>
         </is>
       </c>
       <c r="C71" s="63" t="n"/>
@@ -18351,32 +18433,49 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="25" t="n"/>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>National Science Review</t>
+        </is>
+      </c>
+      <c r="C72" s="63" t="n"/>
+      <c r="D72" s="63" t="n"/>
+      <c r="E72" s="63" t="n"/>
+      <c r="F72" s="63" t="n"/>
+      <c r="G72" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
     <mergeCell ref="A12:A26"/>
+    <mergeCell ref="G57:G66"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="A67:A70"/>
     <mergeCell ref="B4:B11"/>
     <mergeCell ref="G17:G19"/>
-    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B57:B66"/>
     <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="G56:G65"/>
+    <mergeCell ref="A39:A66"/>
+    <mergeCell ref="G39:G54"/>
+    <mergeCell ref="B55:B56"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G38:G53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="G30:G36"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A30:A38"/>
+    <mergeCell ref="A71:A72"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="B56:B65"/>
-    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="B39:B54"/>
     <mergeCell ref="A2:A11"/>
-    <mergeCell ref="G29:G35"/>
-    <mergeCell ref="A38:A65"/>
-    <mergeCell ref="A29:A37"/>
-    <mergeCell ref="B38:B53"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G55:G56"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B29:B35"/>
+    <mergeCell ref="B30:B36"/>
     <mergeCell ref="G4:G11"/>
   </mergeCells>
   <hyperlinks>
@@ -18399,7 +18498,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId23"/>
@@ -18407,7 +18506,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId31"/>
@@ -18437,6 +18536,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20376,7 +20476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21126,12 +21226,12 @@
         </is>
       </c>
       <c r="G31" s="38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="24" t="n"/>
-      <c r="B32" s="25" t="n"/>
+      <c r="B32" s="24" t="n"/>
       <c r="C32" s="41" t="inlineStr">
         <is>
           <t>Insights into Ir dynamics via operando X-ray absorption spectroscopy in industrially relevant zero-gap water electrolyzers</t>
@@ -21150,90 +21250,90 @@
           <t>https://doi.org/10.1039/d6ee03447k</t>
         </is>
       </c>
-      <c r="G32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="G32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Turning the bilayer upside down delivers a record-high Ba/Co-free cathode for proton-conducting solid oxide fuel cells</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>Lei Bi</t>
+        </is>
+      </c>
+      <c r="E33" s="42" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee03721f</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n"/>
-      <c r="D33" s="38" t="n"/>
-      <c r="E33" s="38" t="n"/>
-      <c r="F33" s="38" t="n"/>
-      <c r="G33" s="38" t="n">
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="44" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B34" s="45" t="inlineStr">
+      <c r="B35" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C34" s="45" t="inlineStr">
+      <c r="C35" s="45" t="inlineStr">
         <is>
           <t>A Quantitative Examination of Catalyst Component Impacts on Hydrogen Adsorption and Spillover</t>
         </is>
       </c>
-      <c r="D34" s="45" t="inlineStr">
+      <c r="D35" s="45" t="inlineStr">
         <is>
           <t>Bert D. Chandler</t>
         </is>
       </c>
-      <c r="E34" s="46" t="n">
+      <c r="E35" s="46" t="n">
         <v>46238</v>
       </c>
-      <c r="F34" s="47" t="inlineStr">
+      <c r="F35" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c08946</t>
         </is>
       </c>
-      <c r="G34" s="45" t="n">
+      <c r="G35" s="45" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="24" t="n"/>
-      <c r="B35" s="24" t="n"/>
-      <c r="C35" s="48" t="inlineStr">
-        <is>
-          <t>Exceptionally High Proton Conductivity in Cucurbituril-Based Metal–Organic Frameworks with Subnanometer Scale Channels</t>
-        </is>
-      </c>
-      <c r="D35" s="48" t="inlineStr">
-        <is>
-          <t>Zhong-Min Su</t>
-        </is>
-      </c>
-      <c r="E35" s="49" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F35" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c11488</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="24" t="n"/>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="48" t="inlineStr">
         <is>
-          <t>Polarized Metal Nitride Solid Solutions as Electrocatalysts Enabling Ampere-Level Selective Formic Acid Synthesis</t>
+          <t>Exceptionally High Proton Conductivity in Cucurbituril-Based Metal–Organic Frameworks with Subnanometer Scale Channels</t>
         </is>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>Minghui Yang</t>
+          <t>Zhong-Min Su</t>
         </is>
       </c>
       <c r="E36" s="49" t="n">
@@ -21241,7 +21341,7 @@
       </c>
       <c r="F36" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c10367</t>
+          <t>https://doi.org/10.1021/jacs.6c11488</t>
         </is>
       </c>
       <c r="G36" s="24" t="n"/>
@@ -21251,20 +21351,20 @@
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="48" t="inlineStr">
         <is>
-          <t>Hexaphenylbenzene Nodes Reshape Hydroxide Transport Energetics in Rigid Microporous Membranes</t>
+          <t>Polarized Metal Nitride Solid Solutions as Electrocatalysts Enabling Ampere-Level Selective Formic Acid Synthesis</t>
         </is>
       </c>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>Tongwen Xu</t>
+          <t>Minghui Yang</t>
         </is>
       </c>
       <c r="E37" s="49" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="F37" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c07266</t>
+          <t>https://doi.org/10.1021/jacs.6c10367</t>
         </is>
       </c>
       <c r="G37" s="24" t="n"/>
@@ -21274,12 +21374,12 @@
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="48" t="inlineStr">
         <is>
-          <t>Water Oxidation by Molecular Catalyst Bilayers Self-Assembled on Bismuth Vanadium Oxide (BVO) Photoelectrodes</t>
+          <t>Hexaphenylbenzene Nodes Reshape Hydroxide Transport Energetics in Rigid Microporous Membranes</t>
         </is>
       </c>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>Antoni Llobet</t>
+          <t>Tongwen Xu</t>
         </is>
       </c>
       <c r="E38" s="49" t="n">
@@ -21287,53 +21387,53 @@
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08907</t>
+          <t>https://doi.org/10.1021/jacs.6c07266</t>
         </is>
       </c>
       <c r="G38" s="24" t="n"/>
     </row>
-    <row r="39" ht="48" customHeight="1">
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="24" t="n"/>
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="48" t="inlineStr">
         <is>
-          <t>Nonequilibrium-Induced Defect-Rich Bifunctional Heterojunctions for Highly Selective Paired Electrosynthesis of Ammonium Formate</t>
+          <t>Water Oxidation by Molecular Catalyst Bilayers Self-Assembled on Bismuth Vanadium Oxide (BVO) Photoelectrodes</t>
         </is>
       </c>
       <c r="D39" s="48" t="inlineStr">
         <is>
-          <t>Jieshan Qiu</t>
+          <t>Antoni Llobet</t>
         </is>
       </c>
       <c r="E39" s="49" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08564</t>
+          <t>https://doi.org/10.1021/jacs.6c08907</t>
         </is>
       </c>
       <c r="G39" s="24" t="n"/>
     </row>
-    <row r="40" ht="32" customHeight="1">
+    <row r="40" ht="48" customHeight="1">
       <c r="A40" s="24" t="n"/>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="48" t="inlineStr">
         <is>
-          <t>Essential Role of Ionic Surfactants in Nitrogen Fixation at the Interface of Microdroplets</t>
+          <t>Nonequilibrium-Induced Defect-Rich Bifunctional Heterojunctions for Highly Selective Paired Electrosynthesis of Ammonium Formate</t>
         </is>
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>Jincai Zhao</t>
+          <t>Jieshan Qiu</t>
         </is>
       </c>
       <c r="E40" s="49" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c03518</t>
+          <t>https://doi.org/10.1021/jacs.6c08564</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
@@ -21343,20 +21443,20 @@
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="48" t="inlineStr">
         <is>
-          <t>A Dual-Interlocked Electrocatalyst Design Principle for Durable AEM Water Electrolysis at Industrial Current Densities</t>
+          <t>Essential Role of Ionic Surfactants in Nitrogen Fixation at the Interface of Microdroplets</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
         <is>
-          <t>Changshui Huang</t>
+          <t>Jincai Zhao</t>
         </is>
       </c>
       <c r="E41" s="49" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c14322</t>
+          <t>https://doi.org/10.1021/jacs.6c03518</t>
         </is>
       </c>
       <c r="G41" s="24" t="n"/>
@@ -21366,12 +21466,12 @@
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="48" t="inlineStr">
         <is>
-          <t>Aligning H2 Activation with Functional-Group Polarity: K+-Promoted Switchable Hydrogenation on Pd/TiO2</t>
+          <t>A Dual-Interlocked Electrocatalyst Design Principle for Durable AEM Water Electrolysis at Industrial Current Densities</t>
         </is>
       </c>
       <c r="D42" s="48" t="inlineStr">
         <is>
-          <t>Can Li</t>
+          <t>Changshui Huang</t>
         </is>
       </c>
       <c r="E42" s="49" t="n">
@@ -21379,22 +21479,22 @@
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c10350</t>
+          <t>https://doi.org/10.1021/jacs.6c14322</t>
         </is>
       </c>
       <c r="G42" s="24" t="n"/>
     </row>
-    <row r="43" ht="48" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="24" t="n"/>
       <c r="B43" s="24" t="n"/>
       <c r="C43" s="48" t="inlineStr">
         <is>
-          <t>Programmable Vacancy Topology in High-Entropy-Alloy-Inspired Multiprincipal Alloys Directs Ru-Centered Alkaline Hydrogen Evolution</t>
+          <t>Aligning H2 Activation with Functional-Group Polarity: K+-Promoted Switchable Hydrogenation on Pd/TiO2</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
         <is>
-          <t>Yi Cui</t>
+          <t>Can Li</t>
         </is>
       </c>
       <c r="E43" s="49" t="n">
@@ -21402,30 +21502,30 @@
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09149</t>
+          <t>https://doi.org/10.1021/jacs.6c10350</t>
         </is>
       </c>
       <c r="G43" s="24" t="n"/>
     </row>
-    <row r="44" ht="32" customHeight="1">
+    <row r="44" ht="48" customHeight="1">
       <c r="A44" s="24" t="n"/>
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="48" t="inlineStr">
         <is>
-          <t>Hydrogel-Empowered Interfacial Reactive Hydrogen on Copper Enables Selective Nitrate-To-Ammonia Electrocatalysis</t>
+          <t>Programmable Vacancy Topology in High-Entropy-Alloy-Inspired Multiprincipal Alloys Directs Ru-Centered Alkaline Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>Qiang Xu</t>
+          <t>Yi Cui</t>
         </is>
       </c>
       <c r="E44" s="49" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09690</t>
+          <t>https://doi.org/10.1021/jacs.6c09149</t>
         </is>
       </c>
       <c r="G44" s="24" t="n"/>
@@ -21435,12 +21535,12 @@
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="48" t="inlineStr">
         <is>
-          <t>Toward In Situ Programming Ligand Desorption/Adsorption Dynamics of Metal Nanoparticles in Electrocatalysis</t>
+          <t>Hydrogel-Empowered Interfacial Reactive Hydrogen on Copper Enables Selective Nitrate-To-Ammonia Electrocatalysis</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
         <is>
-          <t>Wenping Hu</t>
+          <t>Qiang Xu</t>
         </is>
       </c>
       <c r="E45" s="49" t="n">
@@ -21448,7 +21548,7 @@
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12699</t>
+          <t>https://doi.org/10.1021/jacs.6c09690</t>
         </is>
       </c>
       <c r="G45" s="24" t="n"/>
@@ -21458,20 +21558,20 @@
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="48" t="inlineStr">
         <is>
-          <t>Decoupling the Impact of Surface Functionalization over Pt at the Cathode on Kinetics and Mass Transport in PEMFCs</t>
+          <t>Toward In Situ Programming Ligand Desorption/Adsorption Dynamics of Metal Nanoparticles in Electrocatalysis</t>
         </is>
       </c>
       <c r="D46" s="48" t="inlineStr">
         <is>
-          <t>Bingjun Xu</t>
+          <t>Wenping Hu</t>
         </is>
       </c>
       <c r="E46" s="49" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="F46" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c11994</t>
+          <t>https://doi.org/10.1021/jacs.6c12699</t>
         </is>
       </c>
       <c r="G46" s="24" t="n"/>
@@ -21481,20 +21581,20 @@
       <c r="B47" s="24" t="n"/>
       <c r="C47" s="48" t="inlineStr">
         <is>
-          <t>Functional Carbon-Directed Synthesis of High-Entropy Alloys with Tuned Structure for Catalysis</t>
+          <t>Decoupling the Impact of Surface Functionalization over Pt at the Cathode on Kinetics and Mass Transport in PEMFCs</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
         <is>
-          <t>Jieshan Qiu</t>
+          <t>Bingjun Xu</t>
         </is>
       </c>
       <c r="E47" s="49" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="F47" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09541</t>
+          <t>https://doi.org/10.1021/jacs.6c11994</t>
         </is>
       </c>
       <c r="G47" s="24" t="n"/>
@@ -21504,12 +21604,12 @@
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="48" t="inlineStr">
         <is>
-          <t>Molecular-Ionic Hybrid Modulates Intermediate Evolution from CO2 to Methanol at High Current Density</t>
+          <t>Functional Carbon-Directed Synthesis of High-Entropy Alloys with Tuned Structure for Catalysis</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>Buxing Han</t>
+          <t>Jieshan Qiu</t>
         </is>
       </c>
       <c r="E48" s="49" t="n">
@@ -21517,22 +21617,22 @@
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c11699</t>
+          <t>https://doi.org/10.1021/jacs.6c09541</t>
         </is>
       </c>
       <c r="G48" s="24" t="n"/>
     </row>
-    <row r="49" ht="48" customHeight="1">
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="24" t="n"/>
       <c r="B49" s="24" t="n"/>
       <c r="C49" s="48" t="inlineStr">
         <is>
-          <t>Nanobubble Radical-Driven N2 Hydrogenation for Sustainable Ammonia Production: A Haber-Bosch Alternative under Mild Conditions</t>
+          <t>Molecular-Ionic Hybrid Modulates Intermediate Evolution from CO2 to Methanol at High Current Density</t>
         </is>
       </c>
       <c r="D49" s="48" t="inlineStr">
         <is>
-          <t>Guanglu Ge</t>
+          <t>Buxing Han</t>
         </is>
       </c>
       <c r="E49" s="49" t="n">
@@ -21540,30 +21640,30 @@
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c06081</t>
+          <t>https://doi.org/10.1021/jacs.6c11699</t>
         </is>
       </c>
       <c r="G49" s="24" t="n"/>
     </row>
-    <row r="50" ht="32" customHeight="1">
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="24" t="n"/>
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="48" t="inlineStr">
         <is>
-          <t>Geometry-Dependent Electronic Structure for Enhanced Ammonia Synthesis: From Nanoparticle to Nanosheet and Metallene</t>
+          <t>Nanobubble Radical-Driven N2 Hydrogenation for Sustainable Ammonia Production: A Haber-Bosch Alternative under Mild Conditions</t>
         </is>
       </c>
       <c r="D50" s="48" t="inlineStr">
         <is>
-          <t>Lilong Jiang</t>
+          <t>Guanglu Ge</t>
         </is>
       </c>
       <c r="E50" s="49" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12661</t>
+          <t>https://doi.org/10.1021/jacs.6c06081</t>
         </is>
       </c>
       <c r="G50" s="24" t="n"/>
@@ -21573,35 +21673,35 @@
       <c r="B51" s="24" t="n"/>
       <c r="C51" s="48" t="inlineStr">
         <is>
-          <t>Lattice-Nitrogen-Mediated Electrochemical Nitrate Reduction Boosted by Single-Atom Antimony Doping</t>
+          <t>Geometry-Dependent Electronic Structure for Enhanced Ammonia Synthesis: From Nanoparticle to Nanosheet and Metallene</t>
         </is>
       </c>
       <c r="D51" s="48" t="inlineStr">
         <is>
-          <t>Hongfei Cheng</t>
+          <t>Lilong Jiang</t>
         </is>
       </c>
       <c r="E51" s="49" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12366</t>
+          <t>https://doi.org/10.1021/jacs.6c12661</t>
         </is>
       </c>
       <c r="G51" s="24" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="24" t="n"/>
-      <c r="B52" s="25" t="n"/>
+      <c r="B52" s="24" t="n"/>
       <c r="C52" s="48" t="inlineStr">
         <is>
-          <t>Main-Group Potassium-Assisted Dual-Site Relay Breaks the Activity–Stability Trade-Off in Acidic Oxygen Reduction</t>
+          <t>Lattice-Nitrogen-Mediated Electrochemical Nitrate Reduction Boosted by Single-Atom Antimony Doping</t>
         </is>
       </c>
       <c r="D52" s="48" t="inlineStr">
         <is>
-          <t>Zhenxing Liang</t>
+          <t>Hongfei Cheng</t>
         </is>
       </c>
       <c r="E52" s="49" t="n">
@@ -21609,159 +21709,159 @@
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12145</t>
-        </is>
-      </c>
-      <c r="G52" s="25" t="n"/>
+          <t>https://doi.org/10.1021/jacs.6c12366</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="24" t="n"/>
-      <c r="B53" s="45" t="inlineStr">
-        <is>
-          <t>ACS Energy Letters</t>
-        </is>
-      </c>
-      <c r="C53" s="45" t="inlineStr">
-        <is>
-          <t>Building a Physics-Aware AI Ecosystem for Solid-State Hydrogen Storage Materials</t>
-        </is>
-      </c>
-      <c r="D53" s="45" t="inlineStr">
-        <is>
-          <t>Hao Li</t>
-        </is>
-      </c>
-      <c r="E53" s="46" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F53" s="47" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acsenergylett.6c01856</t>
-        </is>
-      </c>
-      <c r="G53" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
+      <c r="B53" s="25" t="n"/>
+      <c r="C53" s="48" t="inlineStr">
+        <is>
+          <t>Main-Group Potassium-Assisted Dual-Site Relay Breaks the Activity–Stability Trade-Off in Acidic Oxygen Reduction</t>
+        </is>
+      </c>
+      <c r="D53" s="48" t="inlineStr">
+        <is>
+          <t>Zhenxing Liang</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="n">
+        <v>46256</v>
+      </c>
+      <c r="F53" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c12145</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="n"/>
+    </row>
+    <row r="54" ht="32" customHeight="1">
       <c r="A54" s="24" t="n"/>
       <c r="B54" s="45" t="inlineStr">
         <is>
+          <t>ACS Energy Letters</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="inlineStr">
+        <is>
+          <t>Building a Physics-Aware AI Ecosystem for Solid-State Hydrogen Storage Materials</t>
+        </is>
+      </c>
+      <c r="D54" s="45" t="inlineStr">
+        <is>
+          <t>Hao Li</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F54" s="47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acsenergylett.6c01856</t>
+        </is>
+      </c>
+      <c r="G54" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="45" t="inlineStr">
+        <is>
           <t>Chemical Reviews</t>
         </is>
       </c>
-      <c r="C54" s="45" t="inlineStr">
+      <c r="C55" s="45" t="inlineStr">
         <is>
           <t>A Review of Ammonia (NH3) Adsorption in Porous Solids</t>
         </is>
       </c>
-      <c r="D54" s="45" t="inlineStr">
+      <c r="D55" s="45" t="inlineStr">
         <is>
           <t>Michael Tsapatsis</t>
         </is>
       </c>
-      <c r="E54" s="46" t="n">
+      <c r="E55" s="46" t="n">
         <v>46251</v>
       </c>
-      <c r="F54" s="47" t="inlineStr">
+      <c r="F55" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acs.chemrev.6c00035</t>
         </is>
       </c>
-      <c r="G54" s="45" t="n">
+      <c r="G55" s="45" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="25" t="n"/>
-      <c r="B55" s="25" t="n"/>
-      <c r="C55" s="48" t="inlineStr">
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="25" t="n"/>
+      <c r="B56" s="25" t="n"/>
+      <c r="C56" s="48" t="inlineStr">
         <is>
           <t>Recent Advances and Future Perspectives of Proton-Conducting Electrolytes for Reversible Solid Oxide Cells</t>
         </is>
       </c>
-      <c r="D55" s="48" t="inlineStr">
+      <c r="D56" s="48" t="inlineStr">
         <is>
           <t>Meilin Liu</t>
         </is>
       </c>
-      <c r="E55" s="49" t="n">
+      <c r="E56" s="49" t="n">
         <v>46254</v>
       </c>
-      <c r="F55" s="50" t="inlineStr">
+      <c r="F56" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acs.chemrev.5c00529</t>
         </is>
       </c>
-      <c r="G55" s="25" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="51" t="inlineStr">
+      <c r="G56" s="25" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B56" s="52" t="inlineStr">
+      <c r="B57" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C56" s="52" t="inlineStr">
+      <c r="C57" s="52" t="inlineStr">
         <is>
           <t>Electronic‐Geometric Pre‐Compensation Enables Intermetallic RhSb Bimetallenes for Efficient Nitrite Electroreduction</t>
         </is>
       </c>
-      <c r="D56" s="52" t="inlineStr">
+      <c r="D57" s="52" t="inlineStr">
         <is>
           <t>Yu Chen</t>
         </is>
       </c>
-      <c r="E56" s="53" t="n">
+      <c r="E57" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F56" s="54" t="inlineStr">
+      <c r="F57" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.9586956</t>
         </is>
       </c>
-      <c r="G56" s="52" t="n">
+      <c r="G57" s="52" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="24" t="n"/>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="55" t="inlineStr">
-        <is>
-          <t>In Situ Explosion Induced “Stress + Defect” Structure for Enhanced Hydrogen Evolution Reaction</t>
-        </is>
-      </c>
-      <c r="D57" s="55" t="inlineStr">
-        <is>
-          <t>Siping Pang</t>
-        </is>
-      </c>
-      <c r="E57" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F57" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.4584169</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="48" customHeight="1">
+    <row r="58" ht="32" customHeight="1">
       <c r="A58" s="24" t="n"/>
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>Key Drivers of Activity and Selectivity in Cu‐Based Catalysts for Methanol Synthesis From CO2: Insights From Atomically Dispersed Promoters</t>
+          <t>In Situ Explosion Induced “Stress + Defect” Structure for Enhanced Hydrogen Evolution Reaction</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
         <is>
-          <t>Atsushi Urakawa</t>
+          <t>Siping Pang</t>
         </is>
       </c>
       <c r="E58" s="56" t="n">
@@ -21769,7 +21869,7 @@
       </c>
       <c r="F58" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2693293</t>
+          <t>https://doi.org/10.1002/anie.4584169</t>
         </is>
       </c>
       <c r="G58" s="24" t="n"/>
@@ -21779,12 +21879,12 @@
       <c r="B59" s="24" t="n"/>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Modulating Local Coordination in Single‐Atom Catalysts: From Fundamental Concepts to Emerging Breakthroughs in Electrocatalysis</t>
+          <t>Key Drivers of Activity and Selectivity in Cu‐Based Catalysts for Methanol Synthesis From CO2: Insights From Atomically Dispersed Promoters</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
         <is>
-          <t>Harun Tüysüz</t>
+          <t>Atsushi Urakawa</t>
         </is>
       </c>
       <c r="E59" s="56" t="n">
@@ -21792,22 +21892,22 @@
       </c>
       <c r="F59" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3059499</t>
+          <t>https://doi.org/10.1002/anie.2693293</t>
         </is>
       </c>
       <c r="G59" s="24" t="n"/>
     </row>
-    <row r="60" ht="32" customHeight="1">
+    <row r="60" ht="48" customHeight="1">
       <c r="A60" s="24" t="n"/>
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
-          <t>Natural Sunlight IR‐Driven Highly Efficient Synthesis of Acetaldehyde From Bioethanol Over Cu/Fe2O3</t>
+          <t>Modulating Local Coordination in Single‐Atom Catalysts: From Fundamental Concepts to Emerging Breakthroughs in Electrocatalysis</t>
         </is>
       </c>
       <c r="D60" s="55" t="inlineStr">
         <is>
-          <t>Junwang Tang</t>
+          <t>Harun Tüysüz</t>
         </is>
       </c>
       <c r="E60" s="56" t="n">
@@ -21815,7 +21915,7 @@
       </c>
       <c r="F60" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9513626</t>
+          <t>https://doi.org/10.1002/anie.3059499</t>
         </is>
       </c>
       <c r="G60" s="24" t="n"/>
@@ -21825,12 +21925,12 @@
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Unconventional‐Phase Pd20Te7 Octahedra With High‐Index Facets for Oxygen Reduction</t>
+          <t>Natural Sunlight IR‐Driven Highly Efficient Synthesis of Acetaldehyde From Bioethanol Over Cu/Fe2O3</t>
         </is>
       </c>
       <c r="D61" s="55" t="inlineStr">
         <is>
-          <t>Xiaoqing Huang</t>
+          <t>Junwang Tang</t>
         </is>
       </c>
       <c r="E61" s="56" t="n">
@@ -21838,7 +21938,7 @@
       </c>
       <c r="F61" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9215475</t>
+          <t>https://doi.org/10.1002/anie.9513626</t>
         </is>
       </c>
       <c r="G61" s="24" t="n"/>
@@ -21848,20 +21948,20 @@
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
-          <t>A Bimetallic Covalent Organic Framework Photonic Synaptic Electrocatalysts</t>
+          <t>Unconventional‐Phase Pd20Te7 Octahedra With High‐Index Facets for Oxygen Reduction</t>
         </is>
       </c>
       <c r="D62" s="55" t="inlineStr">
         <is>
-          <t>Wenping Hu</t>
+          <t>Xiaoqing Huang</t>
         </is>
       </c>
       <c r="E62" s="56" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F62" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2636151</t>
+          <t>https://doi.org/10.1002/anie.9215475</t>
         </is>
       </c>
       <c r="G62" s="24" t="n"/>
@@ -21871,12 +21971,12 @@
       <c r="B63" s="24" t="n"/>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>Modulated Structure‐Electronic Coupling at Pt/CeOx–TiO2 Interfaces Boosts Low‐Temperature Preferential CO Oxidation</t>
+          <t>A Bimetallic Covalent Organic Framework Photonic Synaptic Electrocatalysts</t>
         </is>
       </c>
       <c r="D63" s="55" t="inlineStr">
         <is>
-          <t>Hyun You Kim</t>
+          <t>Wenping Hu</t>
         </is>
       </c>
       <c r="E63" s="56" t="n">
@@ -21884,22 +21984,22 @@
       </c>
       <c r="F63" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7158452</t>
+          <t>https://doi.org/10.1002/anie.2636151</t>
         </is>
       </c>
       <c r="G63" s="24" t="n"/>
     </row>
-    <row r="64" ht="64" customHeight="1">
+    <row r="64" ht="32" customHeight="1">
       <c r="A64" s="24" t="n"/>
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="55" t="inlineStr">
         <is>
-          <t>Surface Hydroxyl Steered Adsorption Configuration for Efficient Photocatalysis Coupling Hydrogen Evolution and 5‐Hydroxymethylfurfural Selective Oxidation Toward 2,5‐Furandicarboxylic Acid Production</t>
+          <t>Modulated Structure‐Electronic Coupling at Pt/CeOx–TiO2 Interfaces Boosts Low‐Temperature Preferential CO Oxidation</t>
         </is>
       </c>
       <c r="D64" s="55" t="inlineStr">
         <is>
-          <t>Shaohua Shen</t>
+          <t>Hyun You Kim</t>
         </is>
       </c>
       <c r="E64" s="56" t="n">
@@ -21907,30 +22007,30 @@
       </c>
       <c r="F64" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3914874</t>
+          <t>https://doi.org/10.1002/anie.7158452</t>
         </is>
       </c>
       <c r="G64" s="24" t="n"/>
     </row>
-    <row r="65" ht="32" customHeight="1">
+    <row r="65" ht="64" customHeight="1">
       <c r="A65" s="24" t="n"/>
       <c r="B65" s="24" t="n"/>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>Cr‐Leaching Induced Vacancy Engineering for High‐Performance Anion Exchange Membrane Water Electrolysis</t>
+          <t>Surface Hydroxyl Steered Adsorption Configuration for Efficient Photocatalysis Coupling Hydrogen Evolution and 5‐Hydroxymethylfurfural Selective Oxidation Toward 2,5‐Furandicarboxylic Acid Production</t>
         </is>
       </c>
       <c r="D65" s="55" t="inlineStr">
         <is>
-          <t>Guoxiong Wang</t>
+          <t>Shaohua Shen</t>
         </is>
       </c>
       <c r="E65" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F65" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9991550</t>
+          <t>https://doi.org/10.1002/anie.3914874</t>
         </is>
       </c>
       <c r="G65" s="24" t="n"/>
@@ -21940,35 +22040,35 @@
       <c r="B66" s="24" t="n"/>
       <c r="C66" s="55" t="inlineStr">
         <is>
-          <t>Chlorination‐Induced Symmetry Breaking in Cu Single‐Atom Sites for Boosting Electrocatalytic Nitrate Reduction to Ammonia</t>
+          <t>Cr‐Leaching Induced Vacancy Engineering for High‐Performance Anion Exchange Membrane Water Electrolysis</t>
         </is>
       </c>
       <c r="D66" s="55" t="inlineStr">
         <is>
-          <t>Jingyu Sun</t>
+          <t>Guoxiong Wang</t>
         </is>
       </c>
       <c r="E66" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F66" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9873433</t>
+          <t>https://doi.org/10.1002/anie.9991550</t>
         </is>
       </c>
       <c r="G66" s="24" t="n"/>
     </row>
-    <row r="67" ht="48" customHeight="1">
+    <row r="67" ht="32" customHeight="1">
       <c r="A67" s="24" t="n"/>
       <c r="B67" s="24" t="n"/>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>Hydrophilic RuGd Alloy Redirecting Interfacial Water Adsorption Configuration for Long‐Term and Ampere‐Level Hydrogen Evolution</t>
+          <t>Chlorination‐Induced Symmetry Breaking in Cu Single‐Atom Sites for Boosting Electrocatalytic Nitrate Reduction to Ammonia</t>
         </is>
       </c>
       <c r="D67" s="55" t="inlineStr">
         <is>
-          <t>Gengtao Fu</t>
+          <t>Jingyu Sun</t>
         </is>
       </c>
       <c r="E67" s="56" t="n">
@@ -21976,7 +22076,7 @@
       </c>
       <c r="F67" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6236000</t>
+          <t>https://doi.org/10.1002/anie.9873433</t>
         </is>
       </c>
       <c r="G67" s="24" t="n"/>
@@ -21986,12 +22086,12 @@
       <c r="B68" s="24" t="n"/>
       <c r="C68" s="55" t="inlineStr">
         <is>
-          <t>Oxophilic Gallium Single‐Atom Regulating Micropore‐Confined Os Atomic Clusters Enables Efficient Alkaline Hydrogen Electrocatalysis</t>
+          <t>Hydrophilic RuGd Alloy Redirecting Interfacial Water Adsorption Configuration for Long‐Term and Ampere‐Level Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D68" s="55" t="inlineStr">
         <is>
-          <t>Shaojun Guo</t>
+          <t>Gengtao Fu</t>
         </is>
       </c>
       <c r="E68" s="56" t="n">
@@ -21999,7 +22099,7 @@
       </c>
       <c r="F68" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2044894</t>
+          <t>https://doi.org/10.1002/anie.6236000</t>
         </is>
       </c>
       <c r="G68" s="24" t="n"/>
@@ -22009,81 +22109,81 @@
       <c r="B69" s="24" t="n"/>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Hydroxyl Surface Enrichment Strategy to Achieve Dual‐Mechanism Pathway for Overcoming the Activity–Stability Trade‐Off of Oxygen Evolution Reaction</t>
+          <t>Oxophilic Gallium Single‐Atom Regulating Micropore‐Confined Os Atomic Clusters Enables Efficient Alkaline Hydrogen Electrocatalysis</t>
         </is>
       </c>
       <c r="D69" s="55" t="inlineStr">
         <is>
-          <t>Dapeng Cao</t>
+          <t>Shaojun Guo</t>
         </is>
       </c>
       <c r="E69" s="56" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="F69" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7969121</t>
+          <t>https://doi.org/10.1002/anie.2044894</t>
         </is>
       </c>
       <c r="G69" s="24" t="n"/>
     </row>
-    <row r="70" ht="32" customHeight="1">
+    <row r="70" ht="48" customHeight="1">
       <c r="A70" s="24" t="n"/>
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="55" t="inlineStr">
         <is>
-          <t>Tuning Reaction Pathways by Controlling Atomic Assembly on Oxide Clusters</t>
+          <t>Hydroxyl Surface Enrichment Strategy to Achieve Dual‐Mechanism Pathway for Overcoming the Activity–Stability Trade‐Off of Oxygen Evolution Reaction</t>
         </is>
       </c>
       <c r="D70" s="55" t="inlineStr">
         <is>
-          <t>Jin Wang</t>
+          <t>Dapeng Cao</t>
         </is>
       </c>
       <c r="E70" s="56" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="F70" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4503768</t>
+          <t>https://doi.org/10.1002/anie.7969121</t>
         </is>
       </c>
       <c r="G70" s="24" t="n"/>
     </row>
-    <row r="71" ht="48" customHeight="1">
+    <row r="71" ht="32" customHeight="1">
       <c r="A71" s="24" t="n"/>
       <c r="B71" s="24" t="n"/>
       <c r="C71" s="55" t="inlineStr">
         <is>
-          <t>A Full‐Spectrum‐Responsive MOF‐on‐MOF Heterojunction Photocatalyst for Concurrent Nitrate Reduction and Biomass Oxidation</t>
+          <t>Tuning Reaction Pathways by Controlling Atomic Assembly on Oxide Clusters</t>
         </is>
       </c>
       <c r="D71" s="55" t="inlineStr">
         <is>
-          <t>Chao Liu</t>
+          <t>Jin Wang</t>
         </is>
       </c>
       <c r="E71" s="56" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F71" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.8582451</t>
+          <t>https://doi.org/10.1002/anie.4503768</t>
         </is>
       </c>
       <c r="G71" s="24" t="n"/>
     </row>
-    <row r="72" ht="32" customHeight="1">
+    <row r="72" ht="48" customHeight="1">
       <c r="A72" s="24" t="n"/>
       <c r="B72" s="24" t="n"/>
       <c r="C72" s="55" t="inlineStr">
         <is>
-          <t>Accelerating H* Redistribution via Hydrogen Spillover for Enhanced Electrochemical Hydrogen Production From Formaldehyde</t>
+          <t>A Full‐Spectrum‐Responsive MOF‐on‐MOF Heterojunction Photocatalyst for Concurrent Nitrate Reduction and Biomass Oxidation</t>
         </is>
       </c>
       <c r="D72" s="55" t="inlineStr">
         <is>
-          <t>Yang Hou</t>
+          <t>Chao Liu</t>
         </is>
       </c>
       <c r="E72" s="56" t="n">
@@ -22091,7 +22191,7 @@
       </c>
       <c r="F72" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5574811</t>
+          <t>https://doi.org/10.1002/anie.8582451</t>
         </is>
       </c>
       <c r="G72" s="24" t="n"/>
@@ -22101,12 +22201,12 @@
       <c r="B73" s="24" t="n"/>
       <c r="C73" s="55" t="inlineStr">
         <is>
-          <t>Enhanced Photocatalytic Hydrogen Production Assisted by Seawater Ions</t>
+          <t>Accelerating H* Redistribution via Hydrogen Spillover for Enhanced Electrochemical Hydrogen Production From Formaldehyde</t>
         </is>
       </c>
       <c r="D73" s="55" t="inlineStr">
         <is>
-          <t>Hai‐Long Jiang</t>
+          <t>Yang Hou</t>
         </is>
       </c>
       <c r="E73" s="56" t="n">
@@ -22114,7 +22214,7 @@
       </c>
       <c r="F73" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3256076</t>
+          <t>https://doi.org/10.1002/anie.5574811</t>
         </is>
       </c>
       <c r="G73" s="24" t="n"/>
@@ -22124,12 +22224,12 @@
       <c r="B74" s="24" t="n"/>
       <c r="C74" s="55" t="inlineStr">
         <is>
-          <t>Mimicking Enzymatic Proton Channeling Enables Near‐Unity Selective Ammonia Electrosynthesis Beyond Neutral Limits</t>
+          <t>Enhanced Photocatalytic Hydrogen Production Assisted by Seawater Ions</t>
         </is>
       </c>
       <c r="D74" s="55" t="inlineStr">
         <is>
-          <t>Zhimin Chen</t>
+          <t>Hai‐Long Jiang</t>
         </is>
       </c>
       <c r="E74" s="56" t="n">
@@ -22137,7 +22237,7 @@
       </c>
       <c r="F74" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2808377</t>
+          <t>https://doi.org/10.1002/anie.3256076</t>
         </is>
       </c>
       <c r="G74" s="24" t="n"/>
@@ -22147,12 +22247,12 @@
       <c r="B75" s="24" t="n"/>
       <c r="C75" s="55" t="inlineStr">
         <is>
-          <t>RuCo Nanoalloy Catalysts Obtained From In‐Situ Reconstruction of High‐Entropy Oxides for Green Ammonia Synthesis</t>
+          <t>Mimicking Enzymatic Proton Channeling Enables Near‐Unity Selective Ammonia Electrosynthesis Beyond Neutral Limits</t>
         </is>
       </c>
       <c r="D75" s="55" t="inlineStr">
         <is>
-          <t>Hideo Hosono</t>
+          <t>Zhimin Chen</t>
         </is>
       </c>
       <c r="E75" s="56" t="n">
@@ -22160,76 +22260,76 @@
       </c>
       <c r="F75" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9715444</t>
+          <t>https://doi.org/10.1002/anie.2808377</t>
         </is>
       </c>
       <c r="G75" s="24" t="n"/>
     </row>
-    <row r="76" ht="48" customHeight="1">
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="24" t="n"/>
       <c r="B76" s="24" t="n"/>
       <c r="C76" s="55" t="inlineStr">
         <is>
-          <t>Highly Selective Electrocatalytic Ammonia Synthesis Enabled by Spatial Separation of Active Hydrogen Capture and Spillover Sites</t>
+          <t>RuCo Nanoalloy Catalysts Obtained From In‐Situ Reconstruction of High‐Entropy Oxides for Green Ammonia Synthesis</t>
         </is>
       </c>
       <c r="D76" s="55" t="inlineStr">
         <is>
-          <t>Honggang Fu</t>
+          <t>Hideo Hosono</t>
         </is>
       </c>
       <c r="E76" s="56" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F76" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5589616</t>
+          <t>https://doi.org/10.1002/anie.9715444</t>
         </is>
       </c>
       <c r="G76" s="24" t="n"/>
     </row>
-    <row r="77" ht="64" customHeight="1">
+    <row r="77" ht="48" customHeight="1">
       <c r="A77" s="24" t="n"/>
       <c r="B77" s="24" t="n"/>
       <c r="C77" s="55" t="inlineStr">
         <is>
-          <t>Pt‐Mediated Co‐Adsorption of Hydroxyl and Nitrogen‐Heterocyclic Species Over Cu/CuO Heterostructure Enhances Coupled Azotriazole Electrosynthesis and Dual‐Electrode Hydrogen Production</t>
+          <t>Highly Selective Electrocatalytic Ammonia Synthesis Enabled by Spatial Separation of Active Hydrogen Capture and Spillover Sites</t>
         </is>
       </c>
       <c r="D77" s="55" t="inlineStr">
         <is>
-          <t>Zhengxiao Guo</t>
+          <t>Honggang Fu</t>
         </is>
       </c>
       <c r="E77" s="56" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="F77" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3766558</t>
+          <t>https://doi.org/10.1002/anie.5589616</t>
         </is>
       </c>
       <c r="G77" s="24" t="n"/>
     </row>
-    <row r="78" ht="32" customHeight="1">
+    <row r="78" ht="64" customHeight="1">
       <c r="A78" s="24" t="n"/>
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="55" t="inlineStr">
         <is>
-          <t>Chirality‐Driven Piezocatalysis in MOFs: Achieving Efficient Cocatalyst‐Free Hydrogen Evolution</t>
+          <t>Pt‐Mediated Co‐Adsorption of Hydroxyl and Nitrogen‐Heterocyclic Species Over Cu/CuO Heterostructure Enhances Coupled Azotriazole Electrosynthesis and Dual‐Electrode Hydrogen Production</t>
         </is>
       </c>
       <c r="D78" s="55" t="inlineStr">
         <is>
-          <t>Tianyi Ma</t>
+          <t>Zhengxiao Guo</t>
         </is>
       </c>
       <c r="E78" s="56" t="n">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="F78" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3163680</t>
+          <t>https://doi.org/10.1002/anie.3766558</t>
         </is>
       </c>
       <c r="G78" s="24" t="n"/>
@@ -22239,12 +22339,12 @@
       <c r="B79" s="24" t="n"/>
       <c r="C79" s="55" t="inlineStr">
         <is>
-          <t>Electrocatalytic Deuterated Nitric Acid Reduction to Deuterated Ammonia</t>
+          <t>Chirality‐Driven Piezocatalysis in MOFs: Achieving Efficient Cocatalyst‐Free Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D79" s="55" t="inlineStr">
         <is>
-          <t>Yifu Yu</t>
+          <t>Tianyi Ma</t>
         </is>
       </c>
       <c r="E79" s="56" t="n">
@@ -22252,7 +22352,7 @@
       </c>
       <c r="F79" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1338385</t>
+          <t>https://doi.org/10.1002/anie.3163680</t>
         </is>
       </c>
       <c r="G79" s="24" t="n"/>
@@ -22262,12 +22362,12 @@
       <c r="B80" s="24" t="n"/>
       <c r="C80" s="55" t="inlineStr">
         <is>
-          <t>Intermediate‐Mediated Selectivity in Electrocatalytic Nitrate Reduction for Nitrogen Product Synthesis</t>
+          <t>Electrocatalytic Deuterated Nitric Acid Reduction to Deuterated Ammonia</t>
         </is>
       </c>
       <c r="D80" s="55" t="inlineStr">
         <is>
-          <t>Xiao Zhang</t>
+          <t>Yifu Yu</t>
         </is>
       </c>
       <c r="E80" s="56" t="n">
@@ -22275,7 +22375,7 @@
       </c>
       <c r="F80" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3154221</t>
+          <t>https://doi.org/10.1002/anie.1338385</t>
         </is>
       </c>
       <c r="G80" s="24" t="n"/>
@@ -22285,12 +22385,12 @@
       <c r="B81" s="24" t="n"/>
       <c r="C81" s="55" t="inlineStr">
         <is>
-          <t>Light‐Activated Dual‐Site Pathway Enables Efficient Hydrogen Release From Dodecahydro‐N‐ethylcarbazole</t>
+          <t>Intermediate‐Mediated Selectivity in Electrocatalytic Nitrate Reduction for Nitrogen Product Synthesis</t>
         </is>
       </c>
       <c r="D81" s="55" t="inlineStr">
         <is>
-          <t>Xuebin Yu</t>
+          <t>Xiao Zhang</t>
         </is>
       </c>
       <c r="E81" s="56" t="n">
@@ -22298,7 +22398,7 @@
       </c>
       <c r="F81" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1230832</t>
+          <t>https://doi.org/10.1002/anie.3154221</t>
         </is>
       </c>
       <c r="G81" s="24" t="n"/>
@@ -22308,20 +22408,20 @@
       <c r="B82" s="24" t="n"/>
       <c r="C82" s="55" t="inlineStr">
         <is>
-          <t>Asymmetric Dipole‐Field Engineering in Chiral Mesostructures for Efficient Photocatalytic N2 Reduction</t>
+          <t>Light‐Activated Dual‐Site Pathway Enables Efficient Hydrogen Release From Dodecahydro‐N‐ethylcarbazole</t>
         </is>
       </c>
       <c r="D82" s="55" t="inlineStr">
         <is>
-          <t>Zhijie Yang</t>
+          <t>Xuebin Yu</t>
         </is>
       </c>
       <c r="E82" s="56" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="F82" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9685756</t>
+          <t>https://doi.org/10.1002/anie.1230832</t>
         </is>
       </c>
       <c r="G82" s="24" t="n"/>
@@ -22331,12 +22431,12 @@
       <c r="B83" s="24" t="n"/>
       <c r="C83" s="55" t="inlineStr">
         <is>
-          <t>De Novo Design of a Protein Binder to Probe Gas Channel and Enhance the Oxygen Tolerance of [NiFe]‐Hydrogenase</t>
+          <t>Asymmetric Dipole‐Field Engineering in Chiral Mesostructures for Efficient Photocatalytic N2 Reduction</t>
         </is>
       </c>
       <c r="D83" s="55" t="inlineStr">
         <is>
-          <t>Liyun Zhang</t>
+          <t>Zhijie Yang</t>
         </is>
       </c>
       <c r="E83" s="56" t="n">
@@ -22344,7 +22444,7 @@
       </c>
       <c r="F83" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6395554</t>
+          <t>https://doi.org/10.1002/anie.9685756</t>
         </is>
       </c>
       <c r="G83" s="24" t="n"/>
@@ -22354,12 +22454,12 @@
       <c r="B84" s="24" t="n"/>
       <c r="C84" s="55" t="inlineStr">
         <is>
-          <t>Rerouting Oxygen Evolution Through Interfacial Carbonate Chemistry in Near‐Neutral Seawater Electrolysis</t>
+          <t>De Novo Design of a Protein Binder to Probe Gas Channel and Enhance the Oxygen Tolerance of [NiFe]‐Hydrogenase</t>
         </is>
       </c>
       <c r="D84" s="55" t="inlineStr">
         <is>
-          <t>Ken Sakaushi</t>
+          <t>Liyun Zhang</t>
         </is>
       </c>
       <c r="E84" s="56" t="n">
@@ -22367,30 +22467,30 @@
       </c>
       <c r="F84" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9159016</t>
+          <t>https://doi.org/10.1002/anie.6395554</t>
         </is>
       </c>
       <c r="G84" s="24" t="n"/>
     </row>
-    <row r="85" ht="48" customHeight="1">
+    <row r="85" ht="32" customHeight="1">
       <c r="A85" s="24" t="n"/>
       <c r="B85" s="24" t="n"/>
       <c r="C85" s="55" t="inlineStr">
         <is>
-          <t>Single Atom Catalysis Enables Preferential Middle‐Ring Dehydrogenation of Perhydro‐Dibenzyltoluene for Low‐Temperature Hydrogen Production</t>
+          <t>Rerouting Oxygen Evolution Through Interfacial Carbonate Chemistry in Near‐Neutral Seawater Electrolysis</t>
         </is>
       </c>
       <c r="D85" s="55" t="inlineStr">
         <is>
-          <t>Tao Zhang</t>
+          <t>Ken Sakaushi</t>
         </is>
       </c>
       <c r="E85" s="56" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="F85" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6119233</t>
+          <t>https://doi.org/10.1002/anie.9159016</t>
         </is>
       </c>
       <c r="G85" s="24" t="n"/>
@@ -22400,35 +22500,35 @@
       <c r="B86" s="24" t="n"/>
       <c r="C86" s="55" t="inlineStr">
         <is>
+          <t>Single Atom Catalysis Enables Preferential Middle‐Ring Dehydrogenation of Perhydro‐Dibenzyltoluene for Low‐Temperature Hydrogen Production</t>
+        </is>
+      </c>
+      <c r="D86" s="55" t="inlineStr">
+        <is>
+          <t>Tao Zhang</t>
+        </is>
+      </c>
+      <c r="E86" s="56" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F86" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.6119233</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="n"/>
+    </row>
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="24" t="n"/>
+      <c r="B87" s="24" t="n"/>
+      <c r="C87" s="55" t="inlineStr">
+        <is>
           <t>A Triple‐Site Engineered Heterojunction Photocatalyst for Full‐Spectrum NH3 Synthesis via Synergistic Promotion of Water Oxidation and Nitrate Reduction</t>
         </is>
       </c>
-      <c r="D86" s="55" t="inlineStr">
+      <c r="D87" s="55" t="inlineStr">
         <is>
           <t>Chao Liu</t>
-        </is>
-      </c>
-      <c r="E86" s="56" t="n">
-        <v>46263</v>
-      </c>
-      <c r="F86" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.9657393</t>
-        </is>
-      </c>
-      <c r="G86" s="24" t="n"/>
-    </row>
-    <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="24" t="n"/>
-      <c r="B87" s="25" t="n"/>
-      <c r="C87" s="55" t="inlineStr">
-        <is>
-          <t>Conjugation‐Controlled Ion Response in One‐Dimensional Covalent Organic Frameworks for Seawater Photocatalysis</t>
-        </is>
-      </c>
-      <c r="D87" s="55" t="inlineStr">
-        <is>
-          <t>Bo Tang</t>
         </is>
       </c>
       <c r="E87" s="56" t="n">
@@ -22436,82 +22536,82 @@
       </c>
       <c r="F87" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7279758</t>
-        </is>
-      </c>
-      <c r="G87" s="25" t="n"/>
+          <t>https://doi.org/10.1002/anie.9657393</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="24" t="n"/>
-      <c r="B88" s="52" t="inlineStr">
+      <c r="B88" s="25" t="n"/>
+      <c r="C88" s="55" t="inlineStr">
+        <is>
+          <t>Conjugation‐Controlled Ion Response in One‐Dimensional Covalent Organic Frameworks for Seawater Photocatalysis</t>
+        </is>
+      </c>
+      <c r="D88" s="55" t="inlineStr">
+        <is>
+          <t>Bo Tang</t>
+        </is>
+      </c>
+      <c r="E88" s="56" t="n">
+        <v>46263</v>
+      </c>
+      <c r="F88" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.7279758</t>
+        </is>
+      </c>
+      <c r="G88" s="25" t="n"/>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="24" t="n"/>
+      <c r="B89" s="52" t="inlineStr">
         <is>
           <t>Advanced Materials</t>
         </is>
       </c>
-      <c r="C88" s="52" t="inlineStr">
+      <c r="C89" s="52" t="inlineStr">
         <is>
           <t>Steering the reaction pathway of methane-to-oxygenates with zero CO2 production via photo–thermal catalysis</t>
         </is>
       </c>
-      <c r="D88" s="52" t="inlineStr">
+      <c r="D89" s="52" t="inlineStr">
         <is>
           <t>Li Tan</t>
         </is>
       </c>
-      <c r="E88" s="53" t="n">
+      <c r="E89" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F88" s="54" t="inlineStr">
+      <c r="F89" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/nsr/nwag472</t>
         </is>
       </c>
-      <c r="G88" s="52" t="n">
+      <c r="G89" s="52" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="89" ht="48" customHeight="1">
-      <c r="A89" s="24" t="n"/>
-      <c r="B89" s="24" t="n"/>
-      <c r="C89" s="55" t="inlineStr">
-        <is>
-          <t>Electron delocalization in a fullerene-dumbbell triad: synergistically optimizing carrier dynamics for boosting photocatalytic hydrogen evolution</t>
-        </is>
-      </c>
-      <c r="D89" s="55" t="inlineStr">
-        <is>
-          <t>Chunli Bai</t>
-        </is>
-      </c>
-      <c r="E89" s="56" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F89" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/nsr/nwag479</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="n"/>
-    </row>
-    <row r="90" ht="32" customHeight="1">
+    <row r="90" ht="48" customHeight="1">
       <c r="A90" s="24" t="n"/>
       <c r="B90" s="24" t="n"/>
       <c r="C90" s="55" t="inlineStr">
         <is>
-          <t>High-spin active center enables magnetic-field-enhanced photocatalytic overall water splitting</t>
+          <t>Electron delocalization in a fullerene-dumbbell triad: synergistically optimizing carrier dynamics for boosting photocatalytic hydrogen evolution</t>
         </is>
       </c>
       <c r="D90" s="55" t="inlineStr">
         <is>
-          <t>Jinlong Gong</t>
+          <t>Chunli Bai</t>
         </is>
       </c>
       <c r="E90" s="56" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="F90" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag495</t>
+          <t>https://doi.org/10.1093/nsr/nwag479</t>
         </is>
       </c>
       <c r="G90" s="24" t="n"/>
@@ -22521,12 +22621,12 @@
       <c r="B91" s="24" t="n"/>
       <c r="C91" s="55" t="inlineStr">
         <is>
-          <t>Revealing the kinetics characteristics of low-temperature electrocatalytic ammonia oxidation reaction</t>
+          <t>High-spin active center enables magnetic-field-enhanced photocatalytic overall water splitting</t>
         </is>
       </c>
       <c r="D91" s="55" t="inlineStr">
         <is>
-          <t>Kui Jiao</t>
+          <t>Jinlong Gong</t>
         </is>
       </c>
       <c r="E91" s="56" t="n">
@@ -22534,7 +22634,7 @@
       </c>
       <c r="F91" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag493</t>
+          <t>https://doi.org/10.1093/nsr/nwag495</t>
         </is>
       </c>
       <c r="G91" s="24" t="n"/>
@@ -22544,133 +22644,133 @@
       <c r="B92" s="24" t="n"/>
       <c r="C92" s="55" t="inlineStr">
         <is>
-          <t>Product ammonia accumulation limits electrocatalytic nitric oxide reduction</t>
+          <t>Revealing the kinetics characteristics of low-temperature electrocatalytic ammonia oxidation reaction</t>
         </is>
       </c>
       <c r="D92" s="55" t="inlineStr">
         <is>
-          <t>Jingshan Luo</t>
+          <t>Kui Jiao</t>
         </is>
       </c>
       <c r="E92" s="56" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="F92" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag507</t>
+          <t>https://doi.org/10.1093/nsr/nwag493</t>
         </is>
       </c>
       <c r="G92" s="24" t="n"/>
     </row>
     <row r="93" ht="32" customHeight="1">
       <c r="A93" s="24" t="n"/>
-      <c r="B93" s="25" t="n"/>
+      <c r="B93" s="24" t="n"/>
       <c r="C93" s="55" t="inlineStr">
         <is>
-          <t>Weak interfacial energy for magnesium salt-resistant ampere-level hydrogen production from natural seawater</t>
+          <t>Product ammonia accumulation limits electrocatalytic nitric oxide reduction</t>
         </is>
       </c>
       <c r="D93" s="55" t="inlineStr">
         <is>
-          <t>Lin Jiang</t>
+          <t>Jingshan Luo</t>
         </is>
       </c>
       <c r="E93" s="56" t="n">
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="F93" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag535</t>
-        </is>
-      </c>
-      <c r="G93" s="25" t="n"/>
+          <t>https://doi.org/10.1093/nsr/nwag507</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="n"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="24" t="n"/>
-      <c r="B94" s="52" t="inlineStr">
-        <is>
-          <t>Advanced Energy Materials</t>
-        </is>
-      </c>
-      <c r="C94" s="52" t="inlineStr">
-        <is>
-          <t>Mechanism‐Driven Atomic‐Level Engineering Over RuO2‐Based Catalysts for Proton Exchange Membrane Water Electrolysis</t>
-        </is>
-      </c>
-      <c r="D94" s="52" t="inlineStr">
-        <is>
-          <t>Zongping Shao</t>
-        </is>
-      </c>
-      <c r="E94" s="53" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F94" s="54" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71381</t>
-        </is>
-      </c>
-      <c r="G94" s="52" t="n">
-        <v>20</v>
-      </c>
+      <c r="B94" s="25" t="n"/>
+      <c r="C94" s="55" t="inlineStr">
+        <is>
+          <t>Weak interfacial energy for magnesium salt-resistant ampere-level hydrogen production from natural seawater</t>
+        </is>
+      </c>
+      <c r="D94" s="55" t="inlineStr">
+        <is>
+          <t>Lin Jiang</t>
+        </is>
+      </c>
+      <c r="E94" s="56" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F94" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/nsr/nwag535</t>
+        </is>
+      </c>
+      <c r="G94" s="25" t="n"/>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="24" t="n"/>
-      <c r="B95" s="24" t="n"/>
-      <c r="C95" s="55" t="inlineStr">
-        <is>
-          <t>MXene‐Derived Highly Oriented TiN Enables Ta3N5 Photoanodes for Transmission‐Mode Bias‐Free Solar Water Splitting</t>
-        </is>
-      </c>
-      <c r="D95" s="55" t="inlineStr">
-        <is>
-          <t>Ho Won Jang</t>
-        </is>
-      </c>
-      <c r="E95" s="56" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F95" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71412</t>
-        </is>
-      </c>
-      <c r="G95" s="24" t="n"/>
+      <c r="B95" s="52" t="inlineStr">
+        <is>
+          <t>Advanced Energy Materials</t>
+        </is>
+      </c>
+      <c r="C95" s="52" t="inlineStr">
+        <is>
+          <t>Mechanism‐Driven Atomic‐Level Engineering Over RuO2‐Based Catalysts for Proton Exchange Membrane Water Electrolysis</t>
+        </is>
+      </c>
+      <c r="D95" s="52" t="inlineStr">
+        <is>
+          <t>Zongping Shao</t>
+        </is>
+      </c>
+      <c r="E95" s="53" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F95" s="54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71381</t>
+        </is>
+      </c>
+      <c r="G95" s="52" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="96" ht="32" customHeight="1">
       <c r="A96" s="24" t="n"/>
       <c r="B96" s="24" t="n"/>
       <c r="C96" s="55" t="inlineStr">
         <is>
-          <t>Charge‐Redistribution‐Driven Dual‐Single‐Atom Catalysts on MXene for Hydrogen Evolution</t>
+          <t>MXene‐Derived Highly Oriented TiN Enables Ta3N5 Photoanodes for Transmission‐Mode Bias‐Free Solar Water Splitting</t>
         </is>
       </c>
       <c r="D96" s="55" t="inlineStr">
         <is>
-          <t>Qinfen Gu</t>
+          <t>Ho Won Jang</t>
         </is>
       </c>
       <c r="E96" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F96" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71403</t>
+          <t>https://doi.org/10.1002/aenm.71412</t>
         </is>
       </c>
       <c r="G96" s="24" t="n"/>
     </row>
-    <row r="97" ht="48" customHeight="1">
+    <row r="97" ht="32" customHeight="1">
       <c r="A97" s="24" t="n"/>
       <c r="B97" s="24" t="n"/>
       <c r="C97" s="55" t="inlineStr">
         <is>
-          <t>Electrocatalytic Urea Waste Valorization via Water Electrolysis: Transition‐Metal Phosphides for Sustainable Hydrogen Production</t>
+          <t>Charge‐Redistribution‐Driven Dual‐Single‐Atom Catalysts on MXene for Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D97" s="55" t="inlineStr">
         <is>
-          <t>Yogendra Kumar Mishra</t>
+          <t>Qinfen Gu</t>
         </is>
       </c>
       <c r="E97" s="56" t="n">
@@ -22678,45 +22778,45 @@
       </c>
       <c r="F97" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71260</t>
+          <t>https://doi.org/10.1002/aenm.71403</t>
         </is>
       </c>
       <c r="G97" s="24" t="n"/>
     </row>
-    <row r="98" ht="32" customHeight="1">
+    <row r="98" ht="48" customHeight="1">
       <c r="A98" s="24" t="n"/>
       <c r="B98" s="24" t="n"/>
       <c r="C98" s="55" t="inlineStr">
         <is>
-          <t>Design Principles of Electrocatalysts for Industrial‐Scale Water Electrolysis</t>
+          <t>Electrocatalytic Urea Waste Valorization via Water Electrolysis: Transition‐Metal Phosphides for Sustainable Hydrogen Production</t>
         </is>
       </c>
       <c r="D98" s="55" t="inlineStr">
         <is>
-          <t>John Wang</t>
+          <t>Yogendra Kumar Mishra</t>
         </is>
       </c>
       <c r="E98" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F98" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71379</t>
+          <t>https://doi.org/10.1002/aenm.71260</t>
         </is>
       </c>
       <c r="G98" s="24" t="n"/>
     </row>
-    <row r="99" ht="48" customHeight="1">
+    <row r="99" ht="32" customHeight="1">
       <c r="A99" s="24" t="n"/>
       <c r="B99" s="24" t="n"/>
       <c r="C99" s="55" t="inlineStr">
         <is>
-          <t>Directional Hydroxyl Spillover Enhances the Electrocatalytic Performance of Nickel Tungsten Zinc Heterostructure Toward Overall Water Splitting</t>
+          <t>Design Principles of Electrocatalysts for Industrial‐Scale Water Electrolysis</t>
         </is>
       </c>
       <c r="D99" s="55" t="inlineStr">
         <is>
-          <t>Zhongqing Liu</t>
+          <t>John Wang</t>
         </is>
       </c>
       <c r="E99" s="56" t="n">
@@ -22724,7 +22824,7 @@
       </c>
       <c r="F99" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71444</t>
+          <t>https://doi.org/10.1002/aenm.71379</t>
         </is>
       </c>
       <c r="G99" s="24" t="n"/>
@@ -22734,12 +22834,12 @@
       <c r="B100" s="24" t="n"/>
       <c r="C100" s="55" t="inlineStr">
         <is>
-          <t>Interpretable Machine Learning Framework Deciphers the Role of Local Environment of High‐Entropy Intermetallic Compounds for Alkaline Hydrogen Evolution Reaction</t>
+          <t>Directional Hydroxyl Spillover Enhances the Electrocatalytic Performance of Nickel Tungsten Zinc Heterostructure Toward Overall Water Splitting</t>
         </is>
       </c>
       <c r="D100" s="55" t="inlineStr">
         <is>
-          <t>Li‐Ming Yang</t>
+          <t>Zhongqing Liu</t>
         </is>
       </c>
       <c r="E100" s="56" t="n">
@@ -22747,22 +22847,22 @@
       </c>
       <c r="F100" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71361</t>
+          <t>https://doi.org/10.1002/aenm.71444</t>
         </is>
       </c>
       <c r="G100" s="24" t="n"/>
     </row>
-    <row r="101" ht="32" customHeight="1">
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="24" t="n"/>
       <c r="B101" s="24" t="n"/>
       <c r="C101" s="55" t="inlineStr">
         <is>
-          <t>Seawater Electrolysis for Sustainable Hydrogen Production: From Material Design to System Engineering</t>
+          <t>Interpretable Machine Learning Framework Deciphers the Role of Local Environment of High‐Entropy Intermetallic Compounds for Alkaline Hydrogen Evolution Reaction</t>
         </is>
       </c>
       <c r="D101" s="55" t="inlineStr">
         <is>
-          <t>Jingshan Luo</t>
+          <t>Li‐Ming Yang</t>
         </is>
       </c>
       <c r="E101" s="56" t="n">
@@ -22770,7 +22870,7 @@
       </c>
       <c r="F101" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71426</t>
+          <t>https://doi.org/10.1002/aenm.71361</t>
         </is>
       </c>
       <c r="G101" s="24" t="n"/>
@@ -22780,81 +22880,81 @@
       <c r="B102" s="24" t="n"/>
       <c r="C102" s="55" t="inlineStr">
         <is>
-          <t>Fluorine‐Induced d‐p‐d Orbital Hybridization Promotes Hydrogen Spillover for Efficient Hydrogen Evolution</t>
+          <t>Seawater Electrolysis for Sustainable Hydrogen Production: From Material Design to System Engineering</t>
         </is>
       </c>
       <c r="D102" s="55" t="inlineStr">
         <is>
-          <t>Shichun Mu</t>
+          <t>Jingshan Luo</t>
         </is>
       </c>
       <c r="E102" s="56" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="F102" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71437</t>
+          <t>https://doi.org/10.1002/aenm.71426</t>
         </is>
       </c>
       <c r="G102" s="24" t="n"/>
     </row>
-    <row r="103" ht="48" customHeight="1">
+    <row r="103" ht="32" customHeight="1">
       <c r="A103" s="24" t="n"/>
       <c r="B103" s="24" t="n"/>
       <c r="C103" s="55" t="inlineStr">
         <is>
-          <t>Manipulating Valence‐Heterogeneous Pt Dual Sites via Metal‐Support Interactions for Highly Efficient Alkaline Hydrogen Evolution</t>
+          <t>Fluorine‐Induced d‐p‐d Orbital Hybridization Promotes Hydrogen Spillover for Efficient Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D103" s="55" t="inlineStr">
         <is>
-          <t>Hao Jiang</t>
+          <t>Shichun Mu</t>
         </is>
       </c>
       <c r="E103" s="56" t="n">
-        <v>46249</v>
+        <v>46247</v>
       </c>
       <c r="F103" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71456</t>
+          <t>https://doi.org/10.1002/aenm.71437</t>
         </is>
       </c>
       <c r="G103" s="24" t="n"/>
     </row>
-    <row r="104" ht="32" customHeight="1">
+    <row r="104" ht="48" customHeight="1">
       <c r="A104" s="24" t="n"/>
       <c r="B104" s="24" t="n"/>
       <c r="C104" s="55" t="inlineStr">
         <is>
-          <t>Cu@Cr2O3 Noble‐Metal‐Free Hydrogen‐Evolving Cocatalyst on Al‐Doped SrTiO3 for Photocatalytic Overall Water Splitting</t>
+          <t>Manipulating Valence‐Heterogeneous Pt Dual Sites via Metal‐Support Interactions for Highly Efficient Alkaline Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D104" s="55" t="inlineStr">
         <is>
-          <t>Huagui Yang</t>
+          <t>Hao Jiang</t>
         </is>
       </c>
       <c r="E104" s="56" t="n">
-        <v>46253</v>
+        <v>46249</v>
       </c>
       <c r="F104" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71440</t>
+          <t>https://doi.org/10.1002/aenm.71456</t>
         </is>
       </c>
       <c r="G104" s="24" t="n"/>
     </row>
-    <row r="105" ht="48" customHeight="1">
+    <row r="105" ht="32" customHeight="1">
       <c r="A105" s="24" t="n"/>
       <c r="B105" s="24" t="n"/>
       <c r="C105" s="55" t="inlineStr">
         <is>
-          <t>Electric Double Layer Engineering Induces O‐Down Interfacial Water Reorientation for Efficient and Long‐Term Seawater Electrolysis</t>
+          <t>Cu@Cr2O3 Noble‐Metal‐Free Hydrogen‐Evolving Cocatalyst on Al‐Doped SrTiO3 for Photocatalytic Overall Water Splitting</t>
         </is>
       </c>
       <c r="D105" s="55" t="inlineStr">
         <is>
-          <t>Zhigang Shao</t>
+          <t>Huagui Yang</t>
         </is>
       </c>
       <c r="E105" s="56" t="n">
@@ -22862,68 +22962,68 @@
       </c>
       <c r="F105" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71429</t>
+          <t>https://doi.org/10.1002/aenm.71440</t>
         </is>
       </c>
       <c r="G105" s="24" t="n"/>
     </row>
-    <row r="106" ht="32" customHeight="1">
+    <row r="106" ht="48" customHeight="1">
       <c r="A106" s="24" t="n"/>
       <c r="B106" s="24" t="n"/>
       <c r="C106" s="55" t="inlineStr">
         <is>
-          <t>Indoor NFA‐Organic Photovoltaic for Grid‐Free Water Electrolysis</t>
+          <t>Electric Double Layer Engineering Induces O‐Down Interfacial Water Reorientation for Efficient and Long‐Term Seawater Electrolysis</t>
         </is>
       </c>
       <c r="D106" s="55" t="inlineStr">
         <is>
-          <t>Hyeok Kim</t>
+          <t>Zhigang Shao</t>
         </is>
       </c>
       <c r="E106" s="56" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F106" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71363</t>
+          <t>https://doi.org/10.1002/aenm.71429</t>
         </is>
       </c>
       <c r="G106" s="24" t="n"/>
     </row>
-    <row r="107" ht="48" customHeight="1">
+    <row r="107" ht="32" customHeight="1">
       <c r="A107" s="24" t="n"/>
       <c r="B107" s="24" t="n"/>
       <c r="C107" s="55" t="inlineStr">
         <is>
-          <t>From Top to Bottom: Manufacturing Process‐Context Aware Resolution of Energy Device Electrodes Through a 3D Diffusion Generative Model</t>
+          <t>Indoor NFA‐Organic Photovoltaic for Grid‐Free Water Electrolysis</t>
         </is>
       </c>
       <c r="D107" s="55" t="inlineStr">
         <is>
-          <t>Alejandro A. Franco</t>
+          <t>Hyeok Kim</t>
         </is>
       </c>
       <c r="E107" s="56" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="F107" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71418</t>
+          <t>https://doi.org/10.1002/aenm.71363</t>
         </is>
       </c>
       <c r="G107" s="24" t="n"/>
     </row>
-    <row r="108" ht="32" customHeight="1">
+    <row r="108" ht="48" customHeight="1">
       <c r="A108" s="24" t="n"/>
       <c r="B108" s="24" t="n"/>
       <c r="C108" s="55" t="inlineStr">
         <is>
-          <t>Hybrid Ionomer‐Free Porous Transport Electrodes With Catalyst Coated Membranes for Enhanced Water Electrolysis</t>
+          <t>From Top to Bottom: Manufacturing Process‐Context Aware Resolution of Energy Device Electrodes Through a 3D Diffusion Generative Model</t>
         </is>
       </c>
       <c r="D108" s="55" t="inlineStr">
         <is>
-          <t>Aimy Bazylak</t>
+          <t>Alejandro A. Franco</t>
         </is>
       </c>
       <c r="E108" s="56" t="n">
@@ -22931,7 +23031,7 @@
       </c>
       <c r="F108" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71479</t>
+          <t>https://doi.org/10.1002/aenm.71418</t>
         </is>
       </c>
       <c r="G108" s="24" t="n"/>
@@ -22941,20 +23041,20 @@
       <c r="B109" s="24" t="n"/>
       <c r="C109" s="55" t="inlineStr">
         <is>
-          <t>Pt Single‐Atom Catalysts on FTO for Optically Invisible pH‐Universal Hydrogen Evolution Electrodes</t>
+          <t>Hybrid Ionomer‐Free Porous Transport Electrodes With Catalyst Coated Membranes for Enhanced Water Electrolysis</t>
         </is>
       </c>
       <c r="D109" s="55" t="inlineStr">
         <is>
-          <t>Patrik Schmuki</t>
+          <t>Aimy Bazylak</t>
         </is>
       </c>
       <c r="E109" s="56" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="F109" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71493</t>
+          <t>https://doi.org/10.1002/aenm.71479</t>
         </is>
       </c>
       <c r="G109" s="24" t="n"/>
@@ -22964,20 +23064,20 @@
       <c r="B110" s="24" t="n"/>
       <c r="C110" s="55" t="inlineStr">
         <is>
-          <t>Open AgRh Hollow Nanocubes With Interfacial Step Matching for Selective Nitrate‐to‐Ammonia Electrosynthesis</t>
+          <t>Pt Single‐Atom Catalysts on FTO for Optically Invisible pH‐Universal Hydrogen Evolution Electrodes</t>
         </is>
       </c>
       <c r="D110" s="55" t="inlineStr">
         <is>
-          <t>Xuan Ai</t>
+          <t>Patrik Schmuki</t>
         </is>
       </c>
       <c r="E110" s="56" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="F110" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71507</t>
+          <t>https://doi.org/10.1002/aenm.71493</t>
         </is>
       </c>
       <c r="G110" s="24" t="n"/>
@@ -22987,12 +23087,12 @@
       <c r="B111" s="24" t="n"/>
       <c r="C111" s="55" t="inlineStr">
         <is>
-          <t>Toward Scalable Water Electrolysis Catalysts: Mechanistic Insights, Structure‐Activity Relationships and Multiscale Design</t>
+          <t>Open AgRh Hollow Nanocubes With Interfacial Step Matching for Selective Nitrate‐to‐Ammonia Electrosynthesis</t>
         </is>
       </c>
       <c r="D111" s="55" t="inlineStr">
         <is>
-          <t>Hongwen Huang</t>
+          <t>Xuan Ai</t>
         </is>
       </c>
       <c r="E111" s="56" t="n">
@@ -23000,45 +23100,45 @@
       </c>
       <c r="F111" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71510</t>
+          <t>https://doi.org/10.1002/aenm.71507</t>
         </is>
       </c>
       <c r="G111" s="24" t="n"/>
     </row>
-    <row r="112" ht="48" customHeight="1">
+    <row r="112" ht="32" customHeight="1">
       <c r="A112" s="24" t="n"/>
       <c r="B112" s="24" t="n"/>
       <c r="C112" s="55" t="inlineStr">
         <is>
+          <t>Toward Scalable Water Electrolysis Catalysts: Mechanistic Insights, Structure‐Activity Relationships and Multiscale Design</t>
+        </is>
+      </c>
+      <c r="D112" s="55" t="inlineStr">
+        <is>
+          <t>Hongwen Huang</t>
+        </is>
+      </c>
+      <c r="E112" s="56" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F112" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71510</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="n"/>
+    </row>
+    <row r="113" ht="48" customHeight="1">
+      <c r="A113" s="24" t="n"/>
+      <c r="B113" s="24" t="n"/>
+      <c r="C113" s="55" t="inlineStr">
+        <is>
           <t>Coupled Atmospheric Water Harvesting and Protonic Ceramic Electrolysis Enabling Self‐Sustained Green Hydrogen Production in Arid Regions (Adv. Energy Mater. 32/2026)</t>
         </is>
       </c>
-      <c r="D112" s="55" t="inlineStr">
+      <c r="D113" s="55" t="inlineStr">
         <is>
           <t>Wei Zhou</t>
-        </is>
-      </c>
-      <c r="E112" s="56" t="n">
-        <v>46260</v>
-      </c>
-      <c r="F112" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71346</t>
-        </is>
-      </c>
-      <c r="G112" s="24" t="n"/>
-    </row>
-    <row r="113" ht="48" customHeight="1">
-      <c r="A113" s="25" t="n"/>
-      <c r="B113" s="25" t="n"/>
-      <c r="C113" s="55" t="inlineStr">
-        <is>
-          <t>Functional Motif Directed Decoupling‐Recoupling Strategy for Constructing Multi‐Site Pt‐Based Catalyst Toward Efficient Hydrogen Oxidation in Fuel Cells</t>
-        </is>
-      </c>
-      <c r="D113" s="55" t="inlineStr">
-        <is>
-          <t>Xiaopeng Han</t>
         </is>
       </c>
       <c r="E113" s="56" t="n">
@@ -23046,190 +23146,213 @@
       </c>
       <c r="F113" s="57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1002/aenm.71346</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="48" customHeight="1">
+      <c r="A114" s="25" t="n"/>
+      <c r="B114" s="25" t="n"/>
+      <c r="C114" s="55" t="inlineStr">
+        <is>
+          <t>Functional Motif Directed Decoupling‐Recoupling Strategy for Constructing Multi‐Site Pt‐Based Catalyst Toward Efficient Hydrogen Oxidation in Fuel Cells</t>
+        </is>
+      </c>
+      <c r="D114" s="55" t="inlineStr">
+        <is>
+          <t>Xiaopeng Han</t>
+        </is>
+      </c>
+      <c r="E114" s="56" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F114" s="57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1002/aenm.71431</t>
         </is>
       </c>
-      <c r="G113" s="25" t="n"/>
-    </row>
-    <row r="114" ht="48" customHeight="1">
-      <c r="A114" s="58" t="inlineStr">
+      <c r="G114" s="25" t="n"/>
+    </row>
+    <row r="115" ht="48" customHeight="1">
+      <c r="A115" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B114" s="59" t="inlineStr">
+      <c r="B115" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
         </is>
       </c>
-      <c r="C114" s="59" t="inlineStr">
+      <c r="C115" s="59" t="inlineStr">
         <is>
           <t>Sequentially adaptive electron transfer in heteroatom-modulated NiFe-MOFs for efficient anion exchange membrane water/seawater electrolysis</t>
         </is>
       </c>
-      <c r="D114" s="59" t="inlineStr">
+      <c r="D115" s="59" t="inlineStr">
         <is>
           <t>Liejin Guo</t>
         </is>
       </c>
-      <c r="E114" s="60" t="n">
+      <c r="E115" s="60" t="n">
         <v>46253</v>
       </c>
-      <c r="F114" s="61" t="inlineStr">
+      <c r="F115" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.joule.2026.102630</t>
         </is>
       </c>
-      <c r="G114" s="59" t="n">
+      <c r="G115" s="59" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" ht="32" customHeight="1">
-      <c r="A115" s="24" t="n"/>
-      <c r="B115" s="25" t="n"/>
-      <c r="C115" s="59" t="inlineStr">
-        <is>
-          <t>The dual role of iron in alkaline water electrolysis: A friend or a foe?</t>
-        </is>
-      </c>
-      <c r="D115" s="59" t="inlineStr">
-        <is>
-          <t>Meital Shviro</t>
-        </is>
-      </c>
-      <c r="E115" s="60" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F115" s="61" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.joule.2026.102639</t>
-        </is>
-      </c>
-      <c r="G115" s="25" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="24" t="n"/>
-      <c r="B116" s="59" t="inlineStr">
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="59" t="inlineStr">
+        <is>
+          <t>The dual role of iron in alkaline water electrolysis: A friend or a foe?</t>
+        </is>
+      </c>
+      <c r="D116" s="59" t="inlineStr">
+        <is>
+          <t>Meital Shviro</t>
+        </is>
+      </c>
+      <c r="E116" s="60" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F116" s="61" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.joule.2026.102639</t>
+        </is>
+      </c>
+      <c r="G116" s="25" t="n"/>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="24" t="n"/>
+      <c r="B117" s="59" t="inlineStr">
         <is>
           <t>Chem</t>
         </is>
       </c>
-      <c r="C116" s="59" t="inlineStr">
+      <c r="C117" s="59" t="inlineStr">
         <is>
           <t>Regulating transport processes in oxygen evolution catalyst layers for proton exchange membrane water electrolysis</t>
         </is>
       </c>
-      <c r="D116" s="59" t="inlineStr">
+      <c r="D117" s="59" t="inlineStr">
         <is>
           <t>Huabin Zhang</t>
         </is>
       </c>
-      <c r="E116" s="60" t="n">
+      <c r="E117" s="60" t="n">
         <v>46251</v>
       </c>
-      <c r="F116" s="61" t="inlineStr">
+      <c r="F117" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.chempr.2026.103198</t>
         </is>
       </c>
-      <c r="G116" s="59" t="n">
+      <c r="G117" s="59" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="25" t="n"/>
-      <c r="B117" s="59" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="25" t="n"/>
+      <c r="B118" s="59" t="inlineStr">
         <is>
           <t>Materials Today</t>
         </is>
       </c>
-      <c r="C117" s="59" t="n"/>
-      <c r="D117" s="59" t="n"/>
-      <c r="E117" s="59" t="n"/>
-      <c r="F117" s="59" t="n"/>
-      <c r="G117" s="59" t="n">
+      <c r="C118" s="59" t="n"/>
+      <c r="D118" s="59" t="n"/>
+      <c r="E118" s="59" t="n"/>
+      <c r="F118" s="59" t="n"/>
+      <c r="G118" s="59" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="62" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="62" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B118" s="63" t="inlineStr">
+      <c r="B119" s="63" t="inlineStr">
         <is>
           <t>PNAS</t>
         </is>
       </c>
-      <c r="C118" s="63" t="inlineStr">
+      <c r="C119" s="63" t="inlineStr">
         <is>
           <t>Hydrogen-ready infrastructure risks new carbon lock-in</t>
         </is>
       </c>
-      <c r="D118" s="63" t="inlineStr">
+      <c r="D119" s="63" t="inlineStr">
         <is>
           <t>Y. Frank Cheng</t>
         </is>
       </c>
-      <c r="E118" s="64" t="n">
+      <c r="E119" s="64" t="n">
         <v>46253</v>
       </c>
-      <c r="F118" s="65" t="inlineStr">
+      <c r="F119" s="65" t="inlineStr">
         <is>
           <t>https://doi.org/10.1073/pnas.2601685123</t>
         </is>
       </c>
-      <c r="G118" s="63" t="n">
+      <c r="G119" s="63" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="25" t="n"/>
-      <c r="B119" s="63" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="25" t="n"/>
+      <c r="B120" s="63" t="inlineStr">
         <is>
           <t>National Science Review</t>
         </is>
       </c>
-      <c r="C119" s="63" t="n"/>
-      <c r="D119" s="63" t="n"/>
-      <c r="E119" s="63" t="n"/>
-      <c r="F119" s="63" t="n"/>
-      <c r="G119" s="63" t="n">
+      <c r="C120" s="63" t="n"/>
+      <c r="D120" s="63" t="n"/>
+      <c r="E120" s="63" t="n"/>
+      <c r="F120" s="63" t="n"/>
+      <c r="G120" s="63" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="G114:G115"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="G34:G52"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B94:B113"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="B35:B53"/>
+    <mergeCell ref="A57:A114"/>
     <mergeCell ref="G16:G29"/>
-    <mergeCell ref="G94:G113"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="G56:G87"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A34:A55"/>
-    <mergeCell ref="A56:A113"/>
-    <mergeCell ref="G88:G93"/>
-    <mergeCell ref="B34:B52"/>
-    <mergeCell ref="B56:B87"/>
-    <mergeCell ref="A6:A30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="G31:G33"/>
     <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G95:G114"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="G55:G56"/>
     <mergeCell ref="B16:B29"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="G57:G88"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="A35:A56"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="B95:B114"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="G89:G94"/>
+    <mergeCell ref="B57:B88"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="B89:B94"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A6:A30"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="G35:G53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
@@ -23258,7 +23381,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId30"/>
@@ -23341,7 +23464,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/monthly/2026-08 文献统计表.xlsx
+++ b/output/monthly/2026-08 文献统计表.xlsx
@@ -5590,7 +5590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6719,12 +6719,12 @@
         </is>
       </c>
       <c r="G48" s="38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="24" t="n"/>
-      <c r="B49" s="25" t="n"/>
+      <c r="B49" s="24" t="n"/>
       <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Unlocking the energy-saving potential of electrochromic windows</t>
@@ -6743,122 +6743,130 @@
           <t>https://doi.org/10.1039/d6ee04338k</t>
         </is>
       </c>
-      <c r="G49" s="25" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="25" t="n"/>
-      <c r="B50" s="38" t="inlineStr">
+      <c r="G49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="25" t="n"/>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Sustainable integrated drop-in fuel production – a holistic optimization-based approach</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>Alexander Mitsos</t>
+        </is>
+      </c>
+      <c r="E50" s="42" t="n">
+        <v>46264</v>
+      </c>
+      <c r="F50" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee02816k</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="38" t="n"/>
-      <c r="E50" s="38" t="n"/>
-      <c r="F50" s="38" t="n"/>
-      <c r="G50" s="38" t="n">
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="38" t="n"/>
+      <c r="E51" s="38" t="n"/>
+      <c r="F51" s="38" t="n"/>
+      <c r="G51" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="44" t="inlineStr">
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B51" s="45" t="inlineStr">
+      <c r="B52" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C51" s="45" t="inlineStr">
+      <c r="C52" s="45" t="inlineStr">
         <is>
           <t>One-Pot Sequential Alkaline-Acid Route to ZSM-5 Nanosheets with Low Framework Defects and Suppressed Aluminum Zoning</t>
         </is>
       </c>
-      <c r="D51" s="45" t="inlineStr">
+      <c r="D52" s="45" t="inlineStr">
         <is>
           <t>Yahong Zhang</t>
         </is>
       </c>
-      <c r="E51" s="46" t="n">
+      <c r="E52" s="46" t="n">
         <v>46244</v>
       </c>
-      <c r="F51" s="47" t="inlineStr">
+      <c r="F52" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c12379</t>
         </is>
       </c>
-      <c r="G51" s="45" t="n">
+      <c r="G52" s="45" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="24" t="n"/>
-      <c r="B52" s="24" t="n"/>
-      <c r="C52" s="48" t="inlineStr">
-        <is>
-          <t>Metallic Ag-BiAg Heterostructured Dendrites Accelerate Carbon–Nitrogen Coupling for Air Plasma-Derived Amino Acid Electrosynthesis</t>
-        </is>
-      </c>
-      <c r="D52" s="48" t="inlineStr">
-        <is>
-          <t>Changzheng Wu</t>
-        </is>
-      </c>
-      <c r="E52" s="49" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F52" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c11127</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="n"/>
     </row>
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="24" t="n"/>
-      <c r="B53" s="25" t="n"/>
+      <c r="B53" s="24" t="n"/>
       <c r="C53" s="48" t="inlineStr">
         <is>
+          <t>Metallic Ag-BiAg Heterostructured Dendrites Accelerate Carbon–Nitrogen Coupling for Air Plasma-Derived Amino Acid Electrosynthesis</t>
+        </is>
+      </c>
+      <c r="D53" s="48" t="inlineStr">
+        <is>
+          <t>Changzheng Wu</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F53" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c11127</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="n"/>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="24" t="n"/>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="48" t="inlineStr">
+        <is>
           <t>Catalytic Combustion of Extremely Low Concentrations of Methane by Pt/CeO2 {111} Nanocrystals Driven by the Synergy of Photons and Phonons</t>
         </is>
       </c>
-      <c r="D53" s="48" t="inlineStr">
+      <c r="D54" s="48" t="inlineStr">
         <is>
           <t>Junwang Tang</t>
         </is>
       </c>
-      <c r="E53" s="49" t="n">
+      <c r="E54" s="49" t="n">
         <v>46253</v>
       </c>
-      <c r="F53" s="50" t="inlineStr">
+      <c r="F54" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c05483</t>
         </is>
       </c>
-      <c r="G53" s="25" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="24" t="n"/>
-      <c r="B54" s="45" t="inlineStr">
+      <c r="G54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="45" t="inlineStr">
         <is>
           <t>ACS Energy Letters</t>
-        </is>
-      </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
-      <c r="G54" s="45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="25" t="n"/>
-      <c r="B55" s="45" t="inlineStr">
-        <is>
-          <t>Chemical Reviews</t>
         </is>
       </c>
       <c r="C55" s="45" t="n"/>
@@ -6869,73 +6877,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="51" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="25" t="n"/>
+      <c r="B56" s="45" t="inlineStr">
+        <is>
+          <t>Chemical Reviews</t>
+        </is>
+      </c>
+      <c r="C56" s="45" t="n"/>
+      <c r="D56" s="45" t="n"/>
+      <c r="E56" s="45" t="n"/>
+      <c r="F56" s="45" t="n"/>
+      <c r="G56" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B56" s="52" t="inlineStr">
+      <c r="B57" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C56" s="52" t="inlineStr">
+      <c r="C57" s="52" t="inlineStr">
         <is>
           <t>Induced‐Fit for Oxygen Adsorption: Flexible Conjugated Microporous Polymers With Self‐Adaptive Active Sites for H2O2 Photosynthesis</t>
         </is>
       </c>
-      <c r="D56" s="52" t="inlineStr">
+      <c r="D57" s="52" t="inlineStr">
         <is>
           <t>Hanjun Sun</t>
         </is>
       </c>
-      <c r="E56" s="53" t="n">
+      <c r="E57" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F56" s="54" t="inlineStr">
+      <c r="F57" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.5802081</t>
         </is>
       </c>
-      <c r="G56" s="52" t="n">
+      <c r="G57" s="52" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="24" t="n"/>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="55" t="inlineStr">
-        <is>
-          <t>Molecular Segments Reorganization Strategy Coupled With Retrosynthetic Analysis for Designing Sustainable Alternatives to Alkylphenol Ethoxylates</t>
-        </is>
-      </c>
-      <c r="D57" s="55" t="inlineStr">
-        <is>
-          <t>Jinxiang Dong</t>
-        </is>
-      </c>
-      <c r="E57" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F57" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.2280699</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
+    <row r="58" ht="48" customHeight="1">
       <c r="A58" s="24" t="n"/>
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>Natural Sunlight IR‐Driven Highly Efficient Synthesis of Acetaldehyde From Bioethanol Over Cu/Fe2O3</t>
+          <t>Molecular Segments Reorganization Strategy Coupled With Retrosynthetic Analysis for Designing Sustainable Alternatives to Alkylphenol Ethoxylates</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
         <is>
-          <t>Junwang Tang</t>
+          <t>Jinxiang Dong</t>
         </is>
       </c>
       <c r="E58" s="56" t="n">
@@ -6943,114 +6943,114 @@
       </c>
       <c r="F58" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9513626</t>
+          <t>https://doi.org/10.1002/anie.2280699</t>
         </is>
       </c>
       <c r="G58" s="24" t="n"/>
     </row>
-    <row r="59" ht="64" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="24" t="n"/>
       <c r="B59" s="24" t="n"/>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Surface Hydroxyl Steered Adsorption Configuration for Efficient Photocatalysis Coupling Hydrogen Evolution and 5‐Hydroxymethylfurfural Selective Oxidation Toward 2,5‐Furandicarboxylic Acid Production</t>
+          <t>Natural Sunlight IR‐Driven Highly Efficient Synthesis of Acetaldehyde From Bioethanol Over Cu/Fe2O3</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
         <is>
-          <t>Shaohua Shen</t>
+          <t>Junwang Tang</t>
         </is>
       </c>
       <c r="E59" s="56" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F59" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3914874</t>
+          <t>https://doi.org/10.1002/anie.9513626</t>
         </is>
       </c>
       <c r="G59" s="24" t="n"/>
     </row>
-    <row r="60" ht="48" customHeight="1">
+    <row r="60" ht="64" customHeight="1">
       <c r="A60" s="24" t="n"/>
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
-          <t>A Universal Fenton‐Like Strategy for Selective Generation of 1O2 in Mixed Industrial Wastewater Treatment and Green Chemical Synthesis</t>
+          <t>Surface Hydroxyl Steered Adsorption Configuration for Efficient Photocatalysis Coupling Hydrogen Evolution and 5‐Hydroxymethylfurfural Selective Oxidation Toward 2,5‐Furandicarboxylic Acid Production</t>
         </is>
       </c>
       <c r="D60" s="55" t="inlineStr">
         <is>
-          <t>Sihui Zhan</t>
+          <t>Shaohua Shen</t>
         </is>
       </c>
       <c r="E60" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F60" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4329489</t>
+          <t>https://doi.org/10.1002/anie.3914874</t>
         </is>
       </c>
       <c r="G60" s="24" t="n"/>
     </row>
-    <row r="61" ht="32" customHeight="1">
+    <row r="61" ht="48" customHeight="1">
       <c r="A61" s="24" t="n"/>
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Epitaxial Oxide Interfaces Create Poison‐Resistant CuO Sites for Environmental Catalysis</t>
+          <t>A Universal Fenton‐Like Strategy for Selective Generation of 1O2 in Mixed Industrial Wastewater Treatment and Green Chemical Synthesis</t>
         </is>
       </c>
       <c r="D61" s="55" t="inlineStr">
         <is>
-          <t>Dengsong Zhang</t>
+          <t>Sihui Zhan</t>
         </is>
       </c>
       <c r="E61" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F61" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7111765</t>
+          <t>https://doi.org/10.1002/anie.4329489</t>
         </is>
       </c>
       <c r="G61" s="24" t="n"/>
     </row>
-    <row r="62" ht="48" customHeight="1">
+    <row r="62" ht="32" customHeight="1">
       <c r="A62" s="24" t="n"/>
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
-          <t>Activating Triplet Excitons in COFs via Layer‐Bridging Co Single Atoms for Photocatalytic H2O2 Production and Tandem C─N Coupling</t>
+          <t>Epitaxial Oxide Interfaces Create Poison‐Resistant CuO Sites for Environmental Catalysis</t>
         </is>
       </c>
       <c r="D62" s="55" t="inlineStr">
         <is>
-          <t>Hermenegildo García</t>
+          <t>Dengsong Zhang</t>
         </is>
       </c>
       <c r="E62" s="56" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="F62" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1580812</t>
+          <t>https://doi.org/10.1002/anie.7111765</t>
         </is>
       </c>
       <c r="G62" s="24" t="n"/>
     </row>
-    <row r="63" ht="32" customHeight="1">
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="24" t="n"/>
       <c r="B63" s="24" t="n"/>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>Selective Adsorption of o‐Xylene From all C8 Aromatics via Secondary Connectivity Manipulation in B←N Frameworks</t>
+          <t>Activating Triplet Excitons in COFs via Layer‐Bridging Co Single Atoms for Photocatalytic H2O2 Production and Tandem C─N Coupling</t>
         </is>
       </c>
       <c r="D63" s="55" t="inlineStr">
         <is>
-          <t>Yangjian Quan</t>
+          <t>Hermenegildo García</t>
         </is>
       </c>
       <c r="E63" s="56" t="n">
@@ -7058,22 +7058,22 @@
       </c>
       <c r="F63" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1406923</t>
+          <t>https://doi.org/10.1002/anie.1580812</t>
         </is>
       </c>
       <c r="G63" s="24" t="n"/>
     </row>
-    <row r="64" ht="48" customHeight="1">
+    <row r="64" ht="32" customHeight="1">
       <c r="A64" s="24" t="n"/>
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="55" t="inlineStr">
         <is>
-          <t>Site‐Specific Molecular Spectroscopy Reveals Monomeric Cu Active Sites in SSZ‐13 Zeolite for Methane Oxidation and NOx Reduction</t>
+          <t>Selective Adsorption of o‐Xylene From all C8 Aromatics via Secondary Connectivity Manipulation in B←N Frameworks</t>
         </is>
       </c>
       <c r="D64" s="55" t="inlineStr">
         <is>
-          <t>Kunlun Ding</t>
+          <t>Yangjian Quan</t>
         </is>
       </c>
       <c r="E64" s="56" t="n">
@@ -7081,22 +7081,22 @@
       </c>
       <c r="F64" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.8285953</t>
+          <t>https://doi.org/10.1002/anie.1406923</t>
         </is>
       </c>
       <c r="G64" s="24" t="n"/>
     </row>
-    <row r="65" ht="32" customHeight="1">
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="24" t="n"/>
       <c r="B65" s="24" t="n"/>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>Zn─F Diatomic Sites Promote Electrochemical C─N Coupling for the Synthesis of Amino Acids</t>
+          <t>Site‐Specific Molecular Spectroscopy Reveals Monomeric Cu Active Sites in SSZ‐13 Zeolite for Methane Oxidation and NOx Reduction</t>
         </is>
       </c>
       <c r="D65" s="55" t="inlineStr">
         <is>
-          <t>Lei Wang</t>
+          <t>Kunlun Ding</t>
         </is>
       </c>
       <c r="E65" s="56" t="n">
@@ -7104,185 +7104,193 @@
       </c>
       <c r="F65" s="57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1002/anie.8285953</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="n"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="24" t="n"/>
+      <c r="B66" s="24" t="n"/>
+      <c r="C66" s="55" t="inlineStr">
+        <is>
+          <t>Zn─F Diatomic Sites Promote Electrochemical C─N Coupling for the Synthesis of Amino Acids</t>
+        </is>
+      </c>
+      <c r="D66" s="55" t="inlineStr">
+        <is>
+          <t>Lei Wang</t>
+        </is>
+      </c>
+      <c r="E66" s="56" t="n">
+        <v>46253</v>
+      </c>
+      <c r="F66" s="57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1002/anie.1293701</t>
         </is>
       </c>
-      <c r="G65" s="24" t="n"/>
-    </row>
-    <row r="66" ht="48" customHeight="1">
-      <c r="A66" s="24" t="n"/>
-      <c r="B66" s="25" t="n"/>
-      <c r="C66" s="55" t="inlineStr">
+      <c r="G66" s="24" t="n"/>
+    </row>
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="24" t="n"/>
+      <c r="B67" s="25" t="n"/>
+      <c r="C67" s="55" t="inlineStr">
         <is>
           <t>Asymmetric Dual Sites Enable Spatially Resolved Biradical‐Mediated C–N Coupling for N,N‐Dimethylformamide Photoelectrosynthesis</t>
         </is>
       </c>
-      <c r="D66" s="55" t="inlineStr">
+      <c r="D67" s="55" t="inlineStr">
         <is>
           <t>Jungang Hou</t>
         </is>
       </c>
-      <c r="E66" s="56" t="n">
+      <c r="E67" s="56" t="n">
         <v>46256</v>
       </c>
-      <c r="F66" s="57" t="inlineStr">
+      <c r="F67" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.9125401</t>
         </is>
       </c>
-      <c r="G66" s="25" t="n"/>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="24" t="n"/>
-      <c r="B67" s="52" t="inlineStr">
+      <c r="G67" s="25" t="n"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="24" t="n"/>
+      <c r="B68" s="52" t="inlineStr">
         <is>
           <t>Advanced Materials</t>
         </is>
       </c>
-      <c r="C67" s="52" t="inlineStr">
+      <c r="C68" s="52" t="inlineStr">
         <is>
           <t>Steering the reaction pathway of methane-to-oxygenates with zero CO2 production via photo–thermal catalysis</t>
         </is>
       </c>
-      <c r="D67" s="52" t="inlineStr">
+      <c r="D68" s="52" t="inlineStr">
         <is>
           <t>Li Tan</t>
         </is>
       </c>
-      <c r="E67" s="53" t="n">
+      <c r="E68" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F67" s="54" t="inlineStr">
+      <c r="F68" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/nsr/nwag472</t>
         </is>
       </c>
-      <c r="G67" s="52" t="n">
+      <c r="G68" s="52" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="24" t="n"/>
-      <c r="B68" s="24" t="n"/>
-      <c r="C68" s="55" t="inlineStr">
-        <is>
-          <t>Molecular-level petroleum refining by graded membranes</t>
-        </is>
-      </c>
-      <c r="D68" s="55" t="inlineStr">
-        <is>
-          <t>Weishen Yang</t>
-        </is>
-      </c>
-      <c r="E68" s="56" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F68" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/nsr/nwag488</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="n"/>
-    </row>
-    <row r="69" ht="32" customHeight="1">
+    <row r="69" ht="18" customHeight="1">
       <c r="A69" s="24" t="n"/>
       <c r="B69" s="24" t="n"/>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Unraveling the potential of urban greenery for extreme heat and ozone mitigation in Northern Hemisphere cities</t>
+          <t>Molecular-level petroleum refining by graded membranes</t>
         </is>
       </c>
       <c r="D69" s="55" t="inlineStr">
         <is>
-          <t>Aijun Ding</t>
+          <t>Weishen Yang</t>
         </is>
       </c>
       <c r="E69" s="56" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="F69" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag494</t>
+          <t>https://doi.org/10.1093/nsr/nwag488</t>
         </is>
       </c>
       <c r="G69" s="24" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="24" t="n"/>
-      <c r="B70" s="25" t="n"/>
+      <c r="B70" s="24" t="n"/>
       <c r="C70" s="55" t="inlineStr">
         <is>
+          <t>Unraveling the potential of urban greenery for extreme heat and ozone mitigation in Northern Hemisphere cities</t>
+        </is>
+      </c>
+      <c r="D70" s="55" t="inlineStr">
+        <is>
+          <t>Aijun Ding</t>
+        </is>
+      </c>
+      <c r="E70" s="56" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F70" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/nsr/nwag494</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="n"/>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="24" t="n"/>
+      <c r="B71" s="25" t="n"/>
+      <c r="C71" s="55" t="inlineStr">
+        <is>
           <t>Digging high-speed hierarchical pores within zeolite crystals for deep desulfurization</t>
         </is>
       </c>
-      <c r="D70" s="55" t="inlineStr">
+      <c r="D71" s="55" t="inlineStr">
         <is>
           <t>Bao-Lian Su</t>
         </is>
       </c>
-      <c r="E70" s="56" t="n">
+      <c r="E71" s="56" t="n">
         <v>46259</v>
       </c>
-      <c r="F70" s="57" t="inlineStr">
+      <c r="F71" s="57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/nsr/nwag536</t>
         </is>
       </c>
-      <c r="G70" s="25" t="n"/>
-    </row>
-    <row r="71" ht="48" customHeight="1">
-      <c r="A71" s="25" t="n"/>
-      <c r="B71" s="52" t="inlineStr">
+      <c r="G71" s="25" t="n"/>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="25" t="n"/>
+      <c r="B72" s="52" t="inlineStr">
         <is>
           <t>Advanced Energy Materials</t>
         </is>
       </c>
-      <c r="C71" s="52" t="inlineStr">
+      <c r="C72" s="52" t="inlineStr">
         <is>
           <t>The New Type All‐Thin‐Film Electrochromic Devices: Separated‐Function Design for High‐Performance Intelligent VIS‐IR Multi‐Band Modulation</t>
         </is>
       </c>
-      <c r="D71" s="52" t="inlineStr">
+      <c r="D72" s="52" t="inlineStr">
         <is>
           <t>Xungang Diao</t>
         </is>
       </c>
-      <c r="E71" s="53" t="n">
+      <c r="E72" s="53" t="n">
         <v>46256</v>
       </c>
-      <c r="F71" s="54" t="inlineStr">
+      <c r="F72" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aenm.71448</t>
         </is>
       </c>
-      <c r="G71" s="52" t="n">
+      <c r="G72" s="52" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="58" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B72" s="59" t="inlineStr">
+      <c r="B73" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
-        </is>
-      </c>
-      <c r="C72" s="59" t="n"/>
-      <c r="D72" s="59" t="n"/>
-      <c r="E72" s="59" t="n"/>
-      <c r="F72" s="59" t="n"/>
-      <c r="G72" s="59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="24" t="n"/>
-      <c r="B73" s="59" t="inlineStr">
-        <is>
-          <t>Chem</t>
         </is>
       </c>
       <c r="C73" s="59" t="n"/>
@@ -7294,10 +7302,10 @@
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="25" t="n"/>
+      <c r="A74" s="24" t="n"/>
       <c r="B74" s="59" t="inlineStr">
         <is>
-          <t>Materials Today</t>
+          <t>Chem</t>
         </is>
       </c>
       <c r="C74" s="59" t="n"/>
@@ -7308,104 +7316,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="62" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="25" t="n"/>
+      <c r="B75" s="59" t="inlineStr">
+        <is>
+          <t>Materials Today</t>
+        </is>
+      </c>
+      <c r="C75" s="59" t="n"/>
+      <c r="D75" s="59" t="n"/>
+      <c r="E75" s="59" t="n"/>
+      <c r="F75" s="59" t="n"/>
+      <c r="G75" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="62" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B75" s="63" t="inlineStr">
+      <c r="B76" s="63" t="inlineStr">
         <is>
           <t>PNAS</t>
         </is>
       </c>
-      <c r="C75" s="63" t="inlineStr">
+      <c r="C76" s="63" t="inlineStr">
         <is>
           <t>The effectiveness of green place-based industrial policy: Evidence from the Inflation Reduction Act</t>
         </is>
       </c>
-      <c r="D75" s="63" t="inlineStr">
+      <c r="D76" s="63" t="inlineStr">
         <is>
           <t>Katherine Stapleton</t>
         </is>
       </c>
-      <c r="E75" s="64" t="n">
+      <c r="E76" s="64" t="n">
         <v>46248</v>
       </c>
-      <c r="F75" s="65" t="inlineStr">
+      <c r="F76" s="65" t="inlineStr">
         <is>
           <t>https://doi.org/10.1073/pnas.2600276123</t>
         </is>
       </c>
-      <c r="G75" s="63" t="n">
+      <c r="G76" s="63" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="24" t="n"/>
-      <c r="B76" s="25" t="n"/>
-      <c r="C76" s="63" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="24" t="n"/>
+      <c r="B77" s="25" t="n"/>
+      <c r="C77" s="63" t="inlineStr">
         <is>
           <t>Can seaweed mitigate methane from cows on a global scale?</t>
         </is>
       </c>
-      <c r="D76" s="63" t="inlineStr">
+      <c r="D77" s="63" t="inlineStr">
         <is>
           <t>Allessandra DiCorato</t>
         </is>
       </c>
-      <c r="E76" s="64" t="n">
+      <c r="E77" s="64" t="n">
         <v>46260</v>
       </c>
-      <c r="F76" s="65" t="inlineStr">
+      <c r="F77" s="65" t="inlineStr">
         <is>
           <t>https://doi.org/10.1073/pnas.2626533123</t>
         </is>
       </c>
-      <c r="G76" s="25" t="n"/>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="25" t="n"/>
-      <c r="B77" s="63" t="inlineStr">
+      <c r="G77" s="25" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="25" t="n"/>
+      <c r="B78" s="63" t="inlineStr">
         <is>
           <t>National Science Review</t>
         </is>
       </c>
-      <c r="C77" s="63" t="n"/>
-      <c r="D77" s="63" t="n"/>
-      <c r="E77" s="63" t="n"/>
-      <c r="F77" s="63" t="n"/>
-      <c r="G77" s="63" t="n">
+      <c r="C78" s="63" t="n"/>
+      <c r="D78" s="63" t="n"/>
+      <c r="E78" s="63" t="n"/>
+      <c r="F78" s="63" t="n"/>
+      <c r="G78" s="63" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="G57:G67"/>
+    <mergeCell ref="G76:G77"/>
     <mergeCell ref="A7:A47"/>
-    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="A73:A75"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G51:G53"/>
     <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B52:B54"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="A76:A78"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="G67:G70"/>
     <mergeCell ref="G18:G46"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B57:B67"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="A57:A72"/>
     <mergeCell ref="B18:B46"/>
-    <mergeCell ref="G56:G66"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B56:B66"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A52:A56"/>
     <mergeCell ref="G12:G15"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="G68:G71"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
@@ -7451,10 +7474,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId50"/>
@@ -7470,8 +7493,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12527,7 +12551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13102,7 +13126,7 @@
         </is>
       </c>
       <c r="G24" s="38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
@@ -13245,7 +13269,7 @@
     </row>
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="24" t="n"/>
-      <c r="B31" s="25" t="n"/>
+      <c r="B31" s="24" t="n"/>
       <c r="C31" s="41" t="inlineStr">
         <is>
           <t>A Natural Mineral/Polymer-Based Halogen-Free Solid-State Electrolyte Enables Stable Four-Electron Iodine Chemistry with Suppressed High Voltage Self-Discharge</t>
@@ -13264,98 +13288,98 @@
           <t>https://doi.org/10.1039/d6ee04388g</t>
         </is>
       </c>
-      <c r="G31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="G31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="41" t="inlineStr">
+        <is>
+          <t>Understanding Interfacial Chemistries of LiPF6-Asymmetrically Fluorinated Glyme Ether Electrolytes for High-Voltage Lithium Metal Batteries</t>
+        </is>
+      </c>
+      <c r="D32" s="41" t="inlineStr">
+        <is>
+          <t>Yuzhang Li</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F32" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee05502h</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="38" t="n"/>
-      <c r="E32" s="38" t="n"/>
-      <c r="F32" s="38" t="n"/>
-      <c r="G32" s="38" t="n">
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="44" t="inlineStr">
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B34" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C34" s="45" t="inlineStr">
         <is>
           <t>Unveiling Dual-Interface Coordination Orchestration for Durable Aqueous Zinc–Iodine Pouch Cells with Four-Electron Chemistry</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D34" s="45" t="inlineStr">
         <is>
           <t>Zhongwei Chen</t>
         </is>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E34" s="46" t="n">
         <v>46238</v>
       </c>
-      <c r="F33" s="47" t="inlineStr">
+      <c r="F34" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c11308</t>
         </is>
       </c>
-      <c r="G33" s="45" t="n">
+      <c r="G34" s="45" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="48" t="inlineStr">
-        <is>
-          <t>Electron Push–Pull Effect Drives Reversible Six-Electron Redox Reaction in Aqueous Zinc–Dual Halogen Batteries</t>
-        </is>
-      </c>
-      <c r="D34" s="48" t="inlineStr">
-        <is>
-          <t>Liang Zhang</t>
-        </is>
-      </c>
-      <c r="E34" s="49" t="n">
-        <v>46240</v>
-      </c>
-      <c r="F34" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c08547</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="24" t="n"/>
       <c r="B35" s="24" t="n"/>
       <c r="C35" s="48" t="inlineStr">
         <is>
-          <t>Electron-Deficient Species-Driven Interphase Transformation for Practical Lithium Batteries</t>
+          <t>Electron Push–Pull Effect Drives Reversible Six-Electron Redox Reaction in Aqueous Zinc–Dual Halogen Batteries</t>
         </is>
       </c>
       <c r="D35" s="48" t="inlineStr">
         <is>
-          <t>Guangmin Zhou</t>
+          <t>Liang Zhang</t>
         </is>
       </c>
       <c r="E35" s="49" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="F35" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09703</t>
+          <t>https://doi.org/10.1021/jacs.6c08547</t>
         </is>
       </c>
       <c r="G35" s="24" t="n"/>
@@ -13365,12 +13389,12 @@
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="48" t="inlineStr">
         <is>
-          <t>High-Voltage Sodium–Metal Batteries with Asymmetric Fluoroalkoxylated Organoborate Anion Chemistry</t>
+          <t>Electron-Deficient Species-Driven Interphase Transformation for Practical Lithium Batteries</t>
         </is>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>Arumugam Manthiram</t>
+          <t>Guangmin Zhou</t>
         </is>
       </c>
       <c r="E36" s="49" t="n">
@@ -13378,7 +13402,7 @@
       </c>
       <c r="F36" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08026</t>
+          <t>https://doi.org/10.1021/jacs.6c09703</t>
         </is>
       </c>
       <c r="G36" s="24" t="n"/>
@@ -13388,12 +13412,12 @@
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="48" t="inlineStr">
         <is>
-          <t>Prismatic Na-Ion Coordination in the Sulfide-Chloride Solid Electrolyte Enables Fast Na-Ion Transport</t>
+          <t>High-Voltage Sodium–Metal Batteries with Asymmetric Fluoroalkoxylated Organoborate Anion Chemistry</t>
         </is>
       </c>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>Yu-Guo Guo</t>
+          <t>Arumugam Manthiram</t>
         </is>
       </c>
       <c r="E37" s="49" t="n">
@@ -13401,7 +13425,7 @@
       </c>
       <c r="F37" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c10148</t>
+          <t>https://doi.org/10.1021/jacs.6c08026</t>
         </is>
       </c>
       <c r="G37" s="24" t="n"/>
@@ -13411,20 +13435,20 @@
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="48" t="inlineStr">
         <is>
-          <t>An Electronically Coupled Interfacial Energy Descriptor for Predicting Coulombic Efficiency in Aqueous Zinc Batteries</t>
+          <t>Prismatic Na-Ion Coordination in the Sulfide-Chloride Solid Electrolyte Enables Fast Na-Ion Transport</t>
         </is>
       </c>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>Xiaodong Chen</t>
+          <t>Yu-Guo Guo</t>
         </is>
       </c>
       <c r="E38" s="49" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08057</t>
+          <t>https://doi.org/10.1021/jacs.6c10148</t>
         </is>
       </c>
       <c r="G38" s="24" t="n"/>
@@ -13434,20 +13458,20 @@
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="48" t="inlineStr">
         <is>
-          <t>Enhanced Sodium-Ion Transport across Solid Electrolyte Interphase via Electric-Field Modulation</t>
+          <t>An Electronically Coupled Interfacial Energy Descriptor for Predicting Coulombic Efficiency in Aqueous Zinc Batteries</t>
         </is>
       </c>
       <c r="D39" s="48" t="inlineStr">
         <is>
-          <t>Xiulin Fan</t>
+          <t>Xiaodong Chen</t>
         </is>
       </c>
       <c r="E39" s="49" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08495</t>
+          <t>https://doi.org/10.1021/jacs.6c08057</t>
         </is>
       </c>
       <c r="G39" s="24" t="n"/>
@@ -13457,66 +13481,66 @@
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="48" t="inlineStr">
         <is>
-          <t>Interfacial Lithium Redox Kinetics Regulated by Solvent Asymmetry and Moment of Inertia in Li Metal Batteries</t>
+          <t>Enhanced Sodium-Ion Transport across Solid Electrolyte Interphase via Electric-Field Modulation</t>
         </is>
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>Zhenan Bao</t>
+          <t>Xiulin Fan</t>
         </is>
       </c>
       <c r="E40" s="49" t="n">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.5c21712</t>
+          <t>https://doi.org/10.1021/jacs.6c08495</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
     </row>
-    <row r="41" ht="48" customHeight="1">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="24" t="n"/>
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="48" t="inlineStr">
         <is>
-          <t>Revealing Excited-State Electrochemical Reaction Pathways at Solid Electrolyte Interphases by Ab Initio Nonadiabatic Molecular Dynamics</t>
+          <t>Interfacial Lithium Redox Kinetics Regulated by Solvent Asymmetry and Moment of Inertia in Li Metal Batteries</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
         <is>
-          <t>Jin Zhao</t>
+          <t>Zhenan Bao</t>
         </is>
       </c>
       <c r="E41" s="49" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12254</t>
+          <t>https://doi.org/10.1021/jacs.5c21712</t>
         </is>
       </c>
       <c r="G41" s="24" t="n"/>
     </row>
-    <row r="42" ht="32" customHeight="1">
+    <row r="42" ht="48" customHeight="1">
       <c r="A42" s="24" t="n"/>
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="48" t="inlineStr">
         <is>
-          <t>Interfacial Chemistry of Storage-Induced Degradation in High-Nickel Cathodes</t>
+          <t>Revealing Excited-State Electrochemical Reaction Pathways at Solid Electrolyte Interphases by Ab Initio Nonadiabatic Molecular Dynamics</t>
         </is>
       </c>
       <c r="D42" s="48" t="inlineStr">
         <is>
-          <t>Fuqiang Huang</t>
+          <t>Jin Zhao</t>
         </is>
       </c>
       <c r="E42" s="49" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c06113</t>
+          <t>https://doi.org/10.1021/jacs.6c12254</t>
         </is>
       </c>
       <c r="G42" s="24" t="n"/>
@@ -13526,20 +13550,20 @@
       <c r="B43" s="24" t="n"/>
       <c r="C43" s="48" t="inlineStr">
         <is>
-          <t>Early Gas Evolution during Electrode Polarization in Water-in-Salt Electrolyte</t>
+          <t>Interfacial Chemistry of Storage-Induced Degradation in High-Nickel Cathodes</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
         <is>
-          <t>Brian M. Tackett</t>
+          <t>Fuqiang Huang</t>
         </is>
       </c>
       <c r="E43" s="49" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c13982</t>
+          <t>https://doi.org/10.1021/jacs.6c06113</t>
         </is>
       </c>
       <c r="G43" s="24" t="n"/>
@@ -13549,250 +13573,250 @@
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="48" t="inlineStr">
         <is>
-          <t>Tailoring Energy Landscapes for Vehicular Transport in Single-Ion Conducting Organo-Ionic Solids</t>
+          <t>Early Gas Evolution during Electrode Polarization in Water-in-Salt Electrolyte</t>
         </is>
       </c>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>Brett A. Helms</t>
+          <t>Brian M. Tackett</t>
         </is>
       </c>
       <c r="E44" s="49" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c07483</t>
+          <t>https://doi.org/10.1021/jacs.6c13982</t>
         </is>
       </c>
       <c r="G44" s="24" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="24" t="n"/>
-      <c r="B45" s="25" t="n"/>
+      <c r="B45" s="24" t="n"/>
       <c r="C45" s="48" t="inlineStr">
         <is>
-          <t>Migration-Coupled Local Fluoride Relaxation in Li2– x La(1+ x )/3Nb2O6F Single Crystals</t>
+          <t>Tailoring Energy Landscapes for Vehicular Transport in Single-Ion Conducting Organo-Ionic Solids</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
         <is>
-          <t>Yasutoshi Iriyama</t>
+          <t>Brett A. Helms</t>
         </is>
       </c>
       <c r="E45" s="49" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08912</t>
-        </is>
-      </c>
-      <c r="G45" s="25" t="n"/>
+          <t>https://doi.org/10.1021/jacs.6c07483</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="24" t="n"/>
-      <c r="B46" s="45" t="inlineStr">
-        <is>
-          <t>ACS Energy Letters</t>
-        </is>
-      </c>
-      <c r="C46" s="45" t="inlineStr">
-        <is>
-          <t>Decoupling Sodium Metal Artifacts from Hard Carbon Electrochemistry in Sodium-Ion Batteries</t>
-        </is>
-      </c>
-      <c r="D46" s="45" t="inlineStr">
-        <is>
-          <t>Clare P. Grey</t>
-        </is>
-      </c>
-      <c r="E46" s="46" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F46" s="47" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acsenergylett.6c01946</t>
-        </is>
-      </c>
-      <c r="G46" s="45" t="n">
-        <v>5</v>
-      </c>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>Migration-Coupled Local Fluoride Relaxation in Li2– x La(1+ x )/3Nb2O6F Single Crystals</t>
+        </is>
+      </c>
+      <c r="D46" s="48" t="inlineStr">
+        <is>
+          <t>Yasutoshi Iriyama</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F46" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c08912</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="24" t="n"/>
-      <c r="B47" s="24" t="n"/>
-      <c r="C47" s="48" t="inlineStr">
-        <is>
-          <t>Coupling LiF Dissolution Chemistry with Solvation Regulation for High-Power and Wide-Temperature Li/CF x Batteries</t>
-        </is>
-      </c>
-      <c r="D47" s="48" t="inlineStr">
-        <is>
-          <t>Jin Zhou</t>
-        </is>
-      </c>
-      <c r="E47" s="49" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F47" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acsenergylett.6c01466</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="n"/>
-    </row>
-    <row r="48" ht="48" customHeight="1">
+      <c r="B47" s="45" t="inlineStr">
+        <is>
+          <t>ACS Energy Letters</t>
+        </is>
+      </c>
+      <c r="C47" s="45" t="inlineStr">
+        <is>
+          <t>Decoupling Sodium Metal Artifacts from Hard Carbon Electrochemistry in Sodium-Ion Batteries</t>
+        </is>
+      </c>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>Clare P. Grey</t>
+        </is>
+      </c>
+      <c r="E47" s="46" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F47" s="47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acsenergylett.6c01946</t>
+        </is>
+      </c>
+      <c r="G47" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="24" t="n"/>
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="48" t="inlineStr">
         <is>
-          <t>Progress on Halide Solid State Electrolytes: Structural Regulation, Interfacial Engineering, and Machine Learning Driven Paradigms</t>
+          <t>Coupling LiF Dissolution Chemistry with Solvation Regulation for High-Power and Wide-Temperature Li/CF x Batteries</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>Chunwen Sun</t>
+          <t>Jin Zhou</t>
         </is>
       </c>
       <c r="E48" s="49" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/acsenergylett.6c01447</t>
+          <t>https://doi.org/10.1021/acsenergylett.6c01466</t>
         </is>
       </c>
       <c r="G48" s="24" t="n"/>
     </row>
-    <row r="49" ht="32" customHeight="1">
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="24" t="n"/>
       <c r="B49" s="24" t="n"/>
       <c r="C49" s="48" t="inlineStr">
         <is>
+          <t>Progress on Halide Solid State Electrolytes: Structural Regulation, Interfacial Engineering, and Machine Learning Driven Paradigms</t>
+        </is>
+      </c>
+      <c r="D49" s="48" t="inlineStr">
+        <is>
+          <t>Chunwen Sun</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F49" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acsenergylett.6c01447</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="48" t="inlineStr">
+        <is>
           <t>Dual-Driven Cathode Electrolyte Interphase Regulation for Durable Sodium-Ion Batteries</t>
         </is>
       </c>
-      <c r="D49" s="48" t="inlineStr">
+      <c r="D50" s="48" t="inlineStr">
         <is>
           <t>Weishan Li</t>
         </is>
       </c>
-      <c r="E49" s="49" t="n">
+      <c r="E50" s="49" t="n">
         <v>46250</v>
       </c>
-      <c r="F49" s="50" t="inlineStr">
+      <c r="F50" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acsenergylett.6c02224</t>
         </is>
       </c>
-      <c r="G49" s="24" t="n"/>
-    </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" s="24" t="n"/>
-      <c r="B50" s="25" t="n"/>
-      <c r="C50" s="48" t="inlineStr">
+      <c r="G50" s="24" t="n"/>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="24" t="n"/>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="48" t="inlineStr">
         <is>
           <t>Insights into the Oxide Cathode Active Material/Sulfide-Based Solid-State Electrolyte Interface in All-Solid-State Lithium Batteries: Coupling Mechanical and (Electro)chemical Perspectives</t>
         </is>
       </c>
-      <c r="D50" s="48" t="inlineStr">
+      <c r="D51" s="48" t="inlineStr">
         <is>
           <t>Rutao Wang</t>
         </is>
       </c>
-      <c r="E50" s="49" t="n">
+      <c r="E51" s="49" t="n">
         <v>46251</v>
       </c>
-      <c r="F50" s="50" t="inlineStr">
+      <c r="F51" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acsenergylett.6c01559</t>
         </is>
       </c>
-      <c r="G50" s="25" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="45" t="inlineStr">
+      <c r="G51" s="25" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="45" t="inlineStr">
         <is>
           <t>Chemical Reviews</t>
         </is>
       </c>
-      <c r="C51" s="45" t="n"/>
-      <c r="D51" s="45" t="n"/>
-      <c r="E51" s="45" t="n"/>
-      <c r="F51" s="45" t="n"/>
-      <c r="G51" s="45" t="n">
+      <c r="C52" s="45" t="n"/>
+      <c r="D52" s="45" t="n"/>
+      <c r="E52" s="45" t="n"/>
+      <c r="F52" s="45" t="n"/>
+      <c r="G52" s="45" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="51" t="inlineStr">
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B52" s="52" t="inlineStr">
+      <c r="B53" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C52" s="52" t="inlineStr">
+      <c r="C53" s="52" t="inlineStr">
         <is>
           <t>Competitive Adsorption and Structural Reinforcement Synergy Stabilizes High‐Voltage Quasi‐Solid‐State Batteries</t>
         </is>
       </c>
-      <c r="D52" s="52" t="inlineStr">
+      <c r="D53" s="52" t="inlineStr">
         <is>
           <t>Yun Zheng</t>
         </is>
       </c>
-      <c r="E52" s="53" t="n">
+      <c r="E53" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F52" s="54" t="inlineStr">
+      <c r="F53" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.4447296</t>
         </is>
       </c>
-      <c r="G52" s="52" t="n">
+      <c r="G53" s="52" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="24" t="n"/>
-      <c r="B53" s="24" t="n"/>
-      <c r="C53" s="55" t="inlineStr">
-        <is>
-          <t>Deciphering Kinetic Principles of Dual‐Anion Electrolytes for Extreme Fast‐Charging Lithium‐Ion Batteries</t>
-        </is>
-      </c>
-      <c r="D53" s="55" t="inlineStr">
-        <is>
-          <t>Zheng Chen</t>
-        </is>
-      </c>
-      <c r="E53" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F53" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.5861510</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="n"/>
-    </row>
-    <row r="54" ht="48" customHeight="1">
+    <row r="54" ht="32" customHeight="1">
       <c r="A54" s="24" t="n"/>
       <c r="B54" s="24" t="n"/>
       <c r="C54" s="55" t="inlineStr">
         <is>
-          <t>Dual‐Domain Coupling‐Driven Interface Remodeling Enables Ultra‐Dilute Flame‐Retardant Electrolytes for High‐Voltage, Wide‐Temperature Batteries</t>
+          <t>Deciphering Kinetic Principles of Dual‐Anion Electrolytes for Extreme Fast‐Charging Lithium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D54" s="55" t="inlineStr">
         <is>
-          <t>Xing‐Long Wu</t>
+          <t>Zheng Chen</t>
         </is>
       </c>
       <c r="E54" s="56" t="n">
@@ -13800,22 +13824,22 @@
       </c>
       <c r="F54" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.8321379</t>
+          <t>https://doi.org/10.1002/anie.5861510</t>
         </is>
       </c>
       <c r="G54" s="24" t="n"/>
     </row>
-    <row r="55" ht="32" customHeight="1">
+    <row r="55" ht="48" customHeight="1">
       <c r="A55" s="24" t="n"/>
       <c r="B55" s="24" t="n"/>
       <c r="C55" s="55" t="inlineStr">
         <is>
-          <t>Isotopic Engineering of Water Reactivity for Stable Aqueous Iron‐Metal Batteries</t>
+          <t>Dual‐Domain Coupling‐Driven Interface Remodeling Enables Ultra‐Dilute Flame‐Retardant Electrolytes for High‐Voltage, Wide‐Temperature Batteries</t>
         </is>
       </c>
       <c r="D55" s="55" t="inlineStr">
         <is>
-          <t>Hanfeng Liang</t>
+          <t>Xing‐Long Wu</t>
         </is>
       </c>
       <c r="E55" s="56" t="n">
@@ -13823,7 +13847,7 @@
       </c>
       <c r="F55" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5007458</t>
+          <t>https://doi.org/10.1002/anie.8321379</t>
         </is>
       </c>
       <c r="G55" s="24" t="n"/>
@@ -13833,12 +13857,12 @@
       <c r="B56" s="24" t="n"/>
       <c r="C56" s="55" t="inlineStr">
         <is>
-          <t>Modulating Lewis Acidity of Covalent Organic Frameworks to Boost Li+ Transport</t>
+          <t>Isotopic Engineering of Water Reactivity for Stable Aqueous Iron‐Metal Batteries</t>
         </is>
       </c>
       <c r="D56" s="55" t="inlineStr">
         <is>
-          <t>Hong Guo</t>
+          <t>Hanfeng Liang</t>
         </is>
       </c>
       <c r="E56" s="56" t="n">
@@ -13846,7 +13870,7 @@
       </c>
       <c r="F56" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6421920</t>
+          <t>https://doi.org/10.1002/anie.5007458</t>
         </is>
       </c>
       <c r="G56" s="24" t="n"/>
@@ -13856,20 +13880,20 @@
       <c r="B57" s="24" t="n"/>
       <c r="C57" s="55" t="inlineStr">
         <is>
-          <t>Ion Bridging Enables Dual‐Interface Engineering for High Capacity and Long Cycling Aqueous Zinc–Sulfur Battery</t>
+          <t>Modulating Lewis Acidity of Covalent Organic Frameworks to Boost Li+ Transport</t>
         </is>
       </c>
       <c r="D57" s="55" t="inlineStr">
         <is>
-          <t>Bao‐Lian Su</t>
+          <t>Hong Guo</t>
         </is>
       </c>
       <c r="E57" s="56" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="F57" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9631813</t>
+          <t>https://doi.org/10.1002/anie.6421920</t>
         </is>
       </c>
       <c r="G57" s="24" t="n"/>
@@ -13879,12 +13903,12 @@
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>Ionic Liquid Electrolytes for Extreme Temperature Conditions: Challenges and Perspective</t>
+          <t>Ion Bridging Enables Dual‐Interface Engineering for High Capacity and Long Cycling Aqueous Zinc–Sulfur Battery</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
         <is>
-          <t>Haolin Tang</t>
+          <t>Bao‐Lian Su</t>
         </is>
       </c>
       <c r="E58" s="56" t="n">
@@ -13892,22 +13916,22 @@
       </c>
       <c r="F58" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7793957</t>
+          <t>https://doi.org/10.1002/anie.9631813</t>
         </is>
       </c>
       <c r="G58" s="24" t="n"/>
     </row>
-    <row r="59" ht="48" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="24" t="n"/>
       <c r="B59" s="24" t="n"/>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Regulating Solvation Chemistry via Strongly Coordinating Anion and Weakly Solvating Cosolvent for Low‐Temperature Sodium Metal Batteries</t>
+          <t>Ionic Liquid Electrolytes for Extreme Temperature Conditions: Challenges and Perspective</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
         <is>
-          <t>Shijian Zheng</t>
+          <t>Haolin Tang</t>
         </is>
       </c>
       <c r="E59" s="56" t="n">
@@ -13915,7 +13939,7 @@
       </c>
       <c r="F59" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2602693</t>
+          <t>https://doi.org/10.1002/anie.7793957</t>
         </is>
       </c>
       <c r="G59" s="24" t="n"/>
@@ -13925,43 +13949,43 @@
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
-          <t>Decoupling Ion Transport and Desolvation via Spatially Heterogeneous Solvation Structure for Wide‐Temperature Sodium‐Ion Batteries</t>
+          <t>Regulating Solvation Chemistry via Strongly Coordinating Anion and Weakly Solvating Cosolvent for Low‐Temperature Sodium Metal Batteries</t>
         </is>
       </c>
       <c r="D60" s="55" t="inlineStr">
         <is>
-          <t>Pengjian Zuo</t>
+          <t>Shijian Zheng</t>
         </is>
       </c>
       <c r="E60" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F60" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4522198</t>
+          <t>https://doi.org/10.1002/anie.2602693</t>
         </is>
       </c>
       <c r="G60" s="24" t="n"/>
     </row>
-    <row r="61" ht="32" customHeight="1">
+    <row r="61" ht="48" customHeight="1">
       <c r="A61" s="24" t="n"/>
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>A Three‐Dimensional Ionic Conjugated Metal–Organic Framework</t>
+          <t>Decoupling Ion Transport and Desolvation via Spatially Heterogeneous Solvation Structure for Wide‐Temperature Sodium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D61" s="55" t="inlineStr">
         <is>
-          <t>Long Chen</t>
+          <t>Pengjian Zuo</t>
         </is>
       </c>
       <c r="E61" s="56" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="F61" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4078759</t>
+          <t>https://doi.org/10.1002/anie.4522198</t>
         </is>
       </c>
       <c r="G61" s="24" t="n"/>
@@ -13971,12 +13995,12 @@
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
-          <t>Programming Ion‐Engineered Interphase for Practical Zinc Batteries Through Exogenous Cation‐Anion Synergy Chemistry</t>
+          <t>A Three‐Dimensional Ionic Conjugated Metal–Organic Framework</t>
         </is>
       </c>
       <c r="D62" s="55" t="inlineStr">
         <is>
-          <t>Libao Chen</t>
+          <t>Long Chen</t>
         </is>
       </c>
       <c r="E62" s="56" t="n">
@@ -13984,45 +14008,45 @@
       </c>
       <c r="F62" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3578686</t>
+          <t>https://doi.org/10.1002/anie.4078759</t>
         </is>
       </c>
       <c r="G62" s="24" t="n"/>
     </row>
-    <row r="63" ht="48" customHeight="1">
+    <row r="63" ht="32" customHeight="1">
       <c r="A63" s="24" t="n"/>
       <c r="B63" s="24" t="n"/>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>Toward Robust Anion‐Derived Interphases: A Novel Ternary‐Solvent Electrolyte for High‐Voltage Fast‐Charging Sodium Batteries</t>
+          <t>Programming Ion‐Engineered Interphase for Practical Zinc Batteries Through Exogenous Cation‐Anion Synergy Chemistry</t>
         </is>
       </c>
       <c r="D63" s="55" t="inlineStr">
         <is>
-          <t>Xinming Fan</t>
+          <t>Libao Chen</t>
         </is>
       </c>
       <c r="E63" s="56" t="n">
-        <v>46250</v>
+        <v>46248</v>
       </c>
       <c r="F63" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3464448</t>
+          <t>https://doi.org/10.1002/anie.3578686</t>
         </is>
       </c>
       <c r="G63" s="24" t="n"/>
     </row>
-    <row r="64" ht="32" customHeight="1">
+    <row r="64" ht="48" customHeight="1">
       <c r="A64" s="24" t="n"/>
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="55" t="inlineStr">
         <is>
-          <t>“Armor Polymerization” Unlocks Polymer Electrolytes With Simultaneous Rapid Li+ Conduction and High Solidification</t>
+          <t>Toward Robust Anion‐Derived Interphases: A Novel Ternary‐Solvent Electrolyte for High‐Voltage Fast‐Charging Sodium Batteries</t>
         </is>
       </c>
       <c r="D64" s="55" t="inlineStr">
         <is>
-          <t>Yun Zheng</t>
+          <t>Xinming Fan</t>
         </is>
       </c>
       <c r="E64" s="56" t="n">
@@ -14030,30 +14054,30 @@
       </c>
       <c r="F64" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4583501</t>
+          <t>https://doi.org/10.1002/anie.3464448</t>
         </is>
       </c>
       <c r="G64" s="24" t="n"/>
     </row>
-    <row r="65" ht="48" customHeight="1">
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="24" t="n"/>
       <c r="B65" s="24" t="n"/>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>Enthalpy‐Entropy Molecular Design of Gel Polymer Electrolytes for Regulating Solvation Chemistry in Lithium–Sulfur Batteries</t>
+          <t>“Armor Polymerization” Unlocks Polymer Electrolytes With Simultaneous Rapid Li+ Conduction and High Solidification</t>
         </is>
       </c>
       <c r="D65" s="55" t="inlineStr">
         <is>
-          <t>Fangyuan Hu</t>
+          <t>Yun Zheng</t>
         </is>
       </c>
       <c r="E65" s="56" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="F65" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7695165</t>
+          <t>https://doi.org/10.1002/anie.4583501</t>
         </is>
       </c>
       <c r="G65" s="24" t="n"/>
@@ -14063,20 +14087,20 @@
       <c r="B66" s="24" t="n"/>
       <c r="C66" s="55" t="inlineStr">
         <is>
-          <t>Electrochemically Activated Highly Reversible Sulfate Conversion Enables High‐Voltage and Large‐Volumetric‐Capacity Zinc‐Based Anion–Cation Shuttle Battery</t>
+          <t>Enthalpy‐Entropy Molecular Design of Gel Polymer Electrolytes for Regulating Solvation Chemistry in Lithium–Sulfur Batteries</t>
         </is>
       </c>
       <c r="D66" s="55" t="inlineStr">
         <is>
-          <t>Bao‐Lian Su</t>
+          <t>Fangyuan Hu</t>
         </is>
       </c>
       <c r="E66" s="56" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F66" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3330483</t>
+          <t>https://doi.org/10.1002/anie.7695165</t>
         </is>
       </c>
       <c r="G66" s="24" t="n"/>
@@ -14086,12 +14110,12 @@
       <c r="B67" s="24" t="n"/>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>Implanted Zn2+‐Conducting Hydrogel Interphase Enables Highly Compacted Thick Iodine Electrodes for Ah‐Level Aqueous Zinc–Iodine Pouch Batteries</t>
+          <t>Electrochemically Activated Highly Reversible Sulfate Conversion Enables High‐Voltage and Large‐Volumetric‐Capacity Zinc‐Based Anion–Cation Shuttle Battery</t>
         </is>
       </c>
       <c r="D67" s="55" t="inlineStr">
         <is>
-          <t>Yang Yang</t>
+          <t>Bao‐Lian Su</t>
         </is>
       </c>
       <c r="E67" s="56" t="n">
@@ -14099,45 +14123,45 @@
       </c>
       <c r="F67" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6865881</t>
+          <t>https://doi.org/10.1002/anie.3330483</t>
         </is>
       </c>
       <c r="G67" s="24" t="n"/>
     </row>
-    <row r="68" ht="32" customHeight="1">
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="24" t="n"/>
       <c r="B68" s="24" t="n"/>
       <c r="C68" s="55" t="inlineStr">
         <is>
-          <t>Beyond Surface Catalysis: Dynamic Cation‐Regulated Interfacial Water Gating for Aqueous Polysulfide Electrochemistry</t>
+          <t>Implanted Zn2+‐Conducting Hydrogel Interphase Enables Highly Compacted Thick Iodine Electrodes for Ah‐Level Aqueous Zinc–Iodine Pouch Batteries</t>
         </is>
       </c>
       <c r="D68" s="55" t="inlineStr">
         <is>
-          <t>Zhejun Li</t>
+          <t>Yang Yang</t>
         </is>
       </c>
       <c r="E68" s="56" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F68" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6113925</t>
+          <t>https://doi.org/10.1002/anie.6865881</t>
         </is>
       </c>
       <c r="G68" s="24" t="n"/>
     </row>
-    <row r="69" ht="48" customHeight="1">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="24" t="n"/>
       <c r="B69" s="24" t="n"/>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Engineering Li+ Kinetic‐Buffering and Anion‐Anchoring Interphase via One‐Step Sequential In Situ Polymerization for Stable Solid Li Metal Batteries</t>
+          <t>Beyond Surface Catalysis: Dynamic Cation‐Regulated Interfacial Water Gating for Aqueous Polysulfide Electrochemistry</t>
         </is>
       </c>
       <c r="D69" s="55" t="inlineStr">
         <is>
-          <t>Qian Wang</t>
+          <t>Zhejun Li</t>
         </is>
       </c>
       <c r="E69" s="56" t="n">
@@ -14145,30 +14169,30 @@
       </c>
       <c r="F69" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1504807</t>
+          <t>https://doi.org/10.1002/anie.6113925</t>
         </is>
       </c>
       <c r="G69" s="24" t="n"/>
     </row>
-    <row r="70" ht="32" customHeight="1">
+    <row r="70" ht="48" customHeight="1">
       <c r="A70" s="24" t="n"/>
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="55" t="inlineStr">
         <is>
-          <t>Deuterated Aprotic Electrolytes Enable Rechargeable Lithium Batteries With High (Electro)Chemical and Thermal Stability</t>
+          <t>Engineering Li+ Kinetic‐Buffering and Anion‐Anchoring Interphase via One‐Step Sequential In Situ Polymerization for Stable Solid Li Metal Batteries</t>
         </is>
       </c>
       <c r="D70" s="55" t="inlineStr">
         <is>
-          <t>Sen Xin</t>
+          <t>Qian Wang</t>
         </is>
       </c>
       <c r="E70" s="56" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="F70" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6024891</t>
+          <t>https://doi.org/10.1002/anie.1504807</t>
         </is>
       </c>
       <c r="G70" s="24" t="n"/>
@@ -14178,35 +14202,35 @@
       <c r="B71" s="24" t="n"/>
       <c r="C71" s="55" t="inlineStr">
         <is>
-          <t>Eliminating Interfacial Stress Concentration Enables High‐Energy and High‐Safety Gel Polymer Lithium Metal Pouch Cells</t>
+          <t>Deuterated Aprotic Electrolytes Enable Rechargeable Lithium Batteries With High (Electro)Chemical and Thermal Stability</t>
         </is>
       </c>
       <c r="D71" s="55" t="inlineStr">
         <is>
-          <t>Weifeng Wei</t>
+          <t>Sen Xin</t>
         </is>
       </c>
       <c r="E71" s="56" t="n">
-        <v>46259</v>
+        <v>46257</v>
       </c>
       <c r="F71" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5503056</t>
+          <t>https://doi.org/10.1002/anie.6024891</t>
         </is>
       </c>
       <c r="G71" s="24" t="n"/>
     </row>
-    <row r="72" ht="48" customHeight="1">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="24" t="n"/>
       <c r="B72" s="24" t="n"/>
       <c r="C72" s="55" t="inlineStr">
         <is>
-          <t>Mechanically Interlocked Networks Enable High‐Performance Propylene Carbonate‐Based Gel Electrolytes for Durable Lithium‐Ion Batteries</t>
+          <t>Eliminating Interfacial Stress Concentration Enables High‐Energy and High‐Safety Gel Polymer Lithium Metal Pouch Cells</t>
         </is>
       </c>
       <c r="D72" s="55" t="inlineStr">
         <is>
-          <t>Zheng Liang</t>
+          <t>Weifeng Wei</t>
         </is>
       </c>
       <c r="E72" s="56" t="n">
@@ -14214,7 +14238,7 @@
       </c>
       <c r="F72" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1853847</t>
+          <t>https://doi.org/10.1002/anie.5503056</t>
         </is>
       </c>
       <c r="G72" s="24" t="n"/>
@@ -14224,12 +14248,12 @@
       <c r="B73" s="24" t="n"/>
       <c r="C73" s="55" t="inlineStr">
         <is>
-          <t>Steric‐Electronic Engineering of Ester Carbonyls Enables Thermodynamic‐Kinetic Regulation of Electron Transfer for High‐Voltage and High‐Rate Lithium Metal Batteries</t>
+          <t>Mechanically Interlocked Networks Enable High‐Performance Propylene Carbonate‐Based Gel Electrolytes for Durable Lithium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D73" s="55" t="inlineStr">
         <is>
-          <t>Jinkui Feng</t>
+          <t>Zheng Liang</t>
         </is>
       </c>
       <c r="E73" s="56" t="n">
@@ -14237,30 +14261,30 @@
       </c>
       <c r="F73" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5288915</t>
+          <t>https://doi.org/10.1002/anie.1853847</t>
         </is>
       </c>
       <c r="G73" s="24" t="n"/>
     </row>
-    <row r="74" ht="32" customHeight="1">
+    <row r="74" ht="48" customHeight="1">
       <c r="A74" s="24" t="n"/>
       <c r="B74" s="24" t="n"/>
       <c r="C74" s="55" t="inlineStr">
         <is>
-          <t>A Dual‐Interface Stabilizing Additive for High‐voltage Sodium Metal Batteries</t>
+          <t>Steric‐Electronic Engineering of Ester Carbonyls Enables Thermodynamic‐Kinetic Regulation of Electron Transfer for High‐Voltage and High‐Rate Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="D74" s="55" t="inlineStr">
         <is>
-          <t>Qifeng Zheng</t>
+          <t>Jinkui Feng</t>
         </is>
       </c>
       <c r="E74" s="56" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="F74" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5330124</t>
+          <t>https://doi.org/10.1002/anie.5288915</t>
         </is>
       </c>
       <c r="G74" s="24" t="n"/>
@@ -14270,12 +14294,12 @@
       <c r="B75" s="24" t="n"/>
       <c r="C75" s="55" t="inlineStr">
         <is>
-          <t>Adaptive Solvation Evolution by Molecular Design Enables High‐Performance Wide‐Temperature Lithium‐Ion Batteries</t>
+          <t>A Dual‐Interface Stabilizing Additive for High‐voltage Sodium Metal Batteries</t>
         </is>
       </c>
       <c r="D75" s="55" t="inlineStr">
         <is>
-          <t>Chunzhong Li</t>
+          <t>Qifeng Zheng</t>
         </is>
       </c>
       <c r="E75" s="56" t="n">
@@ -14283,22 +14307,22 @@
       </c>
       <c r="F75" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2577060</t>
+          <t>https://doi.org/10.1002/anie.5330124</t>
         </is>
       </c>
       <c r="G75" s="24" t="n"/>
     </row>
-    <row r="76" ht="48" customHeight="1">
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="24" t="n"/>
       <c r="B76" s="24" t="n"/>
       <c r="C76" s="55" t="inlineStr">
         <is>
-          <t>Descriptor‐Guided Dynamic Solvation‐Shell Reconstruction Enables PEO‐Based Polymer Electrolytes With 10.9 mS cm−1 Ionic Conductivity</t>
+          <t>Adaptive Solvation Evolution by Molecular Design Enables High‐Performance Wide‐Temperature Lithium‐Ion Batteries</t>
         </is>
       </c>
       <c r="D76" s="55" t="inlineStr">
         <is>
-          <t>Yulong Liu</t>
+          <t>Chunzhong Li</t>
         </is>
       </c>
       <c r="E76" s="56" t="n">
@@ -14306,30 +14330,30 @@
       </c>
       <c r="F76" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3211208</t>
+          <t>https://doi.org/10.1002/anie.2577060</t>
         </is>
       </c>
       <c r="G76" s="24" t="n"/>
     </row>
-    <row r="77" ht="32" customHeight="1">
+    <row r="77" ht="48" customHeight="1">
       <c r="A77" s="24" t="n"/>
       <c r="B77" s="24" t="n"/>
       <c r="C77" s="55" t="inlineStr">
         <is>
-          <t>Enabling Fast Charging of Lithium‐Ion Batteries With Regioisomeric Nitrile Additives for Interphase Regulation</t>
+          <t>Descriptor‐Guided Dynamic Solvation‐Shell Reconstruction Enables PEO‐Based Polymer Electrolytes With 10.9 mS cm−1 Ionic Conductivity</t>
         </is>
       </c>
       <c r="D77" s="55" t="inlineStr">
         <is>
-          <t>Arumugam Manthiram</t>
+          <t>Yulong Liu</t>
         </is>
       </c>
       <c r="E77" s="56" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="F77" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6426355</t>
+          <t>https://doi.org/10.1002/anie.3211208</t>
         </is>
       </c>
       <c r="G77" s="24" t="n"/>
@@ -14339,12 +14363,12 @@
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="55" t="inlineStr">
         <is>
-          <t>Non‐Entangled Chains Enable Rapid Na+ Transport Through Ion‐Traps in Gel Polymer Electrolytes at Low Temperatures</t>
+          <t>Enabling Fast Charging of Lithium‐Ion Batteries With Regioisomeric Nitrile Additives for Interphase Regulation</t>
         </is>
       </c>
       <c r="D78" s="55" t="inlineStr">
         <is>
-          <t>Xian‐Ming Zhang</t>
+          <t>Arumugam Manthiram</t>
         </is>
       </c>
       <c r="E78" s="56" t="n">
@@ -14352,22 +14376,22 @@
       </c>
       <c r="F78" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1625450</t>
+          <t>https://doi.org/10.1002/anie.6426355</t>
         </is>
       </c>
       <c r="G78" s="24" t="n"/>
     </row>
-    <row r="79" ht="48" customHeight="1">
+    <row r="79" ht="32" customHeight="1">
       <c r="A79" s="24" t="n"/>
       <c r="B79" s="24" t="n"/>
       <c r="C79" s="55" t="inlineStr">
         <is>
-          <t>Synergistic Molecular and Polymer Network Design Enables Stable LiPF6‐Based Gel Polymer Electrolytes for Lithium Metal Batteries</t>
+          <t>Non‐Entangled Chains Enable Rapid Na+ Transport Through Ion‐Traps in Gel Polymer Electrolytes at Low Temperatures</t>
         </is>
       </c>
       <c r="D79" s="55" t="inlineStr">
         <is>
-          <t>Baohua Li</t>
+          <t>Xian‐Ming Zhang</t>
         </is>
       </c>
       <c r="E79" s="56" t="n">
@@ -14375,53 +14399,53 @@
       </c>
       <c r="F79" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6028878</t>
+          <t>https://doi.org/10.1002/anie.1625450</t>
         </is>
       </c>
       <c r="G79" s="24" t="n"/>
     </row>
-    <row r="80" ht="32" customHeight="1">
+    <row r="80" ht="48" customHeight="1">
       <c r="A80" s="24" t="n"/>
       <c r="B80" s="24" t="n"/>
       <c r="C80" s="55" t="inlineStr">
         <is>
-          <t>Local Acidity as a Corrosiveness Descriptor of Fluorinated Ether Solvents in Lithium–Metal Batteries</t>
+          <t>Synergistic Molecular and Polymer Network Design Enables Stable LiPF6‐Based Gel Polymer Electrolytes for Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="D80" s="55" t="inlineStr">
         <is>
-          <t>Jang Wook Choi</t>
+          <t>Baohua Li</t>
         </is>
       </c>
       <c r="E80" s="56" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="F80" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1576222</t>
+          <t>https://doi.org/10.1002/anie.6028878</t>
         </is>
       </c>
       <c r="G80" s="24" t="n"/>
     </row>
-    <row r="81" ht="48" customHeight="1">
+    <row r="81" ht="32" customHeight="1">
       <c r="A81" s="24" t="n"/>
       <c r="B81" s="24" t="n"/>
       <c r="C81" s="55" t="inlineStr">
         <is>
-          <t>4.8 V and All‐Climate (−60 to 55°C) All‐Solid‐State Batteries Enabled by Dual‐Phase Symbiotic Halide Solid Electrolytes</t>
+          <t>Local Acidity as a Corrosiveness Descriptor of Fluorinated Ether Solvents in Lithium–Metal Batteries</t>
         </is>
       </c>
       <c r="D81" s="55" t="inlineStr">
         <is>
-          <t>Xiaoling Xiao</t>
+          <t>Jang Wook Choi</t>
         </is>
       </c>
       <c r="E81" s="56" t="n">
-        <v>46265</v>
+        <v>46263</v>
       </c>
       <c r="F81" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4852008</t>
+          <t>https://doi.org/10.1002/anie.1576222</t>
         </is>
       </c>
       <c r="G81" s="24" t="n"/>
@@ -14431,12 +14455,12 @@
       <c r="B82" s="24" t="n"/>
       <c r="C82" s="55" t="inlineStr">
         <is>
-          <t>Na2Ti3O7‐Assisted Grain‐Boundary Tailoring of NASICON Electrolytes for Room‐to‐Subzero‐Temperature All‐Solid‐State Sodium Metal Batteries</t>
+          <t>4.8 V and All‐Climate (−60 to 55°C) All‐Solid‐State Batteries Enabled by Dual‐Phase Symbiotic Halide Solid Electrolytes</t>
         </is>
       </c>
       <c r="D82" s="55" t="inlineStr">
         <is>
-          <t>Yan Yu</t>
+          <t>Xiaoling Xiao</t>
         </is>
       </c>
       <c r="E82" s="56" t="n">
@@ -14444,22 +14468,22 @@
       </c>
       <c r="F82" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.8268615</t>
+          <t>https://doi.org/10.1002/anie.4852008</t>
         </is>
       </c>
       <c r="G82" s="24" t="n"/>
     </row>
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="24" t="n"/>
-      <c r="B83" s="25" t="n"/>
+      <c r="B83" s="24" t="n"/>
       <c r="C83" s="55" t="inlineStr">
         <is>
-          <t>Sequencing 4f–2p Gradient Orbital Coupling Within Guanidinium‐Based Coordination Nanoplates to Boost Lithium‐Ion Conductivity</t>
+          <t>Na2Ti3O7‐Assisted Grain‐Boundary Tailoring of NASICON Electrolytes for Room‐to‐Subzero‐Temperature All‐Solid‐State Sodium Metal Batteries</t>
         </is>
       </c>
       <c r="D83" s="55" t="inlineStr">
         <is>
-          <t>Amal Kumar Mandal</t>
+          <t>Yan Yu</t>
         </is>
       </c>
       <c r="E83" s="56" t="n">
@@ -14467,103 +14491,103 @@
       </c>
       <c r="F83" s="57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1002/anie.8268615</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="n"/>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="24" t="n"/>
+      <c r="B84" s="25" t="n"/>
+      <c r="C84" s="55" t="inlineStr">
+        <is>
+          <t>Sequencing 4f–2p Gradient Orbital Coupling Within Guanidinium‐Based Coordination Nanoplates to Boost Lithium‐Ion Conductivity</t>
+        </is>
+      </c>
+      <c r="D84" s="55" t="inlineStr">
+        <is>
+          <t>Amal Kumar Mandal</t>
+        </is>
+      </c>
+      <c r="E84" s="56" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F84" s="57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1002/anie.1258536</t>
         </is>
       </c>
-      <c r="G83" s="25" t="n"/>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="24" t="n"/>
-      <c r="B84" s="52" t="inlineStr">
-        <is>
-          <t>Advanced Materials</t>
-        </is>
-      </c>
-      <c r="C84" s="52" t="inlineStr">
-        <is>
-          <t>A 5 µm-thick electrolyte with a high-entropy interphase for practical solid-state lithium metal batteries</t>
-        </is>
-      </c>
-      <c r="D84" s="52" t="inlineStr">
-        <is>
-          <t>Hui-Ming Cheng</t>
-        </is>
-      </c>
-      <c r="E84" s="53" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F84" s="54" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/nsr/nwag511</t>
-        </is>
-      </c>
-      <c r="G84" s="52" t="n">
-        <v>1</v>
-      </c>
+      <c r="G84" s="25" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="24" t="n"/>
       <c r="B85" s="52" t="inlineStr">
         <is>
+          <t>Advanced Materials</t>
+        </is>
+      </c>
+      <c r="C85" s="52" t="inlineStr">
+        <is>
+          <t>A 5 µm-thick electrolyte with a high-entropy interphase for practical solid-state lithium metal batteries</t>
+        </is>
+      </c>
+      <c r="D85" s="52" t="inlineStr">
+        <is>
+          <t>Hui-Ming Cheng</t>
+        </is>
+      </c>
+      <c r="E85" s="53" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F85" s="54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/nsr/nwag511</t>
+        </is>
+      </c>
+      <c r="G85" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="24" t="n"/>
+      <c r="B86" s="52" t="inlineStr">
+        <is>
           <t>Advanced Energy Materials</t>
         </is>
       </c>
-      <c r="C85" s="52" t="inlineStr">
+      <c r="C86" s="52" t="inlineStr">
         <is>
           <t>Breaking the Polarity–Coordination Coupling in Electrolyte Design for High‐Voltage Lithium Batteries</t>
         </is>
       </c>
-      <c r="D85" s="52" t="inlineStr">
+      <c r="D86" s="52" t="inlineStr">
         <is>
           <t>Shan Fang</t>
         </is>
       </c>
-      <c r="E85" s="53" t="n">
+      <c r="E86" s="53" t="n">
         <v>46238</v>
       </c>
-      <c r="F85" s="54" t="inlineStr">
+      <c r="F86" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aenm.71380</t>
         </is>
       </c>
-      <c r="G85" s="52" t="n">
+      <c r="G86" s="52" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="86" ht="48" customHeight="1">
-      <c r="A86" s="24" t="n"/>
-      <c r="B86" s="24" t="n"/>
-      <c r="C86" s="55" t="inlineStr">
-        <is>
-          <t>Garnet‐Induced Amorphization of Fluoride Solid Electrolyte Interlayer Enables High‐Voltage and Large‐Capacity Lithium Metal Solid‐State Batteries</t>
-        </is>
-      </c>
-      <c r="D86" s="55" t="inlineStr">
-        <is>
-          <t>Chilin Li</t>
-        </is>
-      </c>
-      <c r="E86" s="56" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F86" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71375</t>
-        </is>
-      </c>
-      <c r="G86" s="24" t="n"/>
-    </row>
-    <row r="87" ht="32" customHeight="1">
+    <row r="87" ht="48" customHeight="1">
       <c r="A87" s="24" t="n"/>
       <c r="B87" s="24" t="n"/>
       <c r="C87" s="55" t="inlineStr">
         <is>
-          <t>Perfluorinated Asymmetric Magnesium Salts Enable Stable and Dendrite‐Free Magnesium Batteries</t>
+          <t>Garnet‐Induced Amorphization of Fluoride Solid Electrolyte Interlayer Enables High‐Voltage and Large‐Capacity Lithium Metal Solid‐State Batteries</t>
         </is>
       </c>
       <c r="D87" s="55" t="inlineStr">
         <is>
-          <t>Junwu Zhu</t>
+          <t>Chilin Li</t>
         </is>
       </c>
       <c r="E87" s="56" t="n">
@@ -14571,45 +14595,45 @@
       </c>
       <c r="F87" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71383</t>
+          <t>https://doi.org/10.1002/aenm.71375</t>
         </is>
       </c>
       <c r="G87" s="24" t="n"/>
     </row>
-    <row r="88" ht="48" customHeight="1">
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="24" t="n"/>
       <c r="B88" s="24" t="n"/>
       <c r="C88" s="55" t="inlineStr">
         <is>
-          <t>Dynamic Li+ Releasing‐Pulling Design of Weakly Coordinated Gel Polymer Electrolytes Realizing Practical Wide‐Temperature Lithium Metal Batteries</t>
+          <t>Perfluorinated Asymmetric Magnesium Salts Enable Stable and Dendrite‐Free Magnesium Batteries</t>
         </is>
       </c>
       <c r="D88" s="55" t="inlineStr">
         <is>
-          <t>Haiming Xie</t>
+          <t>Junwu Zhu</t>
         </is>
       </c>
       <c r="E88" s="56" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="F88" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71386</t>
+          <t>https://doi.org/10.1002/aenm.71383</t>
         </is>
       </c>
       <c r="G88" s="24" t="n"/>
     </row>
-    <row r="89" ht="32" customHeight="1">
+    <row r="89" ht="48" customHeight="1">
       <c r="A89" s="24" t="n"/>
       <c r="B89" s="24" t="n"/>
       <c r="C89" s="55" t="inlineStr">
         <is>
-          <t>Progress and Perspectives of In Situ Polymerized Solid‐State Electrolytes for Sodium Batteries</t>
+          <t>Dynamic Li+ Releasing‐Pulling Design of Weakly Coordinated Gel Polymer Electrolytes Realizing Practical Wide‐Temperature Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="D89" s="55" t="inlineStr">
         <is>
-          <t>Yong‐Sheng Hu</t>
+          <t>Haiming Xie</t>
         </is>
       </c>
       <c r="E89" s="56" t="n">
@@ -14617,30 +14641,30 @@
       </c>
       <c r="F89" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71378</t>
+          <t>https://doi.org/10.1002/aenm.71386</t>
         </is>
       </c>
       <c r="G89" s="24" t="n"/>
     </row>
-    <row r="90" ht="48" customHeight="1">
+    <row r="90" ht="32" customHeight="1">
       <c r="A90" s="24" t="n"/>
       <c r="B90" s="24" t="n"/>
       <c r="C90" s="55" t="inlineStr">
         <is>
-          <t>Halide Solid‐State Electrolytes for all‐Solid‐State Lithium Batteries: Structure, Transport, Interface Relationships and Design Principles</t>
+          <t>Progress and Perspectives of In Situ Polymerized Solid‐State Electrolytes for Sodium Batteries</t>
         </is>
       </c>
       <c r="D90" s="55" t="inlineStr">
         <is>
-          <t>Yanwei Ma</t>
+          <t>Yong‐Sheng Hu</t>
         </is>
       </c>
       <c r="E90" s="56" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="F90" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71414</t>
+          <t>https://doi.org/10.1002/aenm.71378</t>
         </is>
       </c>
       <c r="G90" s="24" t="n"/>
@@ -14650,12 +14674,12 @@
       <c r="B91" s="24" t="n"/>
       <c r="C91" s="55" t="inlineStr">
         <is>
-          <t>Reconstructing Solvation Structure via Strongly Nucleophilic Anions for High‐Rate and Low‐Temperature Graphite||LFP Pouch Cells in PC‐Based Electrolyte</t>
+          <t>Halide Solid‐State Electrolytes for all‐Solid‐State Lithium Batteries: Structure, Transport, Interface Relationships and Design Principles</t>
         </is>
       </c>
       <c r="D91" s="55" t="inlineStr">
         <is>
-          <t>Ge Li</t>
+          <t>Yanwei Ma</t>
         </is>
       </c>
       <c r="E91" s="56" t="n">
@@ -14663,7 +14687,7 @@
       </c>
       <c r="F91" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71406</t>
+          <t>https://doi.org/10.1002/aenm.71414</t>
         </is>
       </c>
       <c r="G91" s="24" t="n"/>
@@ -14673,12 +14697,12 @@
       <c r="B92" s="24" t="n"/>
       <c r="C92" s="55" t="inlineStr">
         <is>
-          <t>Regulating Uniform Zinc Deposition via Covalently Tethered Imidazolium Cations in Polyacrylamide Hydrogel Electrolytes for Stable Aqueous Zinc Batteries</t>
+          <t>Reconstructing Solvation Structure via Strongly Nucleophilic Anions for High‐Rate and Low‐Temperature Graphite||LFP Pouch Cells in PC‐Based Electrolyte</t>
         </is>
       </c>
       <c r="D92" s="55" t="inlineStr">
         <is>
-          <t>Cheng Zhang</t>
+          <t>Ge Li</t>
         </is>
       </c>
       <c r="E92" s="56" t="n">
@@ -14686,30 +14710,30 @@
       </c>
       <c r="F92" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71370</t>
+          <t>https://doi.org/10.1002/aenm.71406</t>
         </is>
       </c>
       <c r="G92" s="24" t="n"/>
     </row>
-    <row r="93" ht="32" customHeight="1">
+    <row r="93" ht="48" customHeight="1">
       <c r="A93" s="24" t="n"/>
       <c r="B93" s="24" t="n"/>
       <c r="C93" s="55" t="inlineStr">
         <is>
-          <t>Multiscale Confinement Electrolyte Enables Low‐Temperature Stable Aqueous Zinc‐Iodine Batteries</t>
+          <t>Regulating Uniform Zinc Deposition via Covalently Tethered Imidazolium Cations in Polyacrylamide Hydrogel Electrolytes for Stable Aqueous Zinc Batteries</t>
         </is>
       </c>
       <c r="D93" s="55" t="inlineStr">
         <is>
-          <t>Shaoming Huang</t>
+          <t>Cheng Zhang</t>
         </is>
       </c>
       <c r="E93" s="56" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="F93" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71384</t>
+          <t>https://doi.org/10.1002/aenm.71370</t>
         </is>
       </c>
       <c r="G93" s="24" t="n"/>
@@ -14719,20 +14743,20 @@
       <c r="B94" s="24" t="n"/>
       <c r="C94" s="55" t="inlineStr">
         <is>
-          <t>Chemomechanically Adaptive MXene–Si–Ag Dual‐Seed Interlayer Enabling Low‐Pressure Sulfide all‐Solid‐State Batteries</t>
+          <t>Multiscale Confinement Electrolyte Enables Low‐Temperature Stable Aqueous Zinc‐Iodine Batteries</t>
         </is>
       </c>
       <c r="D94" s="55" t="inlineStr">
         <is>
-          <t>Soojin Park</t>
+          <t>Shaoming Huang</t>
         </is>
       </c>
       <c r="E94" s="56" t="n">
-        <v>46249</v>
+        <v>46247</v>
       </c>
       <c r="F94" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71461</t>
+          <t>https://doi.org/10.1002/aenm.71384</t>
         </is>
       </c>
       <c r="G94" s="24" t="n"/>
@@ -14742,12 +14766,12 @@
       <c r="B95" s="24" t="n"/>
       <c r="C95" s="55" t="inlineStr">
         <is>
-          <t>Reveal Non‐Uniform Passivation on Lithium Metal Anode With Operando Spectroscopic Ellipsometry</t>
+          <t>Chemomechanically Adaptive MXene–Si–Ag Dual‐Seed Interlayer Enabling Low‐Pressure Sulfide all‐Solid‐State Batteries</t>
         </is>
       </c>
       <c r="D95" s="55" t="inlineStr">
         <is>
-          <t>Feifei Shi</t>
+          <t>Soojin Park</t>
         </is>
       </c>
       <c r="E95" s="56" t="n">
@@ -14755,7 +14779,7 @@
       </c>
       <c r="F95" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71434</t>
+          <t>https://doi.org/10.1002/aenm.71461</t>
         </is>
       </c>
       <c r="G95" s="24" t="n"/>
@@ -14765,12 +14789,12 @@
       <c r="B96" s="24" t="n"/>
       <c r="C96" s="55" t="inlineStr">
         <is>
-          <t>Tailoring Electrolyte Chemistry Through Precise Organic Synthesis for Lithium Metal Batteries</t>
+          <t>Reveal Non‐Uniform Passivation on Lithium Metal Anode With Operando Spectroscopic Ellipsometry</t>
         </is>
       </c>
       <c r="D96" s="55" t="inlineStr">
         <is>
-          <t>Cao Guan</t>
+          <t>Feifei Shi</t>
         </is>
       </c>
       <c r="E96" s="56" t="n">
@@ -14778,7 +14802,7 @@
       </c>
       <c r="F96" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71447</t>
+          <t>https://doi.org/10.1002/aenm.71434</t>
         </is>
       </c>
       <c r="G96" s="24" t="n"/>
@@ -14788,43 +14812,43 @@
       <c r="B97" s="24" t="n"/>
       <c r="C97" s="55" t="inlineStr">
         <is>
-          <t>Ether‐Based Electrolytes and the Solvation Structure in Sodium Ion Batteries</t>
+          <t>Tailoring Electrolyte Chemistry Through Precise Organic Synthesis for Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="D97" s="55" t="inlineStr">
         <is>
-          <t>John T. S. Irvine</t>
+          <t>Cao Guan</t>
         </is>
       </c>
       <c r="E97" s="56" t="n">
-        <v>46252</v>
+        <v>46249</v>
       </c>
       <c r="F97" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71452</t>
+          <t>https://doi.org/10.1002/aenm.71447</t>
         </is>
       </c>
       <c r="G97" s="24" t="n"/>
     </row>
-    <row r="98" ht="48" customHeight="1">
+    <row r="98" ht="32" customHeight="1">
       <c r="A98" s="24" t="n"/>
       <c r="B98" s="24" t="n"/>
       <c r="C98" s="55" t="inlineStr">
         <is>
-          <t>Decoupling Thermodynamic and Kinetic Moisture Instability Reveals a Critical Humidity Threshold for Sodium Thiophosphate Solid Electrolyte</t>
+          <t>Ether‐Based Electrolytes and the Solvation Structure in Sodium Ion Batteries</t>
         </is>
       </c>
       <c r="D98" s="55" t="inlineStr">
         <is>
-          <t>Chengcheng Fang</t>
+          <t>John T. S. Irvine</t>
         </is>
       </c>
       <c r="E98" s="56" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="F98" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71467</t>
+          <t>https://doi.org/10.1002/aenm.71452</t>
         </is>
       </c>
       <c r="G98" s="24" t="n"/>
@@ -14834,12 +14858,12 @@
       <c r="B99" s="24" t="n"/>
       <c r="C99" s="55" t="inlineStr">
         <is>
-          <t>Pushing Energy Density Limits: Anode‐Less Solid‐State Battery Integrated With Amorphous Lithium Vanadium Oxide Thin‐Film Cathode (Adv. Energy Mater. 31/2026)</t>
+          <t>Decoupling Thermodynamic and Kinetic Moisture Instability Reveals a Critical Humidity Threshold for Sodium Thiophosphate Solid Electrolyte</t>
         </is>
       </c>
       <c r="D99" s="55" t="inlineStr">
         <is>
-          <t>Hyun‐Suk Kim</t>
+          <t>Chengcheng Fang</t>
         </is>
       </c>
       <c r="E99" s="56" t="n">
@@ -14847,7 +14871,7 @@
       </c>
       <c r="F99" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71327</t>
+          <t>https://doi.org/10.1002/aenm.71467</t>
         </is>
       </c>
       <c r="G99" s="24" t="n"/>
@@ -14857,12 +14881,12 @@
       <c r="B100" s="24" t="n"/>
       <c r="C100" s="55" t="inlineStr">
         <is>
-          <t>Understanding the Electrolyte‐Hard Carbon Interphase Synergy in Sodium‐Ion Batteries: From Mechanistic Insights to Design Strategies</t>
+          <t>Pushing Energy Density Limits: Anode‐Less Solid‐State Battery Integrated With Amorphous Lithium Vanadium Oxide Thin‐Film Cathode (Adv. Energy Mater. 31/2026)</t>
         </is>
       </c>
       <c r="D100" s="55" t="inlineStr">
         <is>
-          <t>Xingqiao Wu</t>
+          <t>Hyun‐Suk Kim</t>
         </is>
       </c>
       <c r="E100" s="56" t="n">
@@ -14870,45 +14894,45 @@
       </c>
       <c r="F100" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71425</t>
+          <t>https://doi.org/10.1002/aenm.71327</t>
         </is>
       </c>
       <c r="G100" s="24" t="n"/>
     </row>
-    <row r="101" ht="32" customHeight="1">
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="24" t="n"/>
       <c r="B101" s="24" t="n"/>
       <c r="C101" s="55" t="inlineStr">
         <is>
-          <t>A Fluorine‐Free, Low Ion Pair Electrolyte for Transition Metal‐Free and Halogen‐Free Sodium Batteries</t>
+          <t>Understanding the Electrolyte‐Hard Carbon Interphase Synergy in Sodium‐Ion Batteries: From Mechanistic Insights to Design Strategies</t>
         </is>
       </c>
       <c r="D101" s="55" t="inlineStr">
         <is>
-          <t>Feng Lin</t>
+          <t>Xingqiao Wu</t>
         </is>
       </c>
       <c r="E101" s="56" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F101" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71422</t>
+          <t>https://doi.org/10.1002/aenm.71425</t>
         </is>
       </c>
       <c r="G101" s="24" t="n"/>
     </row>
-    <row r="102" ht="48" customHeight="1">
+    <row r="102" ht="32" customHeight="1">
       <c r="A102" s="24" t="n"/>
       <c r="B102" s="24" t="n"/>
       <c r="C102" s="55" t="inlineStr">
         <is>
-          <t>Fluoride‐Driven Interfacial Engineering: Architecting Functional Layers for High‐Performance Dendrite‐Free Li Metal Batteries</t>
+          <t>A Fluorine‐Free, Low Ion Pair Electrolyte for Transition Metal‐Free and Halogen‐Free Sodium Batteries</t>
         </is>
       </c>
       <c r="D102" s="55" t="inlineStr">
         <is>
-          <t>Hongqiang Wang</t>
+          <t>Feng Lin</t>
         </is>
       </c>
       <c r="E102" s="56" t="n">
@@ -14916,22 +14940,22 @@
       </c>
       <c r="F102" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71463</t>
+          <t>https://doi.org/10.1002/aenm.71422</t>
         </is>
       </c>
       <c r="G102" s="24" t="n"/>
     </row>
-    <row r="103" ht="32" customHeight="1">
+    <row r="103" ht="48" customHeight="1">
       <c r="A103" s="24" t="n"/>
       <c r="B103" s="24" t="n"/>
       <c r="C103" s="55" t="inlineStr">
         <is>
-          <t>Multi‐Selective Dominant Coordination in Multi‐Salt High‐Entropy Electrolytes Toward High‐Performance Silicon Anodes</t>
+          <t>Fluoride‐Driven Interfacial Engineering: Architecting Functional Layers for High‐Performance Dendrite‐Free Li Metal Batteries</t>
         </is>
       </c>
       <c r="D103" s="55" t="inlineStr">
         <is>
-          <t>Wei‐Qiang Han</t>
+          <t>Hongqiang Wang</t>
         </is>
       </c>
       <c r="E103" s="56" t="n">
@@ -14939,7 +14963,7 @@
       </c>
       <c r="F103" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71486</t>
+          <t>https://doi.org/10.1002/aenm.71463</t>
         </is>
       </c>
       <c r="G103" s="24" t="n"/>
@@ -14949,35 +14973,35 @@
       <c r="B104" s="24" t="n"/>
       <c r="C104" s="55" t="inlineStr">
         <is>
-          <t>Composite Hydrogels With Controlled Liquid Metal Release for Dendrite‐Free Zinc Anodes</t>
+          <t>Multi‐Selective Dominant Coordination in Multi‐Salt High‐Entropy Electrolytes Toward High‐Performance Silicon Anodes</t>
         </is>
       </c>
       <c r="D104" s="55" t="inlineStr">
         <is>
-          <t>Jingyi Wu</t>
+          <t>Wei‐Qiang Han</t>
         </is>
       </c>
       <c r="E104" s="56" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="F104" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71504</t>
+          <t>https://doi.org/10.1002/aenm.71486</t>
         </is>
       </c>
       <c r="G104" s="24" t="n"/>
     </row>
-    <row r="105" ht="48" customHeight="1">
+    <row r="105" ht="32" customHeight="1">
       <c r="A105" s="24" t="n"/>
       <c r="B105" s="24" t="n"/>
       <c r="C105" s="55" t="inlineStr">
         <is>
-          <t>Temperature‐Responsive Electrical Double Layer for Self‐Adaptive Solid Electrolyte Interphase Unlocks Wide‐Temperature Aqueous Zinc Ion Batteries</t>
+          <t>Composite Hydrogels With Controlled Liquid Metal Release for Dendrite‐Free Zinc Anodes</t>
         </is>
       </c>
       <c r="D105" s="55" t="inlineStr">
         <is>
-          <t>Lingzhi Zhao</t>
+          <t>Jingyi Wu</t>
         </is>
       </c>
       <c r="E105" s="56" t="n">
@@ -14985,30 +15009,30 @@
       </c>
       <c r="F105" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71472</t>
+          <t>https://doi.org/10.1002/aenm.71504</t>
         </is>
       </c>
       <c r="G105" s="24" t="n"/>
     </row>
-    <row r="106" ht="32" customHeight="1">
+    <row r="106" ht="48" customHeight="1">
       <c r="A106" s="24" t="n"/>
       <c r="B106" s="24" t="n"/>
       <c r="C106" s="55" t="inlineStr">
         <is>
-          <t>Challenges and Design Strategies Toward Aqueous Zinc‐Ion Batteries Beyond Laboratory</t>
+          <t>Temperature‐Responsive Electrical Double Layer for Self‐Adaptive Solid Electrolyte Interphase Unlocks Wide‐Temperature Aqueous Zinc Ion Batteries</t>
         </is>
       </c>
       <c r="D106" s="55" t="inlineStr">
         <is>
-          <t>Anqiang Pan</t>
+          <t>Lingzhi Zhao</t>
         </is>
       </c>
       <c r="E106" s="56" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="F106" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71454</t>
+          <t>https://doi.org/10.1002/aenm.71472</t>
         </is>
       </c>
       <c r="G106" s="24" t="n"/>
@@ -15018,20 +15042,20 @@
       <c r="B107" s="24" t="n"/>
       <c r="C107" s="55" t="inlineStr">
         <is>
-          <t>Coordination Chemistry Enabled Multifunctional Electrolytes for High‐Rate and Long‐Cycle Sodium‐Metal Batteries</t>
+          <t>Challenges and Design Strategies Toward Aqueous Zinc‐Ion Batteries Beyond Laboratory</t>
         </is>
       </c>
       <c r="D107" s="55" t="inlineStr">
         <is>
-          <t>Chengxin Wang</t>
+          <t>Anqiang Pan</t>
         </is>
       </c>
       <c r="E107" s="56" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="F107" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71442</t>
+          <t>https://doi.org/10.1002/aenm.71454</t>
         </is>
       </c>
       <c r="G107" s="24" t="n"/>
@@ -15041,12 +15065,12 @@
       <c r="B108" s="24" t="n"/>
       <c r="C108" s="55" t="inlineStr">
         <is>
-          <t>Dual‑Diol Synergized Electrolyte for Wide‑Temperature Hydrogel Zn‑Ion Batteries</t>
+          <t>Coordination Chemistry Enabled Multifunctional Electrolytes for High‐Rate and Long‐Cycle Sodium‐Metal Batteries</t>
         </is>
       </c>
       <c r="D108" s="55" t="inlineStr">
         <is>
-          <t>Qianyu Zhang</t>
+          <t>Chengxin Wang</t>
         </is>
       </c>
       <c r="E108" s="56" t="n">
@@ -15054,7 +15078,7 @@
       </c>
       <c r="F108" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71520</t>
+          <t>https://doi.org/10.1002/aenm.71442</t>
         </is>
       </c>
       <c r="G108" s="24" t="n"/>
@@ -15064,12 +15088,12 @@
       <c r="B109" s="24" t="n"/>
       <c r="C109" s="55" t="inlineStr">
         <is>
-          <t>Nanocrystalline LCO/LLZO Composite Cathode Films for Solid State Batteries</t>
+          <t>Dual‑Diol Synergized Electrolyte for Wide‑Temperature Hydrogel Zn‑Ion Batteries</t>
         </is>
       </c>
       <c r="D109" s="55" t="inlineStr">
         <is>
-          <t>Jennifer L. M. Rupp</t>
+          <t>Qianyu Zhang</t>
         </is>
       </c>
       <c r="E109" s="56" t="n">
@@ -15077,22 +15101,22 @@
       </c>
       <c r="F109" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71490</t>
+          <t>https://doi.org/10.1002/aenm.71520</t>
         </is>
       </c>
       <c r="G109" s="24" t="n"/>
     </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="25" t="n"/>
-      <c r="B110" s="25" t="n"/>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="24" t="n"/>
+      <c r="B110" s="24" t="n"/>
       <c r="C110" s="55" t="inlineStr">
         <is>
-          <t>Unraveling the Proton Co‐Insertion Chemistry through Electrolyte Hydrogen‐Bond Intervention for Zinc‐Manganese Dioxide Batteries</t>
+          <t>Nanocrystalline LCO/LLZO Composite Cathode Films for Solid State Batteries</t>
         </is>
       </c>
       <c r="D110" s="55" t="inlineStr">
         <is>
-          <t>Fei Xu</t>
+          <t>Jennifer L. M. Rupp</t>
         </is>
       </c>
       <c r="E110" s="56" t="n">
@@ -15100,82 +15124,78 @@
       </c>
       <c r="F110" s="57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1002/aenm.71490</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="n"/>
+    </row>
+    <row r="111" ht="48" customHeight="1">
+      <c r="A111" s="25" t="n"/>
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="55" t="inlineStr">
+        <is>
+          <t>Unraveling the Proton Co‐Insertion Chemistry through Electrolyte Hydrogen‐Bond Intervention for Zinc‐Manganese Dioxide Batteries</t>
+        </is>
+      </c>
+      <c r="D111" s="55" t="inlineStr">
+        <is>
+          <t>Fei Xu</t>
+        </is>
+      </c>
+      <c r="E111" s="56" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F111" s="57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1002/aenm.71483</t>
         </is>
       </c>
-      <c r="G110" s="25" t="n"/>
-    </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="58" t="inlineStr">
+      <c r="G111" s="25" t="n"/>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B111" s="59" t="inlineStr">
+      <c r="B112" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
         </is>
       </c>
-      <c r="C111" s="59" t="inlineStr">
+      <c r="C112" s="59" t="inlineStr">
         <is>
           <t>Molecular charge-topology electrolytes enable &gt;630 Wh kg−1 lithium-metal batteries</t>
         </is>
       </c>
-      <c r="D111" s="59" t="inlineStr">
+      <c r="D112" s="59" t="inlineStr">
         <is>
           <t>Xiulin Fan</t>
         </is>
       </c>
-      <c r="E111" s="60" t="n">
+      <c r="E112" s="60" t="n">
         <v>46254</v>
       </c>
-      <c r="F111" s="61" t="inlineStr">
+      <c r="F112" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.joule.2026.102634</t>
         </is>
       </c>
-      <c r="G111" s="59" t="n">
+      <c r="G112" s="59" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="24" t="n"/>
-      <c r="B112" s="25" t="n"/>
-      <c r="C112" s="59" t="inlineStr">
-        <is>
-          <t>Redox chemistry of halide materials unlocking next-generation all-solid-state batteries</t>
-        </is>
-      </c>
-      <c r="D112" s="59" t="inlineStr">
-        <is>
-          <t>Qiang Zhang</t>
-        </is>
-      </c>
-      <c r="E112" s="60" t="n">
-        <v>46258</v>
-      </c>
-      <c r="F112" s="61" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.joule.2026.102641</t>
-        </is>
-      </c>
-      <c r="G112" s="25" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="24" t="n"/>
-      <c r="B113" s="59" t="inlineStr">
-        <is>
-          <t>Chem</t>
-        </is>
-      </c>
+      <c r="B113" s="25" t="n"/>
       <c r="C113" s="59" t="inlineStr">
         <is>
-          <t>Molecular-scale engineering of sulfide solid electrolytes for all-solid-state batteries: Prospects and challenges</t>
+          <t>Redox chemistry of halide materials unlocking next-generation all-solid-state batteries</t>
         </is>
       </c>
       <c r="D113" s="59" t="inlineStr">
         <is>
-          <t>Ali Coskun</t>
+          <t>Qiang Zhang</t>
         </is>
       </c>
       <c r="E113" s="60" t="n">
@@ -15183,52 +15203,64 @@
       </c>
       <c r="F113" s="61" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1016/j.joule.2026.102641</t>
+        </is>
+      </c>
+      <c r="G113" s="25" t="n"/>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="24" t="n"/>
+      <c r="B114" s="59" t="inlineStr">
+        <is>
+          <t>Chem</t>
+        </is>
+      </c>
+      <c r="C114" s="59" t="inlineStr">
+        <is>
+          <t>Molecular-scale engineering of sulfide solid electrolytes for all-solid-state batteries: Prospects and challenges</t>
+        </is>
+      </c>
+      <c r="D114" s="59" t="inlineStr">
+        <is>
+          <t>Ali Coskun</t>
+        </is>
+      </c>
+      <c r="E114" s="60" t="n">
+        <v>46258</v>
+      </c>
+      <c r="F114" s="61" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.chempr.2026.103206</t>
         </is>
       </c>
-      <c r="G113" s="59" t="n">
+      <c r="G114" s="59" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="25" t="n"/>
-      <c r="B114" s="59" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="25" t="n"/>
+      <c r="B115" s="59" t="inlineStr">
         <is>
           <t>Materials Today</t>
         </is>
       </c>
-      <c r="C114" s="59" t="n"/>
-      <c r="D114" s="59" t="n"/>
-      <c r="E114" s="59" t="n"/>
-      <c r="F114" s="59" t="n"/>
-      <c r="G114" s="59" t="n">
+      <c r="C115" s="59" t="n"/>
+      <c r="D115" s="59" t="n"/>
+      <c r="E115" s="59" t="n"/>
+      <c r="F115" s="59" t="n"/>
+      <c r="G115" s="59" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="62" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="62" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B115" s="63" t="inlineStr">
+      <c r="B116" s="63" t="inlineStr">
         <is>
           <t>PNAS</t>
-        </is>
-      </c>
-      <c r="C115" s="63" t="n"/>
-      <c r="D115" s="63" t="n"/>
-      <c r="E115" s="63" t="n"/>
-      <c r="F115" s="63" t="n"/>
-      <c r="G115" s="63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="25" t="n"/>
-      <c r="B116" s="63" t="inlineStr">
-        <is>
-          <t>National Science Review</t>
         </is>
       </c>
       <c r="C116" s="63" t="n"/>
@@ -15239,31 +15271,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="25" t="n"/>
+      <c r="B117" s="63" t="inlineStr">
+        <is>
+          <t>National Science Review</t>
+        </is>
+      </c>
+      <c r="C117" s="63" t="n"/>
+      <c r="D117" s="63" t="n"/>
+      <c r="E117" s="63" t="n"/>
+      <c r="F117" s="63" t="n"/>
+      <c r="G117" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B52:B83"/>
+    <mergeCell ref="A34:A52"/>
+    <mergeCell ref="G86:G111"/>
+    <mergeCell ref="G24:G32"/>
+    <mergeCell ref="B86:B111"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="G34:G46"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G47:G51"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B24:B32"/>
     <mergeCell ref="G13:G22"/>
+    <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B112:B113"/>
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A116:A117"/>
     <mergeCell ref="B13:B22"/>
-    <mergeCell ref="B33:B45"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B46:B50"/>
-    <mergeCell ref="G24:G31"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="G52:G83"/>
-    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="G53:G84"/>
+    <mergeCell ref="A112:A115"/>
+    <mergeCell ref="A53:A111"/>
     <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G85:G110"/>
-    <mergeCell ref="A33:A51"/>
-    <mergeCell ref="A52:A110"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="G33:G45"/>
-    <mergeCell ref="B3:B5"/>
     <mergeCell ref="A6:A23"/>
-    <mergeCell ref="B85:B110"/>
-    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="B53:B84"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
@@ -15290,7 +15337,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId28"/>
@@ -15308,7 +15355,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId46"/>
@@ -15370,6 +15417,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19062,19 +19110,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="25" t="n"/>
       <c r="B23" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n"/>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="38" t="n"/>
-      <c r="F23" s="38" t="n"/>
+      <c r="C23" s="38" t="inlineStr">
+        <is>
+          <t>Zintl thermoelectrics: from impactful materials to real-world applications</t>
+        </is>
+      </c>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>Zhi-Gang Chen</t>
+        </is>
+      </c>
+      <c r="E23" s="39" t="n">
+        <v>46264</v>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6cs00567e</t>
+        </is>
+      </c>
       <c r="G23" s="38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
@@ -19655,24 +19717,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20476,7 +20539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21226,7 +21289,7 @@
         </is>
       </c>
       <c r="G31" s="38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
@@ -21254,7 +21317,7 @@
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="24" t="n"/>
-      <c r="B33" s="25" t="n"/>
+      <c r="B33" s="24" t="n"/>
       <c r="C33" s="41" t="inlineStr">
         <is>
           <t>Turning the bilayer upside down delivers a record-high Ba/Co-free cathode for proton-conducting solid oxide fuel cells</t>
@@ -21273,90 +21336,90 @@
           <t>https://doi.org/10.1039/d6ee03721f</t>
         </is>
       </c>
-      <c r="G33" s="25" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="G33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Vapor-bridge ion-isolation enables high-durability seawater electrolysis</t>
+        </is>
+      </c>
+      <c r="D34" s="41" t="inlineStr">
+        <is>
+          <t>Ronghui Qi</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F34" s="43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6ee03526d</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>Chemical Society Reviews</t>
         </is>
       </c>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n">
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="38" t="n"/>
+      <c r="E35" s="38" t="n"/>
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="44" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="44" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="B36" s="45" t="inlineStr">
         <is>
           <t>JACS</t>
         </is>
       </c>
-      <c r="C35" s="45" t="inlineStr">
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>A Quantitative Examination of Catalyst Component Impacts on Hydrogen Adsorption and Spillover</t>
         </is>
       </c>
-      <c r="D35" s="45" t="inlineStr">
+      <c r="D36" s="45" t="inlineStr">
         <is>
           <t>Bert D. Chandler</t>
         </is>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E36" s="46" t="n">
         <v>46238</v>
       </c>
-      <c r="F35" s="47" t="inlineStr">
+      <c r="F36" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/jacs.6c08946</t>
         </is>
       </c>
-      <c r="G35" s="45" t="n">
+      <c r="G36" s="45" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="24" t="n"/>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="48" t="inlineStr">
-        <is>
-          <t>Exceptionally High Proton Conductivity in Cucurbituril-Based Metal–Organic Frameworks with Subnanometer Scale Channels</t>
-        </is>
-      </c>
-      <c r="D36" s="48" t="inlineStr">
-        <is>
-          <t>Zhong-Min Su</t>
-        </is>
-      </c>
-      <c r="E36" s="49" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F36" s="50" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/jacs.6c11488</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="24" t="n"/>
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="48" t="inlineStr">
         <is>
-          <t>Polarized Metal Nitride Solid Solutions as Electrocatalysts Enabling Ampere-Level Selective Formic Acid Synthesis</t>
+          <t>Exceptionally High Proton Conductivity in Cucurbituril-Based Metal–Organic Frameworks with Subnanometer Scale Channels</t>
         </is>
       </c>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>Minghui Yang</t>
+          <t>Zhong-Min Su</t>
         </is>
       </c>
       <c r="E37" s="49" t="n">
@@ -21364,7 +21427,7 @@
       </c>
       <c r="F37" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c10367</t>
+          <t>https://doi.org/10.1021/jacs.6c11488</t>
         </is>
       </c>
       <c r="G37" s="24" t="n"/>
@@ -21374,20 +21437,20 @@
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="48" t="inlineStr">
         <is>
-          <t>Hexaphenylbenzene Nodes Reshape Hydroxide Transport Energetics in Rigid Microporous Membranes</t>
+          <t>Polarized Metal Nitride Solid Solutions as Electrocatalysts Enabling Ampere-Level Selective Formic Acid Synthesis</t>
         </is>
       </c>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>Tongwen Xu</t>
+          <t>Minghui Yang</t>
         </is>
       </c>
       <c r="E38" s="49" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c07266</t>
+          <t>https://doi.org/10.1021/jacs.6c10367</t>
         </is>
       </c>
       <c r="G38" s="24" t="n"/>
@@ -21397,12 +21460,12 @@
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="48" t="inlineStr">
         <is>
-          <t>Water Oxidation by Molecular Catalyst Bilayers Self-Assembled on Bismuth Vanadium Oxide (BVO) Photoelectrodes</t>
+          <t>Hexaphenylbenzene Nodes Reshape Hydroxide Transport Energetics in Rigid Microporous Membranes</t>
         </is>
       </c>
       <c r="D39" s="48" t="inlineStr">
         <is>
-          <t>Antoni Llobet</t>
+          <t>Tongwen Xu</t>
         </is>
       </c>
       <c r="E39" s="49" t="n">
@@ -21410,53 +21473,53 @@
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08907</t>
+          <t>https://doi.org/10.1021/jacs.6c07266</t>
         </is>
       </c>
       <c r="G39" s="24" t="n"/>
     </row>
-    <row r="40" ht="48" customHeight="1">
+    <row r="40" ht="32" customHeight="1">
       <c r="A40" s="24" t="n"/>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="48" t="inlineStr">
         <is>
-          <t>Nonequilibrium-Induced Defect-Rich Bifunctional Heterojunctions for Highly Selective Paired Electrosynthesis of Ammonium Formate</t>
+          <t>Water Oxidation by Molecular Catalyst Bilayers Self-Assembled on Bismuth Vanadium Oxide (BVO) Photoelectrodes</t>
         </is>
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>Jieshan Qiu</t>
+          <t>Antoni Llobet</t>
         </is>
       </c>
       <c r="E40" s="49" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c08564</t>
+          <t>https://doi.org/10.1021/jacs.6c08907</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
     </row>
-    <row r="41" ht="32" customHeight="1">
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="24" t="n"/>
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="48" t="inlineStr">
         <is>
-          <t>Essential Role of Ionic Surfactants in Nitrogen Fixation at the Interface of Microdroplets</t>
+          <t>Nonequilibrium-Induced Defect-Rich Bifunctional Heterojunctions for Highly Selective Paired Electrosynthesis of Ammonium Formate</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
         <is>
-          <t>Jincai Zhao</t>
+          <t>Jieshan Qiu</t>
         </is>
       </c>
       <c r="E41" s="49" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c03518</t>
+          <t>https://doi.org/10.1021/jacs.6c08564</t>
         </is>
       </c>
       <c r="G41" s="24" t="n"/>
@@ -21466,20 +21529,20 @@
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="48" t="inlineStr">
         <is>
-          <t>A Dual-Interlocked Electrocatalyst Design Principle for Durable AEM Water Electrolysis at Industrial Current Densities</t>
+          <t>Essential Role of Ionic Surfactants in Nitrogen Fixation at the Interface of Microdroplets</t>
         </is>
       </c>
       <c r="D42" s="48" t="inlineStr">
         <is>
-          <t>Changshui Huang</t>
+          <t>Jincai Zhao</t>
         </is>
       </c>
       <c r="E42" s="49" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c14322</t>
+          <t>https://doi.org/10.1021/jacs.6c03518</t>
         </is>
       </c>
       <c r="G42" s="24" t="n"/>
@@ -21489,12 +21552,12 @@
       <c r="B43" s="24" t="n"/>
       <c r="C43" s="48" t="inlineStr">
         <is>
-          <t>Aligning H2 Activation with Functional-Group Polarity: K+-Promoted Switchable Hydrogenation on Pd/TiO2</t>
+          <t>A Dual-Interlocked Electrocatalyst Design Principle for Durable AEM Water Electrolysis at Industrial Current Densities</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
         <is>
-          <t>Can Li</t>
+          <t>Changshui Huang</t>
         </is>
       </c>
       <c r="E43" s="49" t="n">
@@ -21502,22 +21565,22 @@
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c10350</t>
+          <t>https://doi.org/10.1021/jacs.6c14322</t>
         </is>
       </c>
       <c r="G43" s="24" t="n"/>
     </row>
-    <row r="44" ht="48" customHeight="1">
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="24" t="n"/>
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="48" t="inlineStr">
         <is>
-          <t>Programmable Vacancy Topology in High-Entropy-Alloy-Inspired Multiprincipal Alloys Directs Ru-Centered Alkaline Hydrogen Evolution</t>
+          <t>Aligning H2 Activation with Functional-Group Polarity: K+-Promoted Switchable Hydrogenation on Pd/TiO2</t>
         </is>
       </c>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>Yi Cui</t>
+          <t>Can Li</t>
         </is>
       </c>
       <c r="E44" s="49" t="n">
@@ -21525,30 +21588,30 @@
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09149</t>
+          <t>https://doi.org/10.1021/jacs.6c10350</t>
         </is>
       </c>
       <c r="G44" s="24" t="n"/>
     </row>
-    <row r="45" ht="32" customHeight="1">
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="24" t="n"/>
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="48" t="inlineStr">
         <is>
-          <t>Hydrogel-Empowered Interfacial Reactive Hydrogen on Copper Enables Selective Nitrate-To-Ammonia Electrocatalysis</t>
+          <t>Programmable Vacancy Topology in High-Entropy-Alloy-Inspired Multiprincipal Alloys Directs Ru-Centered Alkaline Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
         <is>
-          <t>Qiang Xu</t>
+          <t>Yi Cui</t>
         </is>
       </c>
       <c r="E45" s="49" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09690</t>
+          <t>https://doi.org/10.1021/jacs.6c09149</t>
         </is>
       </c>
       <c r="G45" s="24" t="n"/>
@@ -21558,12 +21621,12 @@
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="48" t="inlineStr">
         <is>
-          <t>Toward In Situ Programming Ligand Desorption/Adsorption Dynamics of Metal Nanoparticles in Electrocatalysis</t>
+          <t>Hydrogel-Empowered Interfacial Reactive Hydrogen on Copper Enables Selective Nitrate-To-Ammonia Electrocatalysis</t>
         </is>
       </c>
       <c r="D46" s="48" t="inlineStr">
         <is>
-          <t>Wenping Hu</t>
+          <t>Qiang Xu</t>
         </is>
       </c>
       <c r="E46" s="49" t="n">
@@ -21571,7 +21634,7 @@
       </c>
       <c r="F46" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12699</t>
+          <t>https://doi.org/10.1021/jacs.6c09690</t>
         </is>
       </c>
       <c r="G46" s="24" t="n"/>
@@ -21581,20 +21644,20 @@
       <c r="B47" s="24" t="n"/>
       <c r="C47" s="48" t="inlineStr">
         <is>
-          <t>Decoupling the Impact of Surface Functionalization over Pt at the Cathode on Kinetics and Mass Transport in PEMFCs</t>
+          <t>Toward In Situ Programming Ligand Desorption/Adsorption Dynamics of Metal Nanoparticles in Electrocatalysis</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
         <is>
-          <t>Bingjun Xu</t>
+          <t>Wenping Hu</t>
         </is>
       </c>
       <c r="E47" s="49" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="F47" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c11994</t>
+          <t>https://doi.org/10.1021/jacs.6c12699</t>
         </is>
       </c>
       <c r="G47" s="24" t="n"/>
@@ -21604,20 +21667,20 @@
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="48" t="inlineStr">
         <is>
-          <t>Functional Carbon-Directed Synthesis of High-Entropy Alloys with Tuned Structure for Catalysis</t>
+          <t>Decoupling the Impact of Surface Functionalization over Pt at the Cathode on Kinetics and Mass Transport in PEMFCs</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>Jieshan Qiu</t>
+          <t>Bingjun Xu</t>
         </is>
       </c>
       <c r="E48" s="49" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c09541</t>
+          <t>https://doi.org/10.1021/jacs.6c11994</t>
         </is>
       </c>
       <c r="G48" s="24" t="n"/>
@@ -21627,12 +21690,12 @@
       <c r="B49" s="24" t="n"/>
       <c r="C49" s="48" t="inlineStr">
         <is>
-          <t>Molecular-Ionic Hybrid Modulates Intermediate Evolution from CO2 to Methanol at High Current Density</t>
+          <t>Functional Carbon-Directed Synthesis of High-Entropy Alloys with Tuned Structure for Catalysis</t>
         </is>
       </c>
       <c r="D49" s="48" t="inlineStr">
         <is>
-          <t>Buxing Han</t>
+          <t>Jieshan Qiu</t>
         </is>
       </c>
       <c r="E49" s="49" t="n">
@@ -21640,22 +21703,22 @@
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c11699</t>
+          <t>https://doi.org/10.1021/jacs.6c09541</t>
         </is>
       </c>
       <c r="G49" s="24" t="n"/>
     </row>
-    <row r="50" ht="48" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="24" t="n"/>
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="48" t="inlineStr">
         <is>
-          <t>Nanobubble Radical-Driven N2 Hydrogenation for Sustainable Ammonia Production: A Haber-Bosch Alternative under Mild Conditions</t>
+          <t>Molecular-Ionic Hybrid Modulates Intermediate Evolution from CO2 to Methanol at High Current Density</t>
         </is>
       </c>
       <c r="D50" s="48" t="inlineStr">
         <is>
-          <t>Guanglu Ge</t>
+          <t>Buxing Han</t>
         </is>
       </c>
       <c r="E50" s="49" t="n">
@@ -21663,30 +21726,30 @@
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c06081</t>
+          <t>https://doi.org/10.1021/jacs.6c11699</t>
         </is>
       </c>
       <c r="G50" s="24" t="n"/>
     </row>
-    <row r="51" ht="32" customHeight="1">
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="24" t="n"/>
       <c r="B51" s="24" t="n"/>
       <c r="C51" s="48" t="inlineStr">
         <is>
-          <t>Geometry-Dependent Electronic Structure for Enhanced Ammonia Synthesis: From Nanoparticle to Nanosheet and Metallene</t>
+          <t>Nanobubble Radical-Driven N2 Hydrogenation for Sustainable Ammonia Production: A Haber-Bosch Alternative under Mild Conditions</t>
         </is>
       </c>
       <c r="D51" s="48" t="inlineStr">
         <is>
-          <t>Lilong Jiang</t>
+          <t>Guanglu Ge</t>
         </is>
       </c>
       <c r="E51" s="49" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12661</t>
+          <t>https://doi.org/10.1021/jacs.6c06081</t>
         </is>
       </c>
       <c r="G51" s="24" t="n"/>
@@ -21696,35 +21759,35 @@
       <c r="B52" s="24" t="n"/>
       <c r="C52" s="48" t="inlineStr">
         <is>
-          <t>Lattice-Nitrogen-Mediated Electrochemical Nitrate Reduction Boosted by Single-Atom Antimony Doping</t>
+          <t>Geometry-Dependent Electronic Structure for Enhanced Ammonia Synthesis: From Nanoparticle to Nanosheet and Metallene</t>
         </is>
       </c>
       <c r="D52" s="48" t="inlineStr">
         <is>
-          <t>Hongfei Cheng</t>
+          <t>Lilong Jiang</t>
         </is>
       </c>
       <c r="E52" s="49" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12366</t>
+          <t>https://doi.org/10.1021/jacs.6c12661</t>
         </is>
       </c>
       <c r="G52" s="24" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="24" t="n"/>
-      <c r="B53" s="25" t="n"/>
+      <c r="B53" s="24" t="n"/>
       <c r="C53" s="48" t="inlineStr">
         <is>
-          <t>Main-Group Potassium-Assisted Dual-Site Relay Breaks the Activity–Stability Trade-Off in Acidic Oxygen Reduction</t>
+          <t>Lattice-Nitrogen-Mediated Electrochemical Nitrate Reduction Boosted by Single-Atom Antimony Doping</t>
         </is>
       </c>
       <c r="D53" s="48" t="inlineStr">
         <is>
-          <t>Zhenxing Liang</t>
+          <t>Hongfei Cheng</t>
         </is>
       </c>
       <c r="E53" s="49" t="n">
@@ -21732,159 +21795,159 @@
       </c>
       <c r="F53" s="50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/jacs.6c12145</t>
-        </is>
-      </c>
-      <c r="G53" s="25" t="n"/>
+          <t>https://doi.org/10.1021/jacs.6c12366</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="24" t="n"/>
-      <c r="B54" s="45" t="inlineStr">
-        <is>
-          <t>ACS Energy Letters</t>
-        </is>
-      </c>
-      <c r="C54" s="45" t="inlineStr">
-        <is>
-          <t>Building a Physics-Aware AI Ecosystem for Solid-State Hydrogen Storage Materials</t>
-        </is>
-      </c>
-      <c r="D54" s="45" t="inlineStr">
-        <is>
-          <t>Hao Li</t>
-        </is>
-      </c>
-      <c r="E54" s="46" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F54" s="47" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acsenergylett.6c01856</t>
-        </is>
-      </c>
-      <c r="G54" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="48" t="inlineStr">
+        <is>
+          <t>Main-Group Potassium-Assisted Dual-Site Relay Breaks the Activity–Stability Trade-Off in Acidic Oxygen Reduction</t>
+        </is>
+      </c>
+      <c r="D54" s="48" t="inlineStr">
+        <is>
+          <t>Zhenxing Liang</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="n">
+        <v>46256</v>
+      </c>
+      <c r="F54" s="50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/jacs.6c12145</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="24" t="n"/>
       <c r="B55" s="45" t="inlineStr">
         <is>
+          <t>ACS Energy Letters</t>
+        </is>
+      </c>
+      <c r="C55" s="45" t="inlineStr">
+        <is>
+          <t>Building a Physics-Aware AI Ecosystem for Solid-State Hydrogen Storage Materials</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr">
+        <is>
+          <t>Hao Li</t>
+        </is>
+      </c>
+      <c r="E55" s="46" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F55" s="47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acsenergylett.6c01856</t>
+        </is>
+      </c>
+      <c r="G55" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="24" t="n"/>
+      <c r="B56" s="45" t="inlineStr">
+        <is>
           <t>Chemical Reviews</t>
         </is>
       </c>
-      <c r="C55" s="45" t="inlineStr">
+      <c r="C56" s="45" t="inlineStr">
         <is>
           <t>A Review of Ammonia (NH3) Adsorption in Porous Solids</t>
         </is>
       </c>
-      <c r="D55" s="45" t="inlineStr">
+      <c r="D56" s="45" t="inlineStr">
         <is>
           <t>Michael Tsapatsis</t>
         </is>
       </c>
-      <c r="E55" s="46" t="n">
+      <c r="E56" s="46" t="n">
         <v>46251</v>
       </c>
-      <c r="F55" s="47" t="inlineStr">
+      <c r="F56" s="47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acs.chemrev.6c00035</t>
         </is>
       </c>
-      <c r="G55" s="45" t="n">
+      <c r="G56" s="45" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="25" t="n"/>
-      <c r="B56" s="25" t="n"/>
-      <c r="C56" s="48" t="inlineStr">
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="25" t="n"/>
+      <c r="B57" s="25" t="n"/>
+      <c r="C57" s="48" t="inlineStr">
         <is>
           <t>Recent Advances and Future Perspectives of Proton-Conducting Electrolytes for Reversible Solid Oxide Cells</t>
         </is>
       </c>
-      <c r="D56" s="48" t="inlineStr">
+      <c r="D57" s="48" t="inlineStr">
         <is>
           <t>Meilin Liu</t>
         </is>
       </c>
-      <c r="E56" s="49" t="n">
+      <c r="E57" s="49" t="n">
         <v>46254</v>
       </c>
-      <c r="F56" s="50" t="inlineStr">
+      <c r="F57" s="50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acs.chemrev.5c00529</t>
         </is>
       </c>
-      <c r="G56" s="25" t="n"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="51" t="inlineStr">
+      <c r="G57" s="25" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="51" t="inlineStr">
         <is>
           <t>Wiley</t>
         </is>
       </c>
-      <c r="B57" s="52" t="inlineStr">
+      <c r="B58" s="52" t="inlineStr">
         <is>
           <t>Angewandte</t>
         </is>
       </c>
-      <c r="C57" s="52" t="inlineStr">
+      <c r="C58" s="52" t="inlineStr">
         <is>
           <t>Electronic‐Geometric Pre‐Compensation Enables Intermetallic RhSb Bimetallenes for Efficient Nitrite Electroreduction</t>
         </is>
       </c>
-      <c r="D57" s="52" t="inlineStr">
+      <c r="D58" s="52" t="inlineStr">
         <is>
           <t>Yu Chen</t>
         </is>
       </c>
-      <c r="E57" s="53" t="n">
+      <c r="E58" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F57" s="54" t="inlineStr">
+      <c r="F58" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/anie.9586956</t>
         </is>
       </c>
-      <c r="G57" s="52" t="n">
+      <c r="G58" s="52" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="24" t="n"/>
-      <c r="B58" s="24" t="n"/>
-      <c r="C58" s="55" t="inlineStr">
-        <is>
-          <t>In Situ Explosion Induced “Stress + Defect” Structure for Enhanced Hydrogen Evolution Reaction</t>
-        </is>
-      </c>
-      <c r="D58" s="55" t="inlineStr">
-        <is>
-          <t>Siping Pang</t>
-        </is>
-      </c>
-      <c r="E58" s="56" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F58" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.4584169</t>
-        </is>
-      </c>
-      <c r="G58" s="24" t="n"/>
-    </row>
-    <row r="59" ht="48" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="24" t="n"/>
       <c r="B59" s="24" t="n"/>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Key Drivers of Activity and Selectivity in Cu‐Based Catalysts for Methanol Synthesis From CO2: Insights From Atomically Dispersed Promoters</t>
+          <t>In Situ Explosion Induced “Stress + Defect” Structure for Enhanced Hydrogen Evolution Reaction</t>
         </is>
       </c>
       <c r="D59" s="55" t="inlineStr">
         <is>
-          <t>Atsushi Urakawa</t>
+          <t>Siping Pang</t>
         </is>
       </c>
       <c r="E59" s="56" t="n">
@@ -21892,7 +21955,7 @@
       </c>
       <c r="F59" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2693293</t>
+          <t>https://doi.org/10.1002/anie.4584169</t>
         </is>
       </c>
       <c r="G59" s="24" t="n"/>
@@ -21902,12 +21965,12 @@
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
-          <t>Modulating Local Coordination in Single‐Atom Catalysts: From Fundamental Concepts to Emerging Breakthroughs in Electrocatalysis</t>
+          <t>Key Drivers of Activity and Selectivity in Cu‐Based Catalysts for Methanol Synthesis From CO2: Insights From Atomically Dispersed Promoters</t>
         </is>
       </c>
       <c r="D60" s="55" t="inlineStr">
         <is>
-          <t>Harun Tüysüz</t>
+          <t>Atsushi Urakawa</t>
         </is>
       </c>
       <c r="E60" s="56" t="n">
@@ -21915,22 +21978,22 @@
       </c>
       <c r="F60" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3059499</t>
+          <t>https://doi.org/10.1002/anie.2693293</t>
         </is>
       </c>
       <c r="G60" s="24" t="n"/>
     </row>
-    <row r="61" ht="32" customHeight="1">
+    <row r="61" ht="48" customHeight="1">
       <c r="A61" s="24" t="n"/>
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Natural Sunlight IR‐Driven Highly Efficient Synthesis of Acetaldehyde From Bioethanol Over Cu/Fe2O3</t>
+          <t>Modulating Local Coordination in Single‐Atom Catalysts: From Fundamental Concepts to Emerging Breakthroughs in Electrocatalysis</t>
         </is>
       </c>
       <c r="D61" s="55" t="inlineStr">
         <is>
-          <t>Junwang Tang</t>
+          <t>Harun Tüysüz</t>
         </is>
       </c>
       <c r="E61" s="56" t="n">
@@ -21938,7 +22001,7 @@
       </c>
       <c r="F61" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9513626</t>
+          <t>https://doi.org/10.1002/anie.3059499</t>
         </is>
       </c>
       <c r="G61" s="24" t="n"/>
@@ -21948,12 +22011,12 @@
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
-          <t>Unconventional‐Phase Pd20Te7 Octahedra With High‐Index Facets for Oxygen Reduction</t>
+          <t>Natural Sunlight IR‐Driven Highly Efficient Synthesis of Acetaldehyde From Bioethanol Over Cu/Fe2O3</t>
         </is>
       </c>
       <c r="D62" s="55" t="inlineStr">
         <is>
-          <t>Xiaoqing Huang</t>
+          <t>Junwang Tang</t>
         </is>
       </c>
       <c r="E62" s="56" t="n">
@@ -21961,7 +22024,7 @@
       </c>
       <c r="F62" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9215475</t>
+          <t>https://doi.org/10.1002/anie.9513626</t>
         </is>
       </c>
       <c r="G62" s="24" t="n"/>
@@ -21971,20 +22034,20 @@
       <c r="B63" s="24" t="n"/>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>A Bimetallic Covalent Organic Framework Photonic Synaptic Electrocatalysts</t>
+          <t>Unconventional‐Phase Pd20Te7 Octahedra With High‐Index Facets for Oxygen Reduction</t>
         </is>
       </c>
       <c r="D63" s="55" t="inlineStr">
         <is>
-          <t>Wenping Hu</t>
+          <t>Xiaoqing Huang</t>
         </is>
       </c>
       <c r="E63" s="56" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F63" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2636151</t>
+          <t>https://doi.org/10.1002/anie.9215475</t>
         </is>
       </c>
       <c r="G63" s="24" t="n"/>
@@ -21994,12 +22057,12 @@
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="55" t="inlineStr">
         <is>
-          <t>Modulated Structure‐Electronic Coupling at Pt/CeOx–TiO2 Interfaces Boosts Low‐Temperature Preferential CO Oxidation</t>
+          <t>A Bimetallic Covalent Organic Framework Photonic Synaptic Electrocatalysts</t>
         </is>
       </c>
       <c r="D64" s="55" t="inlineStr">
         <is>
-          <t>Hyun You Kim</t>
+          <t>Wenping Hu</t>
         </is>
       </c>
       <c r="E64" s="56" t="n">
@@ -22007,22 +22070,22 @@
       </c>
       <c r="F64" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7158452</t>
+          <t>https://doi.org/10.1002/anie.2636151</t>
         </is>
       </c>
       <c r="G64" s="24" t="n"/>
     </row>
-    <row r="65" ht="64" customHeight="1">
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="24" t="n"/>
       <c r="B65" s="24" t="n"/>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>Surface Hydroxyl Steered Adsorption Configuration for Efficient Photocatalysis Coupling Hydrogen Evolution and 5‐Hydroxymethylfurfural Selective Oxidation Toward 2,5‐Furandicarboxylic Acid Production</t>
+          <t>Modulated Structure‐Electronic Coupling at Pt/CeOx–TiO2 Interfaces Boosts Low‐Temperature Preferential CO Oxidation</t>
         </is>
       </c>
       <c r="D65" s="55" t="inlineStr">
         <is>
-          <t>Shaohua Shen</t>
+          <t>Hyun You Kim</t>
         </is>
       </c>
       <c r="E65" s="56" t="n">
@@ -22030,30 +22093,30 @@
       </c>
       <c r="F65" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3914874</t>
+          <t>https://doi.org/10.1002/anie.7158452</t>
         </is>
       </c>
       <c r="G65" s="24" t="n"/>
     </row>
-    <row r="66" ht="32" customHeight="1">
+    <row r="66" ht="64" customHeight="1">
       <c r="A66" s="24" t="n"/>
       <c r="B66" s="24" t="n"/>
       <c r="C66" s="55" t="inlineStr">
         <is>
-          <t>Cr‐Leaching Induced Vacancy Engineering for High‐Performance Anion Exchange Membrane Water Electrolysis</t>
+          <t>Surface Hydroxyl Steered Adsorption Configuration for Efficient Photocatalysis Coupling Hydrogen Evolution and 5‐Hydroxymethylfurfural Selective Oxidation Toward 2,5‐Furandicarboxylic Acid Production</t>
         </is>
       </c>
       <c r="D66" s="55" t="inlineStr">
         <is>
-          <t>Guoxiong Wang</t>
+          <t>Shaohua Shen</t>
         </is>
       </c>
       <c r="E66" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F66" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9991550</t>
+          <t>https://doi.org/10.1002/anie.3914874</t>
         </is>
       </c>
       <c r="G66" s="24" t="n"/>
@@ -22063,35 +22126,35 @@
       <c r="B67" s="24" t="n"/>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>Chlorination‐Induced Symmetry Breaking in Cu Single‐Atom Sites for Boosting Electrocatalytic Nitrate Reduction to Ammonia</t>
+          <t>Cr‐Leaching Induced Vacancy Engineering for High‐Performance Anion Exchange Membrane Water Electrolysis</t>
         </is>
       </c>
       <c r="D67" s="55" t="inlineStr">
         <is>
-          <t>Jingyu Sun</t>
+          <t>Guoxiong Wang</t>
         </is>
       </c>
       <c r="E67" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F67" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9873433</t>
+          <t>https://doi.org/10.1002/anie.9991550</t>
         </is>
       </c>
       <c r="G67" s="24" t="n"/>
     </row>
-    <row r="68" ht="48" customHeight="1">
+    <row r="68" ht="32" customHeight="1">
       <c r="A68" s="24" t="n"/>
       <c r="B68" s="24" t="n"/>
       <c r="C68" s="55" t="inlineStr">
         <is>
-          <t>Hydrophilic RuGd Alloy Redirecting Interfacial Water Adsorption Configuration for Long‐Term and Ampere‐Level Hydrogen Evolution</t>
+          <t>Chlorination‐Induced Symmetry Breaking in Cu Single‐Atom Sites for Boosting Electrocatalytic Nitrate Reduction to Ammonia</t>
         </is>
       </c>
       <c r="D68" s="55" t="inlineStr">
         <is>
-          <t>Gengtao Fu</t>
+          <t>Jingyu Sun</t>
         </is>
       </c>
       <c r="E68" s="56" t="n">
@@ -22099,7 +22162,7 @@
       </c>
       <c r="F68" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6236000</t>
+          <t>https://doi.org/10.1002/anie.9873433</t>
         </is>
       </c>
       <c r="G68" s="24" t="n"/>
@@ -22109,12 +22172,12 @@
       <c r="B69" s="24" t="n"/>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Oxophilic Gallium Single‐Atom Regulating Micropore‐Confined Os Atomic Clusters Enables Efficient Alkaline Hydrogen Electrocatalysis</t>
+          <t>Hydrophilic RuGd Alloy Redirecting Interfacial Water Adsorption Configuration for Long‐Term and Ampere‐Level Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D69" s="55" t="inlineStr">
         <is>
-          <t>Shaojun Guo</t>
+          <t>Gengtao Fu</t>
         </is>
       </c>
       <c r="E69" s="56" t="n">
@@ -22122,7 +22185,7 @@
       </c>
       <c r="F69" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2044894</t>
+          <t>https://doi.org/10.1002/anie.6236000</t>
         </is>
       </c>
       <c r="G69" s="24" t="n"/>
@@ -22132,81 +22195,81 @@
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="55" t="inlineStr">
         <is>
-          <t>Hydroxyl Surface Enrichment Strategy to Achieve Dual‐Mechanism Pathway for Overcoming the Activity–Stability Trade‐Off of Oxygen Evolution Reaction</t>
+          <t>Oxophilic Gallium Single‐Atom Regulating Micropore‐Confined Os Atomic Clusters Enables Efficient Alkaline Hydrogen Electrocatalysis</t>
         </is>
       </c>
       <c r="D70" s="55" t="inlineStr">
         <is>
-          <t>Dapeng Cao</t>
+          <t>Shaojun Guo</t>
         </is>
       </c>
       <c r="E70" s="56" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="F70" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7969121</t>
+          <t>https://doi.org/10.1002/anie.2044894</t>
         </is>
       </c>
       <c r="G70" s="24" t="n"/>
     </row>
-    <row r="71" ht="32" customHeight="1">
+    <row r="71" ht="48" customHeight="1">
       <c r="A71" s="24" t="n"/>
       <c r="B71" s="24" t="n"/>
       <c r="C71" s="55" t="inlineStr">
         <is>
-          <t>Tuning Reaction Pathways by Controlling Atomic Assembly on Oxide Clusters</t>
+          <t>Hydroxyl Surface Enrichment Strategy to Achieve Dual‐Mechanism Pathway for Overcoming the Activity–Stability Trade‐Off of Oxygen Evolution Reaction</t>
         </is>
       </c>
       <c r="D71" s="55" t="inlineStr">
         <is>
-          <t>Jin Wang</t>
+          <t>Dapeng Cao</t>
         </is>
       </c>
       <c r="E71" s="56" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="F71" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.4503768</t>
+          <t>https://doi.org/10.1002/anie.7969121</t>
         </is>
       </c>
       <c r="G71" s="24" t="n"/>
     </row>
-    <row r="72" ht="48" customHeight="1">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="24" t="n"/>
       <c r="B72" s="24" t="n"/>
       <c r="C72" s="55" t="inlineStr">
         <is>
-          <t>A Full‐Spectrum‐Responsive MOF‐on‐MOF Heterojunction Photocatalyst for Concurrent Nitrate Reduction and Biomass Oxidation</t>
+          <t>Tuning Reaction Pathways by Controlling Atomic Assembly on Oxide Clusters</t>
         </is>
       </c>
       <c r="D72" s="55" t="inlineStr">
         <is>
-          <t>Chao Liu</t>
+          <t>Jin Wang</t>
         </is>
       </c>
       <c r="E72" s="56" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F72" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.8582451</t>
+          <t>https://doi.org/10.1002/anie.4503768</t>
         </is>
       </c>
       <c r="G72" s="24" t="n"/>
     </row>
-    <row r="73" ht="32" customHeight="1">
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="24" t="n"/>
       <c r="B73" s="24" t="n"/>
       <c r="C73" s="55" t="inlineStr">
         <is>
-          <t>Accelerating H* Redistribution via Hydrogen Spillover for Enhanced Electrochemical Hydrogen Production From Formaldehyde</t>
+          <t>A Full‐Spectrum‐Responsive MOF‐on‐MOF Heterojunction Photocatalyst for Concurrent Nitrate Reduction and Biomass Oxidation</t>
         </is>
       </c>
       <c r="D73" s="55" t="inlineStr">
         <is>
-          <t>Yang Hou</t>
+          <t>Chao Liu</t>
         </is>
       </c>
       <c r="E73" s="56" t="n">
@@ -22214,7 +22277,7 @@
       </c>
       <c r="F73" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5574811</t>
+          <t>https://doi.org/10.1002/anie.8582451</t>
         </is>
       </c>
       <c r="G73" s="24" t="n"/>
@@ -22224,12 +22287,12 @@
       <c r="B74" s="24" t="n"/>
       <c r="C74" s="55" t="inlineStr">
         <is>
-          <t>Enhanced Photocatalytic Hydrogen Production Assisted by Seawater Ions</t>
+          <t>Accelerating H* Redistribution via Hydrogen Spillover for Enhanced Electrochemical Hydrogen Production From Formaldehyde</t>
         </is>
       </c>
       <c r="D74" s="55" t="inlineStr">
         <is>
-          <t>Hai‐Long Jiang</t>
+          <t>Yang Hou</t>
         </is>
       </c>
       <c r="E74" s="56" t="n">
@@ -22237,7 +22300,7 @@
       </c>
       <c r="F74" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3256076</t>
+          <t>https://doi.org/10.1002/anie.5574811</t>
         </is>
       </c>
       <c r="G74" s="24" t="n"/>
@@ -22247,12 +22310,12 @@
       <c r="B75" s="24" t="n"/>
       <c r="C75" s="55" t="inlineStr">
         <is>
-          <t>Mimicking Enzymatic Proton Channeling Enables Near‐Unity Selective Ammonia Electrosynthesis Beyond Neutral Limits</t>
+          <t>Enhanced Photocatalytic Hydrogen Production Assisted by Seawater Ions</t>
         </is>
       </c>
       <c r="D75" s="55" t="inlineStr">
         <is>
-          <t>Zhimin Chen</t>
+          <t>Hai‐Long Jiang</t>
         </is>
       </c>
       <c r="E75" s="56" t="n">
@@ -22260,7 +22323,7 @@
       </c>
       <c r="F75" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.2808377</t>
+          <t>https://doi.org/10.1002/anie.3256076</t>
         </is>
       </c>
       <c r="G75" s="24" t="n"/>
@@ -22270,12 +22333,12 @@
       <c r="B76" s="24" t="n"/>
       <c r="C76" s="55" t="inlineStr">
         <is>
-          <t>RuCo Nanoalloy Catalysts Obtained From In‐Situ Reconstruction of High‐Entropy Oxides for Green Ammonia Synthesis</t>
+          <t>Mimicking Enzymatic Proton Channeling Enables Near‐Unity Selective Ammonia Electrosynthesis Beyond Neutral Limits</t>
         </is>
       </c>
       <c r="D76" s="55" t="inlineStr">
         <is>
-          <t>Hideo Hosono</t>
+          <t>Zhimin Chen</t>
         </is>
       </c>
       <c r="E76" s="56" t="n">
@@ -22283,76 +22346,76 @@
       </c>
       <c r="F76" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9715444</t>
+          <t>https://doi.org/10.1002/anie.2808377</t>
         </is>
       </c>
       <c r="G76" s="24" t="n"/>
     </row>
-    <row r="77" ht="48" customHeight="1">
+    <row r="77" ht="32" customHeight="1">
       <c r="A77" s="24" t="n"/>
       <c r="B77" s="24" t="n"/>
       <c r="C77" s="55" t="inlineStr">
         <is>
-          <t>Highly Selective Electrocatalytic Ammonia Synthesis Enabled by Spatial Separation of Active Hydrogen Capture and Spillover Sites</t>
+          <t>RuCo Nanoalloy Catalysts Obtained From In‐Situ Reconstruction of High‐Entropy Oxides for Green Ammonia Synthesis</t>
         </is>
       </c>
       <c r="D77" s="55" t="inlineStr">
         <is>
-          <t>Honggang Fu</t>
+          <t>Hideo Hosono</t>
         </is>
       </c>
       <c r="E77" s="56" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="F77" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.5589616</t>
+          <t>https://doi.org/10.1002/anie.9715444</t>
         </is>
       </c>
       <c r="G77" s="24" t="n"/>
     </row>
-    <row r="78" ht="64" customHeight="1">
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="24" t="n"/>
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="55" t="inlineStr">
         <is>
-          <t>Pt‐Mediated Co‐Adsorption of Hydroxyl and Nitrogen‐Heterocyclic Species Over Cu/CuO Heterostructure Enhances Coupled Azotriazole Electrosynthesis and Dual‐Electrode Hydrogen Production</t>
+          <t>Highly Selective Electrocatalytic Ammonia Synthesis Enabled by Spatial Separation of Active Hydrogen Capture and Spillover Sites</t>
         </is>
       </c>
       <c r="D78" s="55" t="inlineStr">
         <is>
-          <t>Zhengxiao Guo</t>
+          <t>Honggang Fu</t>
         </is>
       </c>
       <c r="E78" s="56" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="F78" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3766558</t>
+          <t>https://doi.org/10.1002/anie.5589616</t>
         </is>
       </c>
       <c r="G78" s="24" t="n"/>
     </row>
-    <row r="79" ht="32" customHeight="1">
+    <row r="79" ht="64" customHeight="1">
       <c r="A79" s="24" t="n"/>
       <c r="B79" s="24" t="n"/>
       <c r="C79" s="55" t="inlineStr">
         <is>
-          <t>Chirality‐Driven Piezocatalysis in MOFs: Achieving Efficient Cocatalyst‐Free Hydrogen Evolution</t>
+          <t>Pt‐Mediated Co‐Adsorption of Hydroxyl and Nitrogen‐Heterocyclic Species Over Cu/CuO Heterostructure Enhances Coupled Azotriazole Electrosynthesis and Dual‐Electrode Hydrogen Production</t>
         </is>
       </c>
       <c r="D79" s="55" t="inlineStr">
         <is>
-          <t>Tianyi Ma</t>
+          <t>Zhengxiao Guo</t>
         </is>
       </c>
       <c r="E79" s="56" t="n">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="F79" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3163680</t>
+          <t>https://doi.org/10.1002/anie.3766558</t>
         </is>
       </c>
       <c r="G79" s="24" t="n"/>
@@ -22362,12 +22425,12 @@
       <c r="B80" s="24" t="n"/>
       <c r="C80" s="55" t="inlineStr">
         <is>
-          <t>Electrocatalytic Deuterated Nitric Acid Reduction to Deuterated Ammonia</t>
+          <t>Chirality‐Driven Piezocatalysis in MOFs: Achieving Efficient Cocatalyst‐Free Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D80" s="55" t="inlineStr">
         <is>
-          <t>Yifu Yu</t>
+          <t>Tianyi Ma</t>
         </is>
       </c>
       <c r="E80" s="56" t="n">
@@ -22375,7 +22438,7 @@
       </c>
       <c r="F80" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1338385</t>
+          <t>https://doi.org/10.1002/anie.3163680</t>
         </is>
       </c>
       <c r="G80" s="24" t="n"/>
@@ -22385,12 +22448,12 @@
       <c r="B81" s="24" t="n"/>
       <c r="C81" s="55" t="inlineStr">
         <is>
-          <t>Intermediate‐Mediated Selectivity in Electrocatalytic Nitrate Reduction for Nitrogen Product Synthesis</t>
+          <t>Electrocatalytic Deuterated Nitric Acid Reduction to Deuterated Ammonia</t>
         </is>
       </c>
       <c r="D81" s="55" t="inlineStr">
         <is>
-          <t>Xiao Zhang</t>
+          <t>Yifu Yu</t>
         </is>
       </c>
       <c r="E81" s="56" t="n">
@@ -22398,7 +22461,7 @@
       </c>
       <c r="F81" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.3154221</t>
+          <t>https://doi.org/10.1002/anie.1338385</t>
         </is>
       </c>
       <c r="G81" s="24" t="n"/>
@@ -22408,12 +22471,12 @@
       <c r="B82" s="24" t="n"/>
       <c r="C82" s="55" t="inlineStr">
         <is>
-          <t>Light‐Activated Dual‐Site Pathway Enables Efficient Hydrogen Release From Dodecahydro‐N‐ethylcarbazole</t>
+          <t>Intermediate‐Mediated Selectivity in Electrocatalytic Nitrate Reduction for Nitrogen Product Synthesis</t>
         </is>
       </c>
       <c r="D82" s="55" t="inlineStr">
         <is>
-          <t>Xuebin Yu</t>
+          <t>Xiao Zhang</t>
         </is>
       </c>
       <c r="E82" s="56" t="n">
@@ -22421,7 +22484,7 @@
       </c>
       <c r="F82" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.1230832</t>
+          <t>https://doi.org/10.1002/anie.3154221</t>
         </is>
       </c>
       <c r="G82" s="24" t="n"/>
@@ -22431,20 +22494,20 @@
       <c r="B83" s="24" t="n"/>
       <c r="C83" s="55" t="inlineStr">
         <is>
-          <t>Asymmetric Dipole‐Field Engineering in Chiral Mesostructures for Efficient Photocatalytic N2 Reduction</t>
+          <t>Light‐Activated Dual‐Site Pathway Enables Efficient Hydrogen Release From Dodecahydro‐N‐ethylcarbazole</t>
         </is>
       </c>
       <c r="D83" s="55" t="inlineStr">
         <is>
-          <t>Zhijie Yang</t>
+          <t>Xuebin Yu</t>
         </is>
       </c>
       <c r="E83" s="56" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="F83" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9685756</t>
+          <t>https://doi.org/10.1002/anie.1230832</t>
         </is>
       </c>
       <c r="G83" s="24" t="n"/>
@@ -22454,12 +22517,12 @@
       <c r="B84" s="24" t="n"/>
       <c r="C84" s="55" t="inlineStr">
         <is>
-          <t>De Novo Design of a Protein Binder to Probe Gas Channel and Enhance the Oxygen Tolerance of [NiFe]‐Hydrogenase</t>
+          <t>Asymmetric Dipole‐Field Engineering in Chiral Mesostructures for Efficient Photocatalytic N2 Reduction</t>
         </is>
       </c>
       <c r="D84" s="55" t="inlineStr">
         <is>
-          <t>Liyun Zhang</t>
+          <t>Zhijie Yang</t>
         </is>
       </c>
       <c r="E84" s="56" t="n">
@@ -22467,7 +22530,7 @@
       </c>
       <c r="F84" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6395554</t>
+          <t>https://doi.org/10.1002/anie.9685756</t>
         </is>
       </c>
       <c r="G84" s="24" t="n"/>
@@ -22477,12 +22540,12 @@
       <c r="B85" s="24" t="n"/>
       <c r="C85" s="55" t="inlineStr">
         <is>
-          <t>Rerouting Oxygen Evolution Through Interfacial Carbonate Chemistry in Near‐Neutral Seawater Electrolysis</t>
+          <t>De Novo Design of a Protein Binder to Probe Gas Channel and Enhance the Oxygen Tolerance of [NiFe]‐Hydrogenase</t>
         </is>
       </c>
       <c r="D85" s="55" t="inlineStr">
         <is>
-          <t>Ken Sakaushi</t>
+          <t>Liyun Zhang</t>
         </is>
       </c>
       <c r="E85" s="56" t="n">
@@ -22490,30 +22553,30 @@
       </c>
       <c r="F85" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.9159016</t>
+          <t>https://doi.org/10.1002/anie.6395554</t>
         </is>
       </c>
       <c r="G85" s="24" t="n"/>
     </row>
-    <row r="86" ht="48" customHeight="1">
+    <row r="86" ht="32" customHeight="1">
       <c r="A86" s="24" t="n"/>
       <c r="B86" s="24" t="n"/>
       <c r="C86" s="55" t="inlineStr">
         <is>
-          <t>Single Atom Catalysis Enables Preferential Middle‐Ring Dehydrogenation of Perhydro‐Dibenzyltoluene for Low‐Temperature Hydrogen Production</t>
+          <t>Rerouting Oxygen Evolution Through Interfacial Carbonate Chemistry in Near‐Neutral Seawater Electrolysis</t>
         </is>
       </c>
       <c r="D86" s="55" t="inlineStr">
         <is>
-          <t>Tao Zhang</t>
+          <t>Ken Sakaushi</t>
         </is>
       </c>
       <c r="E86" s="56" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="F86" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.6119233</t>
+          <t>https://doi.org/10.1002/anie.9159016</t>
         </is>
       </c>
       <c r="G86" s="24" t="n"/>
@@ -22523,35 +22586,35 @@
       <c r="B87" s="24" t="n"/>
       <c r="C87" s="55" t="inlineStr">
         <is>
+          <t>Single Atom Catalysis Enables Preferential Middle‐Ring Dehydrogenation of Perhydro‐Dibenzyltoluene for Low‐Temperature Hydrogen Production</t>
+        </is>
+      </c>
+      <c r="D87" s="55" t="inlineStr">
+        <is>
+          <t>Tao Zhang</t>
+        </is>
+      </c>
+      <c r="E87" s="56" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F87" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.6119233</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="n"/>
+    </row>
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="24" t="n"/>
+      <c r="B88" s="24" t="n"/>
+      <c r="C88" s="55" t="inlineStr">
+        <is>
           <t>A Triple‐Site Engineered Heterojunction Photocatalyst for Full‐Spectrum NH3 Synthesis via Synergistic Promotion of Water Oxidation and Nitrate Reduction</t>
         </is>
       </c>
-      <c r="D87" s="55" t="inlineStr">
+      <c r="D88" s="55" t="inlineStr">
         <is>
           <t>Chao Liu</t>
-        </is>
-      </c>
-      <c r="E87" s="56" t="n">
-        <v>46263</v>
-      </c>
-      <c r="F87" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/anie.9657393</t>
-        </is>
-      </c>
-      <c r="G87" s="24" t="n"/>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="24" t="n"/>
-      <c r="B88" s="25" t="n"/>
-      <c r="C88" s="55" t="inlineStr">
-        <is>
-          <t>Conjugation‐Controlled Ion Response in One‐Dimensional Covalent Organic Frameworks for Seawater Photocatalysis</t>
-        </is>
-      </c>
-      <c r="D88" s="55" t="inlineStr">
-        <is>
-          <t>Bo Tang</t>
         </is>
       </c>
       <c r="E88" s="56" t="n">
@@ -22559,82 +22622,82 @@
       </c>
       <c r="F88" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/anie.7279758</t>
-        </is>
-      </c>
-      <c r="G88" s="25" t="n"/>
+          <t>https://doi.org/10.1002/anie.9657393</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="24" t="n"/>
-      <c r="B89" s="52" t="inlineStr">
+      <c r="B89" s="25" t="n"/>
+      <c r="C89" s="55" t="inlineStr">
+        <is>
+          <t>Conjugation‐Controlled Ion Response in One‐Dimensional Covalent Organic Frameworks for Seawater Photocatalysis</t>
+        </is>
+      </c>
+      <c r="D89" s="55" t="inlineStr">
+        <is>
+          <t>Bo Tang</t>
+        </is>
+      </c>
+      <c r="E89" s="56" t="n">
+        <v>46263</v>
+      </c>
+      <c r="F89" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/anie.7279758</t>
+        </is>
+      </c>
+      <c r="G89" s="25" t="n"/>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="24" t="n"/>
+      <c r="B90" s="52" t="inlineStr">
         <is>
           <t>Advanced Materials</t>
         </is>
       </c>
-      <c r="C89" s="52" t="inlineStr">
+      <c r="C90" s="52" t="inlineStr">
         <is>
           <t>Steering the reaction pathway of methane-to-oxygenates with zero CO2 production via photo–thermal catalysis</t>
         </is>
       </c>
-      <c r="D89" s="52" t="inlineStr">
+      <c r="D90" s="52" t="inlineStr">
         <is>
           <t>Li Tan</t>
         </is>
       </c>
-      <c r="E89" s="53" t="n">
+      <c r="E90" s="53" t="n">
         <v>46239</v>
       </c>
-      <c r="F89" s="54" t="inlineStr">
+      <c r="F90" s="54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/nsr/nwag472</t>
         </is>
       </c>
-      <c r="G89" s="52" t="n">
+      <c r="G90" s="52" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="90" ht="48" customHeight="1">
-      <c r="A90" s="24" t="n"/>
-      <c r="B90" s="24" t="n"/>
-      <c r="C90" s="55" t="inlineStr">
-        <is>
-          <t>Electron delocalization in a fullerene-dumbbell triad: synergistically optimizing carrier dynamics for boosting photocatalytic hydrogen evolution</t>
-        </is>
-      </c>
-      <c r="D90" s="55" t="inlineStr">
-        <is>
-          <t>Chunli Bai</t>
-        </is>
-      </c>
-      <c r="E90" s="56" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F90" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/nsr/nwag479</t>
-        </is>
-      </c>
-      <c r="G90" s="24" t="n"/>
-    </row>
-    <row r="91" ht="32" customHeight="1">
+    <row r="91" ht="48" customHeight="1">
       <c r="A91" s="24" t="n"/>
       <c r="B91" s="24" t="n"/>
       <c r="C91" s="55" t="inlineStr">
         <is>
-          <t>High-spin active center enables magnetic-field-enhanced photocatalytic overall water splitting</t>
+          <t>Electron delocalization in a fullerene-dumbbell triad: synergistically optimizing carrier dynamics for boosting photocatalytic hydrogen evolution</t>
         </is>
       </c>
       <c r="D91" s="55" t="inlineStr">
         <is>
-          <t>Jinlong Gong</t>
+          <t>Chunli Bai</t>
         </is>
       </c>
       <c r="E91" s="56" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="F91" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag495</t>
+          <t>https://doi.org/10.1093/nsr/nwag479</t>
         </is>
       </c>
       <c r="G91" s="24" t="n"/>
@@ -22644,12 +22707,12 @@
       <c r="B92" s="24" t="n"/>
       <c r="C92" s="55" t="inlineStr">
         <is>
-          <t>Revealing the kinetics characteristics of low-temperature electrocatalytic ammonia oxidation reaction</t>
+          <t>High-spin active center enables magnetic-field-enhanced photocatalytic overall water splitting</t>
         </is>
       </c>
       <c r="D92" s="55" t="inlineStr">
         <is>
-          <t>Kui Jiao</t>
+          <t>Jinlong Gong</t>
         </is>
       </c>
       <c r="E92" s="56" t="n">
@@ -22657,7 +22720,7 @@
       </c>
       <c r="F92" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag493</t>
+          <t>https://doi.org/10.1093/nsr/nwag495</t>
         </is>
       </c>
       <c r="G92" s="24" t="n"/>
@@ -22667,133 +22730,133 @@
       <c r="B93" s="24" t="n"/>
       <c r="C93" s="55" t="inlineStr">
         <is>
-          <t>Product ammonia accumulation limits electrocatalytic nitric oxide reduction</t>
+          <t>Revealing the kinetics characteristics of low-temperature electrocatalytic ammonia oxidation reaction</t>
         </is>
       </c>
       <c r="D93" s="55" t="inlineStr">
         <is>
-          <t>Jingshan Luo</t>
+          <t>Kui Jiao</t>
         </is>
       </c>
       <c r="E93" s="56" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="F93" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag507</t>
+          <t>https://doi.org/10.1093/nsr/nwag493</t>
         </is>
       </c>
       <c r="G93" s="24" t="n"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="24" t="n"/>
-      <c r="B94" s="25" t="n"/>
+      <c r="B94" s="24" t="n"/>
       <c r="C94" s="55" t="inlineStr">
         <is>
-          <t>Weak interfacial energy for magnesium salt-resistant ampere-level hydrogen production from natural seawater</t>
+          <t>Product ammonia accumulation limits electrocatalytic nitric oxide reduction</t>
         </is>
       </c>
       <c r="D94" s="55" t="inlineStr">
         <is>
-          <t>Lin Jiang</t>
+          <t>Jingshan Luo</t>
         </is>
       </c>
       <c r="E94" s="56" t="n">
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="F94" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/nsr/nwag535</t>
-        </is>
-      </c>
-      <c r="G94" s="25" t="n"/>
+          <t>https://doi.org/10.1093/nsr/nwag507</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="n"/>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="24" t="n"/>
-      <c r="B95" s="52" t="inlineStr">
-        <is>
-          <t>Advanced Energy Materials</t>
-        </is>
-      </c>
-      <c r="C95" s="52" t="inlineStr">
-        <is>
-          <t>Mechanism‐Driven Atomic‐Level Engineering Over RuO2‐Based Catalysts for Proton Exchange Membrane Water Electrolysis</t>
-        </is>
-      </c>
-      <c r="D95" s="52" t="inlineStr">
-        <is>
-          <t>Zongping Shao</t>
-        </is>
-      </c>
-      <c r="E95" s="53" t="n">
-        <v>46238</v>
-      </c>
-      <c r="F95" s="54" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71381</t>
-        </is>
-      </c>
-      <c r="G95" s="52" t="n">
-        <v>20</v>
-      </c>
+      <c r="B95" s="25" t="n"/>
+      <c r="C95" s="55" t="inlineStr">
+        <is>
+          <t>Weak interfacial energy for magnesium salt-resistant ampere-level hydrogen production from natural seawater</t>
+        </is>
+      </c>
+      <c r="D95" s="55" t="inlineStr">
+        <is>
+          <t>Lin Jiang</t>
+        </is>
+      </c>
+      <c r="E95" s="56" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F95" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/nsr/nwag535</t>
+        </is>
+      </c>
+      <c r="G95" s="25" t="n"/>
     </row>
     <row r="96" ht="32" customHeight="1">
       <c r="A96" s="24" t="n"/>
-      <c r="B96" s="24" t="n"/>
-      <c r="C96" s="55" t="inlineStr">
-        <is>
-          <t>MXene‐Derived Highly Oriented TiN Enables Ta3N5 Photoanodes for Transmission‐Mode Bias‐Free Solar Water Splitting</t>
-        </is>
-      </c>
-      <c r="D96" s="55" t="inlineStr">
-        <is>
-          <t>Ho Won Jang</t>
-        </is>
-      </c>
-      <c r="E96" s="56" t="n">
-        <v>46241</v>
-      </c>
-      <c r="F96" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71412</t>
-        </is>
-      </c>
-      <c r="G96" s="24" t="n"/>
+      <c r="B96" s="52" t="inlineStr">
+        <is>
+          <t>Advanced Energy Materials</t>
+        </is>
+      </c>
+      <c r="C96" s="52" t="inlineStr">
+        <is>
+          <t>Mechanism‐Driven Atomic‐Level Engineering Over RuO2‐Based Catalysts for Proton Exchange Membrane Water Electrolysis</t>
+        </is>
+      </c>
+      <c r="D96" s="52" t="inlineStr">
+        <is>
+          <t>Zongping Shao</t>
+        </is>
+      </c>
+      <c r="E96" s="53" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F96" s="54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71381</t>
+        </is>
+      </c>
+      <c r="G96" s="52" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="97" ht="32" customHeight="1">
       <c r="A97" s="24" t="n"/>
       <c r="B97" s="24" t="n"/>
       <c r="C97" s="55" t="inlineStr">
         <is>
-          <t>Charge‐Redistribution‐Driven Dual‐Single‐Atom Catalysts on MXene for Hydrogen Evolution</t>
+          <t>MXene‐Derived Highly Oriented TiN Enables Ta3N5 Photoanodes for Transmission‐Mode Bias‐Free Solar Water Splitting</t>
         </is>
       </c>
       <c r="D97" s="55" t="inlineStr">
         <is>
-          <t>Qinfen Gu</t>
+          <t>Ho Won Jang</t>
         </is>
       </c>
       <c r="E97" s="56" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F97" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71403</t>
+          <t>https://doi.org/10.1002/aenm.71412</t>
         </is>
       </c>
       <c r="G97" s="24" t="n"/>
     </row>
-    <row r="98" ht="48" customHeight="1">
+    <row r="98" ht="32" customHeight="1">
       <c r="A98" s="24" t="n"/>
       <c r="B98" s="24" t="n"/>
       <c r="C98" s="55" t="inlineStr">
         <is>
-          <t>Electrocatalytic Urea Waste Valorization via Water Electrolysis: Transition‐Metal Phosphides for Sustainable Hydrogen Production</t>
+          <t>Charge‐Redistribution‐Driven Dual‐Single‐Atom Catalysts on MXene for Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D98" s="55" t="inlineStr">
         <is>
-          <t>Yogendra Kumar Mishra</t>
+          <t>Qinfen Gu</t>
         </is>
       </c>
       <c r="E98" s="56" t="n">
@@ -22801,45 +22864,45 @@
       </c>
       <c r="F98" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71260</t>
+          <t>https://doi.org/10.1002/aenm.71403</t>
         </is>
       </c>
       <c r="G98" s="24" t="n"/>
     </row>
-    <row r="99" ht="32" customHeight="1">
+    <row r="99" ht="48" customHeight="1">
       <c r="A99" s="24" t="n"/>
       <c r="B99" s="24" t="n"/>
       <c r="C99" s="55" t="inlineStr">
         <is>
-          <t>Design Principles of Electrocatalysts for Industrial‐Scale Water Electrolysis</t>
+          <t>Electrocatalytic Urea Waste Valorization via Water Electrolysis: Transition‐Metal Phosphides for Sustainable Hydrogen Production</t>
         </is>
       </c>
       <c r="D99" s="55" t="inlineStr">
         <is>
-          <t>John Wang</t>
+          <t>Yogendra Kumar Mishra</t>
         </is>
       </c>
       <c r="E99" s="56" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="F99" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71379</t>
+          <t>https://doi.org/10.1002/aenm.71260</t>
         </is>
       </c>
       <c r="G99" s="24" t="n"/>
     </row>
-    <row r="100" ht="48" customHeight="1">
+    <row r="100" ht="32" customHeight="1">
       <c r="A100" s="24" t="n"/>
       <c r="B100" s="24" t="n"/>
       <c r="C100" s="55" t="inlineStr">
         <is>
-          <t>Directional Hydroxyl Spillover Enhances the Electrocatalytic Performance of Nickel Tungsten Zinc Heterostructure Toward Overall Water Splitting</t>
+          <t>Design Principles of Electrocatalysts for Industrial‐Scale Water Electrolysis</t>
         </is>
       </c>
       <c r="D100" s="55" t="inlineStr">
         <is>
-          <t>Zhongqing Liu</t>
+          <t>John Wang</t>
         </is>
       </c>
       <c r="E100" s="56" t="n">
@@ -22847,7 +22910,7 @@
       </c>
       <c r="F100" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71444</t>
+          <t>https://doi.org/10.1002/aenm.71379</t>
         </is>
       </c>
       <c r="G100" s="24" t="n"/>
@@ -22857,12 +22920,12 @@
       <c r="B101" s="24" t="n"/>
       <c r="C101" s="55" t="inlineStr">
         <is>
-          <t>Interpretable Machine Learning Framework Deciphers the Role of Local Environment of High‐Entropy Intermetallic Compounds for Alkaline Hydrogen Evolution Reaction</t>
+          <t>Directional Hydroxyl Spillover Enhances the Electrocatalytic Performance of Nickel Tungsten Zinc Heterostructure Toward Overall Water Splitting</t>
         </is>
       </c>
       <c r="D101" s="55" t="inlineStr">
         <is>
-          <t>Li‐Ming Yang</t>
+          <t>Zhongqing Liu</t>
         </is>
       </c>
       <c r="E101" s="56" t="n">
@@ -22870,22 +22933,22 @@
       </c>
       <c r="F101" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71361</t>
+          <t>https://doi.org/10.1002/aenm.71444</t>
         </is>
       </c>
       <c r="G101" s="24" t="n"/>
     </row>
-    <row r="102" ht="32" customHeight="1">
+    <row r="102" ht="48" customHeight="1">
       <c r="A102" s="24" t="n"/>
       <c r="B102" s="24" t="n"/>
       <c r="C102" s="55" t="inlineStr">
         <is>
-          <t>Seawater Electrolysis for Sustainable Hydrogen Production: From Material Design to System Engineering</t>
+          <t>Interpretable Machine Learning Framework Deciphers the Role of Local Environment of High‐Entropy Intermetallic Compounds for Alkaline Hydrogen Evolution Reaction</t>
         </is>
       </c>
       <c r="D102" s="55" t="inlineStr">
         <is>
-          <t>Jingshan Luo</t>
+          <t>Li‐Ming Yang</t>
         </is>
       </c>
       <c r="E102" s="56" t="n">
@@ -22893,7 +22956,7 @@
       </c>
       <c r="F102" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71426</t>
+          <t>https://doi.org/10.1002/aenm.71361</t>
         </is>
       </c>
       <c r="G102" s="24" t="n"/>
@@ -22903,81 +22966,81 @@
       <c r="B103" s="24" t="n"/>
       <c r="C103" s="55" t="inlineStr">
         <is>
-          <t>Fluorine‐Induced d‐p‐d Orbital Hybridization Promotes Hydrogen Spillover for Efficient Hydrogen Evolution</t>
+          <t>Seawater Electrolysis for Sustainable Hydrogen Production: From Material Design to System Engineering</t>
         </is>
       </c>
       <c r="D103" s="55" t="inlineStr">
         <is>
-          <t>Shichun Mu</t>
+          <t>Jingshan Luo</t>
         </is>
       </c>
       <c r="E103" s="56" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="F103" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71437</t>
+          <t>https://doi.org/10.1002/aenm.71426</t>
         </is>
       </c>
       <c r="G103" s="24" t="n"/>
     </row>
-    <row r="104" ht="48" customHeight="1">
+    <row r="104" ht="32" customHeight="1">
       <c r="A104" s="24" t="n"/>
       <c r="B104" s="24" t="n"/>
       <c r="C104" s="55" t="inlineStr">
         <is>
-          <t>Manipulating Valence‐Heterogeneous Pt Dual Sites via Metal‐Support Interactions for Highly Efficient Alkaline Hydrogen Evolution</t>
+          <t>Fluorine‐Induced d‐p‐d Orbital Hybridization Promotes Hydrogen Spillover for Efficient Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D104" s="55" t="inlineStr">
         <is>
-          <t>Hao Jiang</t>
+          <t>Shichun Mu</t>
         </is>
       </c>
       <c r="E104" s="56" t="n">
-        <v>46249</v>
+        <v>46247</v>
       </c>
       <c r="F104" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71456</t>
+          <t>https://doi.org/10.1002/aenm.71437</t>
         </is>
       </c>
       <c r="G104" s="24" t="n"/>
     </row>
-    <row r="105" ht="32" customHeight="1">
+    <row r="105" ht="48" customHeight="1">
       <c r="A105" s="24" t="n"/>
       <c r="B105" s="24" t="n"/>
       <c r="C105" s="55" t="inlineStr">
         <is>
-          <t>Cu@Cr2O3 Noble‐Metal‐Free Hydrogen‐Evolving Cocatalyst on Al‐Doped SrTiO3 for Photocatalytic Overall Water Splitting</t>
+          <t>Manipulating Valence‐Heterogeneous Pt Dual Sites via Metal‐Support Interactions for Highly Efficient Alkaline Hydrogen Evolution</t>
         </is>
       </c>
       <c r="D105" s="55" t="inlineStr">
         <is>
-          <t>Huagui Yang</t>
+          <t>Hao Jiang</t>
         </is>
       </c>
       <c r="E105" s="56" t="n">
-        <v>46253</v>
+        <v>46249</v>
       </c>
       <c r="F105" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71440</t>
+          <t>https://doi.org/10.1002/aenm.71456</t>
         </is>
       </c>
       <c r="G105" s="24" t="n"/>
     </row>
-    <row r="106" ht="48" customHeight="1">
+    <row r="106" ht="32" customHeight="1">
       <c r="A106" s="24" t="n"/>
       <c r="B106" s="24" t="n"/>
       <c r="C106" s="55" t="inlineStr">
         <is>
-          <t>Electric Double Layer Engineering Induces O‐Down Interfacial Water Reorientation for Efficient and Long‐Term Seawater Electrolysis</t>
+          <t>Cu@Cr2O3 Noble‐Metal‐Free Hydrogen‐Evolving Cocatalyst on Al‐Doped SrTiO3 for Photocatalytic Overall Water Splitting</t>
         </is>
       </c>
       <c r="D106" s="55" t="inlineStr">
         <is>
-          <t>Zhigang Shao</t>
+          <t>Huagui Yang</t>
         </is>
       </c>
       <c r="E106" s="56" t="n">
@@ -22985,68 +23048,68 @@
       </c>
       <c r="F106" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71429</t>
+          <t>https://doi.org/10.1002/aenm.71440</t>
         </is>
       </c>
       <c r="G106" s="24" t="n"/>
     </row>
-    <row r="107" ht="32" customHeight="1">
+    <row r="107" ht="48" customHeight="1">
       <c r="A107" s="24" t="n"/>
       <c r="B107" s="24" t="n"/>
       <c r="C107" s="55" t="inlineStr">
         <is>
-          <t>Indoor NFA‐Organic Photovoltaic for Grid‐Free Water Electrolysis</t>
+          <t>Electric Double Layer Engineering Induces O‐Down Interfacial Water Reorientation for Efficient and Long‐Term Seawater Electrolysis</t>
         </is>
       </c>
       <c r="D107" s="55" t="inlineStr">
         <is>
-          <t>Hyeok Kim</t>
+          <t>Zhigang Shao</t>
         </is>
       </c>
       <c r="E107" s="56" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="F107" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71363</t>
+          <t>https://doi.org/10.1002/aenm.71429</t>
         </is>
       </c>
       <c r="G107" s="24" t="n"/>
     </row>
-    <row r="108" ht="48" customHeight="1">
+    <row r="108" ht="32" customHeight="1">
       <c r="A108" s="24" t="n"/>
       <c r="B108" s="24" t="n"/>
       <c r="C108" s="55" t="inlineStr">
         <is>
-          <t>From Top to Bottom: Manufacturing Process‐Context Aware Resolution of Energy Device Electrodes Through a 3D Diffusion Generative Model</t>
+          <t>Indoor NFA‐Organic Photovoltaic for Grid‐Free Water Electrolysis</t>
         </is>
       </c>
       <c r="D108" s="55" t="inlineStr">
         <is>
-          <t>Alejandro A. Franco</t>
+          <t>Hyeok Kim</t>
         </is>
       </c>
       <c r="E108" s="56" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="F108" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71418</t>
+          <t>https://doi.org/10.1002/aenm.71363</t>
         </is>
       </c>
       <c r="G108" s="24" t="n"/>
     </row>
-    <row r="109" ht="32" customHeight="1">
+    <row r="109" ht="48" customHeight="1">
       <c r="A109" s="24" t="n"/>
       <c r="B109" s="24" t="n"/>
       <c r="C109" s="55" t="inlineStr">
         <is>
-          <t>Hybrid Ionomer‐Free Porous Transport Electrodes With Catalyst Coated Membranes for Enhanced Water Electrolysis</t>
+          <t>From Top to Bottom: Manufacturing Process‐Context Aware Resolution of Energy Device Electrodes Through a 3D Diffusion Generative Model</t>
         </is>
       </c>
       <c r="D109" s="55" t="inlineStr">
         <is>
-          <t>Aimy Bazylak</t>
+          <t>Alejandro A. Franco</t>
         </is>
       </c>
       <c r="E109" s="56" t="n">
@@ -23054,7 +23117,7 @@
       </c>
       <c r="F109" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71479</t>
+          <t>https://doi.org/10.1002/aenm.71418</t>
         </is>
       </c>
       <c r="G109" s="24" t="n"/>
@@ -23064,20 +23127,20 @@
       <c r="B110" s="24" t="n"/>
       <c r="C110" s="55" t="inlineStr">
         <is>
-          <t>Pt Single‐Atom Catalysts on FTO for Optically Invisible pH‐Universal Hydrogen Evolution Electrodes</t>
+          <t>Hybrid Ionomer‐Free Porous Transport Electrodes With Catalyst Coated Membranes for Enhanced Water Electrolysis</t>
         </is>
       </c>
       <c r="D110" s="55" t="inlineStr">
         <is>
-          <t>Patrik Schmuki</t>
+          <t>Aimy Bazylak</t>
         </is>
       </c>
       <c r="E110" s="56" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="F110" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71493</t>
+          <t>https://doi.org/10.1002/aenm.71479</t>
         </is>
       </c>
       <c r="G110" s="24" t="n"/>
@@ -23087,20 +23150,20 @@
       <c r="B111" s="24" t="n"/>
       <c r="C111" s="55" t="inlineStr">
         <is>
-          <t>Open AgRh Hollow Nanocubes With Interfacial Step Matching for Selective Nitrate‐to‐Ammonia Electrosynthesis</t>
+          <t>Pt Single‐Atom Catalysts on FTO for Optically Invisible pH‐Universal Hydrogen Evolution Electrodes</t>
         </is>
       </c>
       <c r="D111" s="55" t="inlineStr">
         <is>
-          <t>Xuan Ai</t>
+          <t>Patrik Schmuki</t>
         </is>
       </c>
       <c r="E111" s="56" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="F111" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71507</t>
+          <t>https://doi.org/10.1002/aenm.71493</t>
         </is>
       </c>
       <c r="G111" s="24" t="n"/>
@@ -23110,12 +23173,12 @@
       <c r="B112" s="24" t="n"/>
       <c r="C112" s="55" t="inlineStr">
         <is>
-          <t>Toward Scalable Water Electrolysis Catalysts: Mechanistic Insights, Structure‐Activity Relationships and Multiscale Design</t>
+          <t>Open AgRh Hollow Nanocubes With Interfacial Step Matching for Selective Nitrate‐to‐Ammonia Electrosynthesis</t>
         </is>
       </c>
       <c r="D112" s="55" t="inlineStr">
         <is>
-          <t>Hongwen Huang</t>
+          <t>Xuan Ai</t>
         </is>
       </c>
       <c r="E112" s="56" t="n">
@@ -23123,45 +23186,45 @@
       </c>
       <c r="F112" s="57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aenm.71510</t>
+          <t>https://doi.org/10.1002/aenm.71507</t>
         </is>
       </c>
       <c r="G112" s="24" t="n"/>
     </row>
-    <row r="113" ht="48" customHeight="1">
+    <row r="113" ht="32" customHeight="1">
       <c r="A113" s="24" t="n"/>
       <c r="B113" s="24" t="n"/>
       <c r="C113" s="55" t="inlineStr">
         <is>
+          <t>Toward Scalable Water Electrolysis Catalysts: Mechanistic Insights, Structure‐Activity Relationships and Multiscale Design</t>
+        </is>
+      </c>
+      <c r="D113" s="55" t="inlineStr">
+        <is>
+          <t>Hongwen Huang</t>
+        </is>
+      </c>
+      <c r="E113" s="56" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F113" s="57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/aenm.71510</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="48" customHeight="1">
+      <c r="A114" s="24" t="n"/>
+      <c r="B114" s="24" t="n"/>
+      <c r="C114" s="55" t="inlineStr">
+        <is>
           <t>Coupled Atmospheric Water Harvesting and Protonic Ceramic Electrolysis Enabling Self‐Sustained Green Hydrogen Production in Arid Regions (Adv. Energy Mater. 32/2026)</t>
         </is>
       </c>
-      <c r="D113" s="55" t="inlineStr">
+      <c r="D114" s="55" t="inlineStr">
         <is>
           <t>Wei Zhou</t>
-        </is>
-      </c>
-      <c r="E113" s="56" t="n">
-        <v>46260</v>
-      </c>
-      <c r="F113" s="57" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aenm.71346</t>
-        </is>
-      </c>
-      <c r="G113" s="24" t="n"/>
-    </row>
-    <row r="114" ht="48" customHeight="1">
-      <c r="A114" s="25" t="n"/>
-      <c r="B114" s="25" t="n"/>
-      <c r="C114" s="55" t="inlineStr">
-        <is>
-          <t>Functional Motif Directed Decoupling‐Recoupling Strategy for Constructing Multi‐Site Pt‐Based Catalyst Toward Efficient Hydrogen Oxidation in Fuel Cells</t>
-        </is>
-      </c>
-      <c r="D114" s="55" t="inlineStr">
-        <is>
-          <t>Xiaopeng Han</t>
         </is>
       </c>
       <c r="E114" s="56" t="n">
@@ -23169,190 +23232,213 @@
       </c>
       <c r="F114" s="57" t="inlineStr">
         <is>
+          <t>https://doi.org/10.1002/aenm.71346</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="n"/>
+    </row>
+    <row r="115" ht="48" customHeight="1">
+      <c r="A115" s="25" t="n"/>
+      <c r="B115" s="25" t="n"/>
+      <c r="C115" s="55" t="inlineStr">
+        <is>
+          <t>Functional Motif Directed Decoupling‐Recoupling Strategy for Constructing Multi‐Site Pt‐Based Catalyst Toward Efficient Hydrogen Oxidation in Fuel Cells</t>
+        </is>
+      </c>
+      <c r="D115" s="55" t="inlineStr">
+        <is>
+          <t>Xiaopeng Han</t>
+        </is>
+      </c>
+      <c r="E115" s="56" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F115" s="57" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1002/aenm.71431</t>
         </is>
       </c>
-      <c r="G114" s="25" t="n"/>
-    </row>
-    <row r="115" ht="48" customHeight="1">
-      <c r="A115" s="58" t="inlineStr">
+      <c r="G115" s="25" t="n"/>
+    </row>
+    <row r="116" ht="48" customHeight="1">
+      <c r="A116" s="58" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="B115" s="59" t="inlineStr">
+      <c r="B116" s="59" t="inlineStr">
         <is>
           <t>Joule</t>
         </is>
       </c>
-      <c r="C115" s="59" t="inlineStr">
+      <c r="C116" s="59" t="inlineStr">
         <is>
           <t>Sequentially adaptive electron transfer in heteroatom-modulated NiFe-MOFs for efficient anion exchange membrane water/seawater electrolysis</t>
         </is>
       </c>
-      <c r="D115" s="59" t="inlineStr">
+      <c r="D116" s="59" t="inlineStr">
         <is>
           <t>Liejin Guo</t>
         </is>
       </c>
-      <c r="E115" s="60" t="n">
+      <c r="E116" s="60" t="n">
         <v>46253</v>
       </c>
-      <c r="F115" s="61" t="inlineStr">
+      <c r="F116" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.joule.2026.102630</t>
         </is>
       </c>
-      <c r="G115" s="59" t="n">
+      <c r="G116" s="59" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" ht="32" customHeight="1">
-      <c r="A116" s="24" t="n"/>
-      <c r="B116" s="25" t="n"/>
-      <c r="C116" s="59" t="inlineStr">
-        <is>
-          <t>The dual role of iron in alkaline water electrolysis: A friend or a foe?</t>
-        </is>
-      </c>
-      <c r="D116" s="59" t="inlineStr">
-        <is>
-          <t>Meital Shviro</t>
-        </is>
-      </c>
-      <c r="E116" s="60" t="n">
-        <v>46259</v>
-      </c>
-      <c r="F116" s="61" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.joule.2026.102639</t>
-        </is>
-      </c>
-      <c r="G116" s="25" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="24" t="n"/>
-      <c r="B117" s="59" t="inlineStr">
+      <c r="B117" s="25" t="n"/>
+      <c r="C117" s="59" t="inlineStr">
+        <is>
+          <t>The dual role of iron in alkaline water electrolysis: A friend or a foe?</t>
+        </is>
+      </c>
+      <c r="D117" s="59" t="inlineStr">
+        <is>
+          <t>Meital Shviro</t>
+        </is>
+      </c>
+      <c r="E117" s="60" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F117" s="61" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.joule.2026.102639</t>
+        </is>
+      </c>
+      <c r="G117" s="25" t="n"/>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="24" t="n"/>
+      <c r="B118" s="59" t="inlineStr">
         <is>
           <t>Chem</t>
         </is>
       </c>
-      <c r="C117" s="59" t="inlineStr">
+      <c r="C118" s="59" t="inlineStr">
         <is>
           <t>Regulating transport processes in oxygen evolution catalyst layers for proton exchange membrane water electrolysis</t>
         </is>
       </c>
-      <c r="D117" s="59" t="inlineStr">
+      <c r="D118" s="59" t="inlineStr">
         <is>
           <t>Huabin Zhang</t>
         </is>
       </c>
-      <c r="E117" s="60" t="n">
+      <c r="E118" s="60" t="n">
         <v>46251</v>
       </c>
-      <c r="F117" s="61" t="inlineStr">
+      <c r="F118" s="61" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.chempr.2026.103198</t>
         </is>
       </c>
-      <c r="G117" s="59" t="n">
+      <c r="G118" s="59" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="25" t="n"/>
-      <c r="B118" s="59" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="25" t="n"/>
+      <c r="B119" s="59" t="inlineStr">
         <is>
           <t>Materials Today</t>
         </is>
       </c>
-      <c r="C118" s="59" t="n"/>
-      <c r="D118" s="59" t="n"/>
-      <c r="E118" s="59" t="n"/>
-      <c r="F118" s="59" t="n"/>
-      <c r="G118" s="59" t="n">
+      <c r="C119" s="59" t="n"/>
+      <c r="D119" s="59" t="n"/>
+      <c r="E119" s="59" t="n"/>
+      <c r="F119" s="59" t="n"/>
+      <c r="G119" s="59" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="62" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="62" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B119" s="63" t="inlineStr">
+      <c r="B120" s="63" t="inlineStr">
         <is>
           <t>PNAS</t>
         </is>
       </c>
-      <c r="C119" s="63" t="inlineStr">
+      <c r="C120" s="63" t="inlineStr">
         <is>
           <t>Hydrogen-ready infrastructure risks new carbon lock-in</t>
         </is>
       </c>
-      <c r="D119" s="63" t="inlineStr">
+      <c r="D120" s="63" t="inlineStr">
         <is>
           <t>Y. Frank Cheng</t>
         </is>
       </c>
-      <c r="E119" s="64" t="n">
+      <c r="E120" s="64" t="n">
         <v>46253</v>
       </c>
-      <c r="F119" s="65" t="inlineStr">
+      <c r="F120" s="65" t="inlineStr">
         <is>
           <t>https://doi.org/10.1073/pnas.2601685123</t>
         </is>
       </c>
-      <c r="G119" s="63" t="n">
+      <c r="G120" s="63" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="25" t="n"/>
-      <c r="B120" s="63" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="25" t="n"/>
+      <c r="B121" s="63" t="inlineStr">
         <is>
           <t>National Science Review</t>
         </is>
       </c>
-      <c r="C120" s="63" t="n"/>
-      <c r="D120" s="63" t="n"/>
-      <c r="E120" s="63" t="n"/>
-      <c r="F120" s="63" t="n"/>
-      <c r="G120" s="63" t="n">
+      <c r="C121" s="63" t="n"/>
+      <c r="D121" s="63" t="n"/>
+      <c r="E121" s="63" t="n"/>
+      <c r="F121" s="63" t="n"/>
+      <c r="G121" s="63" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="B35:B53"/>
-    <mergeCell ref="A57:A114"/>
+    <mergeCell ref="B58:B89"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="G16:G29"/>
-    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="A116:A119"/>
+    <mergeCell ref="G36:G54"/>
+    <mergeCell ref="G96:G115"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="G31:G34"/>
+    <mergeCell ref="A58:A115"/>
+    <mergeCell ref="A6:A30"/>
+    <mergeCell ref="B96:B115"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G95:G114"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="G58:G89"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="A36:A57"/>
     <mergeCell ref="B16:B29"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G57:G88"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="A35:A56"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="B95:B114"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="G89:G94"/>
-    <mergeCell ref="B57:B88"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="B89:B94"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A6:A30"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="G35:G53"/>
+    <mergeCell ref="G90:G95"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B36:B54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
@@ -23382,7 +23468,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId31"/>
@@ -23465,7 +23551,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
